--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -38,6 +38,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S9" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S10" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S11" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S12" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5119,7 +5120,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -19694,6 +19694,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -20011,6 +20012,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Table S11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Comparison of simulated and measured mass loss in HBSS (validation) with the experimental scatter. Experimental values are mean ± SD (n = 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Time (h)</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Experiment mean (%)</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Experiment SD (%)</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Simulation (%)</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Error (%)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>|Error|/SD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>336</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>-0.0139</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>672</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>RMSE / mean measured mass loss (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>RMSE / 28-day measured mass loss (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.9734</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20025,7 +20236,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Table S11</t>
+          <t>Table S12</t>
         </is>
       </c>
     </row>
@@ -37736,7 +37947,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -37995,7 +38205,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="n"/>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -16431,6 +16431,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -16635,7 +16636,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>0.899 mm³</t>
+          <t>0.361 mm³</t>
         </is>
       </c>
     </row>
@@ -19694,7 +19695,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -20037,7 +20037,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -20170,7 +20169,6 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -16431,7 +16431,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -16614,7 +16613,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>12.26 mm²</t>
+          <t>19.46 mm²</t>
         </is>
       </c>
     </row>
@@ -16658,7 +16657,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>13.6 mm⁻¹</t>
+          <t>53.9 mm⁻¹</t>
         </is>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -17777,7 +17777,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c).</t>
+          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c). Baseline: k_f = 10, k_d = 1, k_ORR = 0.2 (middle curves); each parameter varied by x0.2 and x5.</t>
         </is>
       </c>
     </row>
@@ -17796,17 +17796,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
+          <t>kf 2</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>kf 10</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
           <t>kf 50</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>kf 100</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>kf 200</t>
         </is>
       </c>
     </row>
@@ -17829,13 +17829,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.0429662868919724</v>
+        <v>0.027010018</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>0.0411159613859042</v>
+        <v>0.020944463</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.0380032394640408</v>
+        <v>0.014493756</v>
       </c>
     </row>
     <row r="9">
@@ -17843,13 +17843,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.0651247128436012</v>
+        <v>0.040939532</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>0.0623201438206168</v>
+        <v>0.03174587</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.0576021396367084</v>
+        <v>0.021968426</v>
       </c>
     </row>
     <row r="10">
@@ -17857,13 +17857,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.08306165435694809</v>
+        <v>0.052215282</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>0.0794846383113376</v>
+        <v>0.04048946</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.0734671801811258</v>
+        <v>0.028019068</v>
       </c>
     </row>
     <row r="11">
@@ -17871,13 +17871,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.0987106061462788</v>
+        <v>0.062052726</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>0.0944596744162195</v>
+        <v>0.048117741</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.0873085173138041</v>
+        <v>0.033297907</v>
       </c>
     </row>
     <row r="12">
@@ -17885,13 +17885,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.1128521471737548</v>
+        <v>0.070942563</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.107992215784869</v>
+        <v>0.055011215</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.0998165651097177</v>
+        <v>0.038068252</v>
       </c>
     </row>
     <row r="13">
@@ -17899,13 +17899,13 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.1258979255505868</v>
+        <v>0.079143568</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>0.1204761830715815</v>
+        <v>0.061370546</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.1113554220953369</v>
+        <v>0.042468965</v>
       </c>
     </row>
     <row r="14">
@@ -17913,13 +17913,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.1380977643771973</v>
+        <v>0.086812787</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>0.1321506408475195</v>
+        <v>0.067317512</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.1221460542371383</v>
+        <v>0.04658432</v>
       </c>
     </row>
     <row r="15">
@@ -17927,13 +17927,13 @@
         <v>32</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.149617301026198</v>
+        <v>0.094054345</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0.1431740933798423</v>
+        <v>0.072932857</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.1323349660899929</v>
+        <v>0.050470188</v>
       </c>
     </row>
     <row r="16">
@@ -17941,13 +17941,13 @@
         <v>36</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.1605732988251802</v>
+        <v>0.100941645</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0.1536582756313733</v>
+        <v>0.078273497</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.1420254336179192</v>
+        <v>0.054165959</v>
       </c>
     </row>
     <row r="17">
@@ -17955,13 +17955,13 @@
         <v>40</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.1710518690375297</v>
+        <v>0.107528818</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.1636855905192916</v>
+        <v>0.08338141</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.1512936213489629</v>
+        <v>0.05770068</v>
       </c>
     </row>
     <row r="18">
@@ -17969,13 +17969,13 @@
         <v>44</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.1811187595279918</v>
+        <v>0.113857195</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>0.173318954503539</v>
+        <v>0.088288644</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.1601976825942176</v>
+        <v>0.06109653</v>
       </c>
     </row>
     <row r="19">
@@ -17983,13 +17983,13 @@
         <v>48</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.1908255714463172</v>
+        <v>0.119959216</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.1826077465515357</v>
+        <v>0.093020353</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.1687832580406601</v>
+        <v>0.064370914</v>
       </c>
     </row>
     <row r="20">
@@ -17997,13 +17997,13 @@
         <v>52</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.2002137201785869</v>
+        <v>0.125860914</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0.1915915985127636</v>
+        <v>0.097596725</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.1770869791719161</v>
+        <v>0.06753780500000001</v>
       </c>
     </row>
     <row r="21">
@@ -18011,13 +18011,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.2093170692645675</v>
+        <v>0.131583579</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0.2003029156075511</v>
+        <v>0.102034269</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.1851387979411082</v>
+        <v>0.07060862499999999</v>
       </c>
     </row>
     <row r="22">
@@ -18025,13 +18025,13 @@
         <v>60</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.2181637446482995</v>
+        <v>0.137144889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>0.2087686125477053</v>
+        <v>0.106346693</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.1929635914568685</v>
+        <v>0.073592861</v>
       </c>
     </row>
     <row r="23">
@@ -18039,13 +18039,13 @@
         <v>64</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.2267774218019815</v>
+        <v>0.142559729</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>0.2170113452309337</v>
+        <v>0.11054554</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.2005823004311939</v>
+        <v>0.076498501</v>
       </c>
     </row>
     <row r="24">
@@ -18053,13 +18053,13 @@
         <v>68</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.2351782621332272</v>
+        <v>0.147840773</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>0.2250504068221084</v>
+        <v>0.114640636</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.2080127574220482</v>
+        <v>0.079332344</v>
       </c>
     </row>
     <row r="25">
@@ -18067,13 +18067,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.2433836091685503</v>
+        <v>0.152998923</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>0.2329023939558935</v>
+        <v>0.118640437</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.2152703026005029</v>
+        <v>0.082100242</v>
       </c>
     </row>
     <row r="26">
@@ -18081,13 +18081,13 @@
         <v>76</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.2514085160075617</v>
+        <v>0.158043643</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>0.240581711476345</v>
+        <v>0.12255228</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.2223682502785591</v>
+        <v>0.084807272</v>
       </c>
     </row>
     <row r="27">
@@ -18095,13 +18095,13 @@
         <v>80</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.2592661516327508</v>
+        <v>0.162983211</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>0.2481009612491277</v>
+        <v>0.126382584</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.2293182482859743</v>
+        <v>0.087457877</v>
       </c>
     </row>
     <row r="28">
@@ -18109,13 +18109,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.266968118539215</v>
+        <v>0.16782492</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>0.2554712461126508</v>
+        <v>0.130137006</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.2361305589104971</v>
+        <v>0.09005597</v>
       </c>
     </row>
     <row r="29">
@@ -18123,13 +18123,13 @@
         <v>88</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.2745247043223902</v>
+        <v>0.172575238</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>0.262702410631276</v>
+        <v>0.13382056</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.24281428142463</v>
+        <v>0.092605022</v>
       </c>
     </row>
     <row r="30">
@@ -18137,13 +18137,13 @@
         <v>92</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.281945083320059</v>
+        <v>0.177239931</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>0.2698032340536958</v>
+        <v>0.137437718</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.2493775304359155</v>
+        <v>0.095108128</v>
       </c>
     </row>
     <row r="31">
@@ -18151,13 +18151,13 @@
         <v>96</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.2892374799549966</v>
+        <v>0.181824171</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>0.2767815866212948</v>
+        <v>0.14099249</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.2558275803618279</v>
+        <v>0.097568061</v>
       </c>
     </row>
     <row r="32">
@@ -18165,13 +18165,13 @@
         <v>100</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.296409302338533</v>
+        <v>0.186332614</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0.2836445574181299</v>
+        <v>0.144488486</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.2621709836007526</v>
+        <v>0.099987323</v>
       </c>
     </row>
     <row r="33">
@@ -18179,13 +18179,13 @@
         <v>104</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.3034672525173613</v>
+        <v>0.190769473</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>0.2903985598700048</v>
+        <v>0.147928973</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.268413668044155</v>
+        <v>0.10236817</v>
       </c>
     </row>
     <row r="34">
@@ -18193,13 +18193,13 @@
         <v>108</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.3104174181843009</v>
+        <v>0.195138576</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>0.2970494195057467</v>
+        <v>0.15131692</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.2745610181938094</v>
+        <v>0.10471266</v>
       </c>
     </row>
     <row r="35">
@@ -18207,13 +18207,13 @@
         <v>112</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.3172653495377094</v>
+        <v>0.19944341</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>0.3036024475066994</v>
+        <v>0.154655031</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.2806179431431588</v>
+        <v>0.107022662</v>
       </c>
     </row>
     <row r="36">
@@ -18221,13 +18221,13 @@
         <v>116</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0.3240161241368163</v>
+        <v>0.203687168</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>0.3100625027690888</v>
+        <v>0.157945782</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.2865889339411921</v>
+        <v>0.109299892</v>
       </c>
     </row>
     <row r="37">
@@ -18235,13 +18235,13 @@
         <v>120</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0.3306744019753718</v>
+        <v>0.207872781</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>0.3164340446059475</v>
+        <v>0.161191444</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0.29247811230452</v>
+        <v>0.111545919</v>
       </c>
     </row>
     <row r="38">
@@ -18249,13 +18249,13 @@
         <v>124</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>0.3372444725244616</v>
+        <v>0.212002942</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>0.3227211777640495</v>
+        <v>0.164394109</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.298289272226262</v>
+        <v>0.113762192</v>
       </c>
     </row>
     <row r="39">
@@ -18263,13 +18263,13 @@
         <v>128</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0.3437302951357797</v>
+        <v>0.216080143</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0.3289276910872336</v>
+        <v>0.167555706</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.3040259157123265</v>
+        <v>0.115950045</v>
       </c>
     </row>
     <row r="40">
@@ -18277,13 +18277,13 @@
         <v>132</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0.3501355339198274</v>
+        <v>0.220106686</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0.3350570908925867</v>
+        <v>0.170678021</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.309691283630819</v>
+        <v>0.118110714</v>
       </c>
     </row>
     <row r="41">
@@ -18291,13 +18291,13 @@
         <v>136</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>0.3564635879984575</v>
+        <v>0.224084709</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>0.3411126299201744</v>
+        <v>0.173762711</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.3152883824701072</v>
+        <v>0.120245348</v>
       </c>
     </row>
     <row r="42">
@@ -18305,13 +18305,13 @@
         <v>140</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0.3627176178627089</v>
+        <v>0.228016197</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>0.3470973325557864</v>
+        <v>0.176811318</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.3208200076520545</v>
+        <v>0.122355011</v>
       </c>
     </row>
     <row r="43">
@@ -18319,13 +18319,13 @@
         <v>144</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>0.3689005684338637</v>
+        <v>0.231903003</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>0.3530140168988789</v>
+        <v>0.179825276</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.3262887639292887</v>
+        <v>0.124440696</v>
       </c>
     </row>
     <row r="44">
@@ -18333,13 +18333,13 @@
         <v>148</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0.3750151893198601</v>
+        <v>0.235746854</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>0.3588653141466531</v>
+        <v>0.182805925</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.3316970833017911</v>
+        <v>0.126503332</v>
       </c>
     </row>
     <row r="45">
@@ -18347,13 +18347,13 @@
         <v>152</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0.381064052674456</v>
+        <v>0.239549368</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>0.364653685684121</v>
+        <v>0.185754521</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.3370472408131425</v>
+        <v>0.128543787</v>
       </c>
     </row>
     <row r="46">
@@ -18361,13 +18361,13 @@
         <v>156</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0.3870495689982364</v>
+        <v>0.24331206</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>0.3703814382046497</v>
+        <v>0.188672237</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.3423413685263532</v>
+        <v>0.130562872</v>
       </c>
     </row>
     <row r="47">
@@ -18375,13 +18375,13 @@
         <v>160</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>0.3929740011651573</v>
+        <v>0.247036352</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>0.3760507371324572</v>
+        <v>0.191560177</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.347581467930196</v>
+        <v>0.132561353</v>
       </c>
     </row>
     <row r="48">
@@ -18389,13 +18389,13 @@
         <v>164</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>0.3988394769131198</v>
+        <v>0.250723583</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>0.3816636185752853</v>
+        <v>0.194419377</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.352769420986991</v>
+        <v>0.134539945</v>
       </c>
     </row>
     <row r="49">
@@ -18403,13 +18403,13 @@
         <v>168</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>0.404648</v>
+        <v>0.254375011</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>0.387222</v>
+        <v>0.197250816</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.357907</v>
+        <v>0.136499326</v>
       </c>
     </row>
     <row r="51">
@@ -18420,17 +18420,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>kd 10</t>
+          <t>kd 0.2</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 30</t>
+          <t>kd 1</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 50</t>
+          <t>kd 5</t>
         </is>
       </c>
     </row>
@@ -18453,13 +18453,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>0.0362595205692483</v>
+        <v>0.016113635</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>0.0411159613859042</v>
+        <v>0.020944463</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.0430257487468673</v>
+        <v>0.027010018</v>
       </c>
     </row>
     <row r="54">
@@ -18467,13 +18467,13 @@
         <v>8</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>0.0549591560205343</v>
+        <v>0.024423704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0.0623201438206168</v>
+        <v>0.03174587</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.0652148401621408</v>
+        <v>0.040939532</v>
       </c>
     </row>
     <row r="55">
@@ -18481,13 +18481,13 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>0.0700962541223048</v>
+        <v>0.03115059</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>0.0794846383113376</v>
+        <v>0.04048946</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.0831766049471892</v>
+        <v>0.052215282</v>
       </c>
     </row>
     <row r="56">
@@ -18495,13 +18495,13 @@
         <v>16</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>0.08330250326175349</v>
+        <v>0.037019413</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>0.0944596744162195</v>
+        <v>0.048117741</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.09884721361608451</v>
+        <v>0.062052726</v>
       </c>
     </row>
     <row r="57">
@@ -18509,13 +18509,13 @@
         <v>20</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>0.0952366389494811</v>
+        <v>0.042322911</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>0.107992215784869</v>
+        <v>0.055011215</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>0.1130083253889376</v>
+        <v>0.070942563</v>
       </c>
     </row>
     <row r="58">
@@ -18523,13 +18523,13 @@
         <v>24</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>0.1062460536235003</v>
+        <v>0.047215466</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>0.1204761830715815</v>
+        <v>0.061370546</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>0.1260721580645454</v>
+        <v>0.079143568</v>
       </c>
     </row>
     <row r="59">
@@ -18537,13 +18537,13 @@
         <v>28</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>0.1165415745743145</v>
+        <v>0.051790768</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>0.1321506408475195</v>
+        <v>0.067317512</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>0.1382888804782314</v>
+        <v>0.086812787</v>
       </c>
     </row>
     <row r="60">
@@ -18551,13 +18551,13 @@
         <v>32</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>0.1262629842256263</v>
+        <v>0.056110937</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>0.1431740933798423</v>
+        <v>0.072932857</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>0.1498243592312915</v>
+        <v>0.094054345</v>
       </c>
     </row>
     <row r="61">
@@ -18565,13 +18565,13 @@
         <v>36</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>0.1355088198862138</v>
+        <v>0.060219762</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>0.1536582756313733</v>
+        <v>0.078273497</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>0.1607955192422887</v>
+        <v>0.100941645</v>
       </c>
     </row>
     <row r="62">
@@ -18579,13 +18579,13 @@
         <v>40</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>0.144351751394498</v>
+        <v>0.06414953800000001</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>0.1636855905192916</v>
+        <v>0.08338141</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>0.1712885909456103</v>
+        <v>0.107528818</v>
       </c>
     </row>
     <row r="63">
@@ -18593,13 +18593,13 @@
         <v>44</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>0.1528472637883204</v>
+        <v>0.067924922</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>0.173318954503539</v>
+        <v>0.088288644</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>0.1813694131957121</v>
+        <v>0.113857195</v>
       </c>
     </row>
     <row r="64">
@@ -18607,13 +18607,13 @@
         <v>48</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>0.1610389036034915</v>
+        <v>0.071565264</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>0.1826077465515357</v>
+        <v>0.093020353</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>0.191089658554149</v>
+        <v>0.119959216</v>
       </c>
     </row>
     <row r="65">
@@ -18621,13 +18621,13 @@
         <v>52</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>0.168961621545602</v>
+        <v>0.075086099</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>0.1915915985127636</v>
+        <v>0.097596725</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>0.2004907997225362</v>
+        <v>0.125860914</v>
       </c>
     </row>
     <row r="66">
@@ -18635,13 +18635,13 @@
         <v>56</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>0.1766439952694955</v>
+        <v>0.078500126</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>0.2003029156075511</v>
+        <v>0.102034269</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>0.2096067471050317</v>
+        <v>0.131583579</v>
       </c>
     </row>
     <row r="67">
@@ -18649,13 +18649,13 @@
         <v>60</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>0.1841097604367859</v>
+        <v>0.081817892</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>0.2087686125477053</v>
+        <v>0.106346693</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>0.2184656655697004</v>
+        <v>0.137144889</v>
       </c>
     </row>
     <row r="68">
@@ -18663,13 +18663,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>0.1913788969278228</v>
+        <v>0.08504827700000001</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>0.2170113452309337</v>
+        <v>0.11054554</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>0.2270912633536736</v>
+        <v>0.142559729</v>
       </c>
     </row>
     <row r="69">
@@ -18677,13 +18677,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>0.1984684190816836</v>
+        <v>0.088198843</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>0.2250504068221084</v>
+        <v>0.114640636</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>0.2355037297663172</v>
+        <v>0.147840773</v>
       </c>
     </row>
     <row r="70">
@@ -18691,13 +18691,13 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>0.205392963209808</v>
+        <v>0.091276091</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>0.2329023939558935</v>
+        <v>0.118640437</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>0.2437204323361784</v>
+        <v>0.152998923</v>
       </c>
     </row>
     <row r="71">
@@ -18705,13 +18705,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>0.2121652327179232</v>
+        <v>0.09428567</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>0.240581711476345</v>
+        <v>0.12255228</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>0.2517564449951367</v>
+        <v>0.158043643</v>
       </c>
     </row>
     <row r="72">
@@ -18719,13 +18719,13 @@
         <v>80</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>0.2187963409934311</v>
+        <v>0.097232517</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>0.2481009612491277</v>
+        <v>0.126382584</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>0.2596249549504846</v>
+        <v>0.162983211</v>
       </c>
     </row>
     <row r="73">
@@ -18733,13 +18733,13 @@
         <v>84</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>0.2252960794551408</v>
+        <v>0.100120984</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>0.2554712461126508</v>
+        <v>0.130137006</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>0.2673375807542315</v>
+        <v>0.16782492</v>
       </c>
     </row>
     <row r="74">
@@ -18747,13 +18747,13 @@
         <v>88</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>0.2316731298697421</v>
+        <v>0.102954929</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>0.262702410631276</v>
+        <v>0.13382056</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>0.2749046242390104</v>
+        <v>0.172575238</v>
       </c>
     </row>
     <row r="75">
@@ -18761,13 +18761,13 @@
         <v>92</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>0.2379352345187678</v>
+        <v>0.105737791</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>0.2698032340536958</v>
+        <v>0.137437718</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>0.2823352724391433</v>
+        <v>0.177239931</v>
       </c>
     </row>
     <row r="76">
@@ -18775,13 +18775,13 @@
         <v>96</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>0.2440893340444831</v>
+        <v>0.108472657</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>0.2767815866212948</v>
+        <v>0.14099249</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>0.2896377611593391</v>
+        <v>0.181824171</v>
       </c>
     </row>
     <row r="77">
@@ -18789,13 +18789,13 @@
         <v>100</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>0.2501416801987751</v>
+        <v>0.111162303</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>0.2836445574181299</v>
+        <v>0.144488486</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>0.2968195087631529</v>
+        <v>0.186332614</v>
       </c>
     </row>
     <row r="78">
@@ -18803,13 +18803,13 @@
         <v>104</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>0.2560979288811291</v>
+        <v>0.113809244</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>0.2903985598700048</v>
+        <v>0.147928973</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>0.3038872265723665</v>
+        <v>0.190769473</v>
       </c>
     </row>
     <row r="79">
@@ -18817,13 +18817,13 @@
         <v>108</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>0.2619632175339208</v>
+        <v>0.116415763</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>0.2970494195057467</v>
+        <v>0.15131692</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>0.3108470107046722</v>
+        <v>0.195138576</v>
       </c>
     </row>
     <row r="80">
@@ -18831,13 +18831,13 @@
         <v>112</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>0.2677422300045587</v>
+        <v>0.118983941</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>0.3036024475066994</v>
+        <v>0.154655031</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>0.3177044190394519</v>
+        <v>0.19944341</v>
       </c>
     </row>
     <row r="81">
@@ -18845,13 +18845,13 @@
         <v>116</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>0.2734392512773094</v>
+        <v>0.121515683</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>0.3100625027690888</v>
+        <v>0.157945782</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>0.3244645361628651</v>
+        <v>0.203687168</v>
       </c>
     </row>
     <row r="82">
@@ -18859,13 +18859,13 @@
         <v>120</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>0.2790582139502972</v>
+        <v>0.124012734</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>0.3164340446059475</v>
+        <v>0.161191444</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>0.3311320285177153</v>
+        <v>0.207872781</v>
       </c>
     </row>
     <row r="83">
@@ -18873,13 +18873,13 @@
         <v>124</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>0.284602737935232</v>
+        <v>0.126476707</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>0.3227211777640495</v>
+        <v>0.164394109</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>0.3377111915113681</v>
+        <v>0.212002942</v>
       </c>
     </row>
     <row r="84">
@@ -18887,13 +18887,13 @@
         <v>128</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>0.290076164553987</v>
+        <v>0.128909083</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>0.3289276910872336</v>
+        <v>0.167555706</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>0.3442059899749388</v>
+        <v>0.216080143</v>
       </c>
     </row>
     <row r="85">
@@ -18901,13 +18901,13 @@
         <v>132</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>0.2954815859725299</v>
+        <v>0.131311238</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>0.3350570908925867</v>
+        <v>0.170678021</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>0.3506200930897606</v>
+        <v>0.220106686</v>
       </c>
     </row>
     <row r="86">
@@ -18915,13 +18915,13 @@
         <v>136</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>0.3008218707312362</v>
+        <v>0.133684447</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>0.3411126299201744</v>
+        <v>0.173762711</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>0.356956904681795</v>
+        <v>0.224084709</v>
       </c>
     </row>
     <row r="87">
@@ -18929,13 +18929,13 @@
         <v>140</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>0.3060996859884322</v>
+        <v>0.136029893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>0.3470973325557864</v>
+        <v>0.176811318</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>0.3632195896159441</v>
+        <v>0.228016197</v>
       </c>
     </row>
     <row r="88">
@@ -18943,13 +18943,13 @@
         <v>144</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>0.3113175169817667</v>
+        <v>0.138348684</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>0.3530140168988789</v>
+        <v>0.179825276</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>0.3694110968890221</v>
+        <v>0.231903003</v>
       </c>
     </row>
     <row r="89">
@@ -18957,13 +18957,13 @@
         <v>148</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>0.316477684122725</v>
+        <v>0.140641849</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>0.3588653141466531</v>
+        <v>0.182805925</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>0.3755341799142017</v>
+        <v>0.235746854</v>
       </c>
     </row>
     <row r="90">
@@ -18971,13 +18971,13 @@
         <v>152</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>0.3215823580680902</v>
+        <v>0.142910352</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>0.364653685684121</v>
+        <v>0.185754521</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>0.3815914144048925</v>
+        <v>0.239549368</v>
       </c>
     </row>
     <row r="91">
@@ -18985,13 +18985,13 @@
         <v>156</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>0.3266335730545134</v>
+        <v>0.145155099</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>0.3703814382046497</v>
+        <v>0.188672237</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>0.3875852141976171</v>
+        <v>0.24331206</v>
       </c>
     </row>
     <row r="92">
@@ -18999,13 +18999,13 @@
         <v>160</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>0.3316332387356017</v>
+        <v>0.147376937</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>0.3760507371324572</v>
+        <v>0.191560177</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>0.3935178452979653</v>
+        <v>0.247036352</v>
       </c>
     </row>
     <row r="93">
@@ -19013,13 +19013,13 @@
         <v>164</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>0.3365831507227929</v>
+        <v>0.149576665</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>0.3816636185752853</v>
+        <v>0.194419377</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>0.3993914383884547</v>
+        <v>0.250723583</v>
       </c>
     </row>
     <row r="94">
@@ -19027,13 +19027,13 @@
         <v>168</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>0.341485</v>
+        <v>0.151755034</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>0.387222</v>
+        <v>0.197250816</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>0.405208</v>
+        <v>0.254375011</v>
       </c>
     </row>
     <row r="96">
@@ -19044,17 +19044,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.1</t>
+          <t>kORR 0.04</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 1.0</t>
+          <t>kORR 0.2</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>kORR 5.0</t>
+          <t>kORR 1</t>
         </is>
       </c>
     </row>
@@ -19077,13 +19077,13 @@
         <v>4</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>0.01697153263347878</v>
+        <v>0.002584384</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>0.0495647493221488</v>
+        <v>0.025248274</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>0.1009050257615886</v>
+        <v>0.14042038</v>
       </c>
     </row>
     <row r="99">
@@ -19091,13 +19091,13 @@
         <v>8</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>0.02854260190570757</v>
+        <v>0.004346399</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>0.0725670405056887</v>
+        <v>0.036965637</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>0.1331449797291588</v>
+        <v>0.185285802</v>
       </c>
     </row>
     <row r="100">
@@ -19105,13 +19105,13 @@
         <v>12</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>0.03868672840535325</v>
+        <v>0.005891123</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>0.0906963070941338</v>
+        <v>0.046200682</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>0.1565890176139365</v>
+        <v>0.217910745</v>
       </c>
     </row>
     <row r="101">
@@ -19119,13 +19119,13 @@
         <v>16</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>0.04800274324904673</v>
+        <v>0.007309743</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>0.1062443660014857</v>
+        <v>0.054120861</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>0.1756858540323216</v>
+        <v>0.244486082</v>
       </c>
     </row>
     <row r="102">
@@ -19133,13 +19133,13 @@
         <v>20</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>0.05674773954614969</v>
+        <v>0.00864141</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>0.1201175364406902</v>
+        <v>0.061187851</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>0.1920882497272753</v>
+        <v>0.26731181</v>
       </c>
     </row>
     <row r="103">
@@ -19147,13 +19147,13 @@
         <v>24</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>0.06506306246791116</v>
+        <v>0.009907648</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>0.1327871658916131</v>
+        <v>0.067641758</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>0.2066204474817453</v>
+        <v>0.287534952</v>
       </c>
     </row>
     <row r="104">
@@ -19161,13 +19161,13 @@
         <v>28</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>0.0730372804034199</v>
+        <v>0.011121943</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>0.144536267742072</v>
+        <v>0.07362674800000001</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>0.219761703868764</v>
+        <v>0.305822448</v>
       </c>
     </row>
     <row r="105">
@@ -19175,13 +19175,13 @@
         <v>32</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>0.08073066944093561</v>
+        <v>0.012293473</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>0.155550856537587</v>
+        <v>0.079237578</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>0.2318188742065404</v>
+        <v>0.322601319</v>
       </c>
     </row>
     <row r="106">
@@ -19189,13 +19189,13 @@
         <v>36</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>0.08818667041049572</v>
+        <v>0.013428855</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>0.1659610960008948</v>
+        <v>0.084540552</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>0.2430019739079416</v>
+        <v>0.338163826</v>
       </c>
     </row>
     <row r="107">
@@ -19203,13 +19203,13 @@
         <v>40</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>0.09543794151621743</v>
+        <v>0.014533062</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>0.1758623669350419</v>
+        <v>0.089584258</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>0.2534619650816589</v>
+        <v>0.352720048</v>
       </c>
     </row>
     <row r="108">
@@ -19217,13 +19217,13 @@
         <v>44</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>0.102509845134179</v>
+        <v>0.015609954</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>0.1853270833261321</v>
+        <v>0.094405582</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>0.2633115270176449</v>
+        <v>0.36642679</v>
       </c>
     </row>
     <row r="109">
@@ -19231,13 +19231,13 @@
         <v>48</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>0.1094225919893903</v>
+        <v>0.016662611</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>0.1944117901870695</v>
+        <v>0.09903333</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>0.2726373149795983</v>
+        <v>0.379404644</v>
       </c>
     </row>
     <row r="110">
@@ -19245,13 +19245,13 @@
         <v>52</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>0.1161926288700976</v>
+        <v>0.017693536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>0.2031616623807895</v>
+        <v>0.103490514</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>0.2815076092887747</v>
+        <v>0.391748629</v>
       </c>
     </row>
     <row r="111">
@@ -19259,13 +19259,13 @@
         <v>56</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>0.1228335745422324</v>
+        <v>0.018704803</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>0.2116134821465347</v>
+        <v>0.107795869</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>0.2899773067397644</v>
+        <v>0.403535139</v>
       </c>
     </row>
     <row r="112">
@@ -19273,13 +19273,13 @@
         <v>60</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>0.1293568727616801</v>
+        <v>0.019698155</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>0.2197976812433385</v>
+        <v>0.111964899</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>0.2980913001404203</v>
+        <v>0.414826649</v>
       </c>
     </row>
     <row r="113">
@@ -19287,13 +19287,13 @@
         <v>64</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>0.1357722610678309</v>
+        <v>0.020675075</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>0.2277397840487711</v>
+        <v>0.116010604</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>0.3058868383819964</v>
+        <v>0.425674993</v>
       </c>
     </row>
     <row r="114">
@@ -19301,13 +19301,13 @@
         <v>68</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>0.142088115593446</v>
+        <v>0.021636839</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>0.2354614536156582</v>
+        <v>0.119944021</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>0.3133952185401816</v>
+        <v>0.436123725</v>
       </c>
     </row>
     <row r="115">
@@ -19315,13 +19315,13 @@
         <v>72</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>0.1483117100426936</v>
+        <v>0.022584553</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>0.2429812667383687</v>
+        <v>0.123774613</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>0.3206430269049575</v>
+        <v>0.446209843</v>
       </c>
     </row>
     <row r="116">
@@ -19329,13 +19329,13 @@
         <v>76</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>0.1544494137810347</v>
+        <v>0.023519188</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>0.2503152993086903</v>
+        <v>0.127510568</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>0.3276530673531115</v>
+        <v>0.455965081</v>
       </c>
     </row>
     <row r="117">
@@ -19343,13 +19343,13 @@
         <v>80</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>0.1605068458003621</v>
+        <v>0.024441599</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>0.2574775758847358</v>
+        <v>0.13115903</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>0.3344450680052921</v>
+        <v>0.465416893</v>
       </c>
     </row>
     <row r="118">
@@ -19357,13 +19357,13 @@
         <v>84</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>0.166488996100381</v>
+        <v>0.025352546</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>0.2644804201504752</v>
+        <v>0.134726278</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>0.3410362274648395</v>
+        <v>0.474589212</v>
       </c>
     </row>
     <row r="119">
@@ -19371,13 +19371,13 @@
         <v>88</v>
       </c>
       <c r="B119" s="1" t="n">
-        <v>0.1724003226030893</v>
+        <v>0.026252709</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>0.2713347317691131</v>
+        <v>0.138217863</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>0.3474416428974731</v>
+        <v>0.483503049</v>
       </c>
     </row>
     <row r="120">
@@ -19385,13 +19385,13 @@
         <v>92</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>0.1782448294184555</v>
+        <v>0.027142697</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>0.2780502077150376</v>
+        <v>0.141638725</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>0.353674649677192</v>
+        <v>0.492176959</v>
       </c>
     </row>
     <row r="121">
@@ -19399,13 +19399,13 @@
         <v>96</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>0.1840261307032963</v>
+        <v>0.028023059</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>0.2846355211360706</v>
+        <v>0.144993282</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>0.3597470938874613</v>
+        <v>0.50062743</v>
       </c>
     </row>
     <row r="122">
@@ -19413,13 +19413,13 @@
         <v>100</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>0.1897475032540739</v>
+        <v>0.028894296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>0.2910984673160255</v>
+        <v>0.148285506</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>0.3656695531743668</v>
+        <v>0.5088691789999999</v>
       </c>
     </row>
     <row r="123">
@@ -19427,13 +19427,13 @@
         <v>104</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>0.1954119301915406</v>
+        <v>0.029756862</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>0.2974460838562484</v>
+        <v>0.151518981</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>0.3714515173993034</v>
+        <v>0.516915415</v>
       </c>
     </row>
     <row r="124">
@@ -19441,13 +19441,13 @@
         <v>108</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>0.2010221375300704</v>
+        <v>0.030611171</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>0.3036847504411751</v>
+        <v>0.154696956</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>0.3771015376617351</v>
+        <v>0.5247780359999999</v>
       </c>
     </row>
     <row r="125">
@@ -19455,13 +19455,13 @@
         <v>112</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>0.2065806250107267</v>
+        <v>0.031457604</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>0.3098202722799865</v>
+        <v>0.15782239</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>0.3826273501877372</v>
+        <v>0.532467809</v>
       </c>
     </row>
     <row r="126">
@@ -19469,13 +19469,13 @@
         <v>116</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>0.2120896922702152</v>
+        <v>0.032296511</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>0.3158579503800385</v>
+        <v>0.160897982</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>0.3880359800632164</v>
+        <v>0.539994509</v>
       </c>
     </row>
     <row r="127">
@@ -19483,13 +19483,13 @@
         <v>120</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>0.2175514611874552</v>
+        <v>0.033128217</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>0.321802641110388</v>
+        <v>0.163926206</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>0.3933338286678619</v>
+        <v>0.547367045</v>
       </c>
     </row>
     <row r="128">
@@ -19497,13 +19497,13 @@
         <v>124</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>0.2229678950746506</v>
+        <v>0.033953018</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>0.3276588069885106</v>
+        <v>0.166909336</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>0.3985267478250344</v>
+        <v>0.55459356</v>
       </c>
     </row>
     <row r="129">
@@ -19511,13 +19511,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>0.228340815245661</v>
+        <v>0.034771194</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>0.3334305602235516</v>
+        <v>0.169849466</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>0.4036201030463542</v>
+        <v>0.561681521</v>
       </c>
     </row>
     <row r="130">
@@ -19525,13 +19525,13 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>0.2336719153907026</v>
+        <v>0.035583001</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>0.3391217002422295</v>
+        <v>0.172748532</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>0.4086188277632268</v>
+        <v>0.5686377929999999</v>
       </c>
     </row>
     <row r="131">
@@ -19539,13 +19539,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>0.2389627741053685</v>
+        <v>0.03638868</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>0.3447357461852496</v>
+        <v>0.175608326</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>0.4135274700621696</v>
+        <v>0.575468705</v>
       </c>
     </row>
     <row r="132">
@@ -19553,13 +19553,13 @@
         <v>140</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>0.2442148658581579</v>
+        <v>0.037188456</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>0.3502759651757481</v>
+        <v>0.178430513</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>0.4183502331486854</v>
+        <v>0.582180108</v>
       </c>
     </row>
     <row r="133">
@@ -19567,13 +19567,13 @@
         <v>144</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>0.2494295706300989</v>
+        <v>0.037982539</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>0.3557453970143943</v>
+        <v>0.18121664</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>0.4230910105352574</v>
+        <v>0.5887774180000001</v>
       </c>
     </row>
     <row r="134">
@@ -19581,13 +19581,13 @@
         <v>148</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>0.2546081824195844</v>
+        <v>0.038771126</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>0.3611468758391253</v>
+        <v>0.183968152</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>0.4277534167678934</v>
+        <v>0.595265666</v>
       </c>
     </row>
     <row r="135">
@@ -19595,13 +19595,13 @@
         <v>152</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>0.2597519167730197</v>
+        <v>0.039554401</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>0.3664830491942015</v>
+        <v>0.186686398</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>0.4323408143614345</v>
+        <v>0.601649532</v>
       </c>
     </row>
     <row r="136">
@@ -19609,13 +19609,13 @@
         <v>156</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>0.2648619174755151</v>
+        <v>0.04033254</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>0.371756394878181</v>
+        <v>0.189372639</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>0.4368563374982794</v>
+        <v>0.607933376</v>
       </c>
     </row>
     <row r="137">
@@ -19623,13 +19623,13 @@
         <v>160</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>0.2699392625144103</v>
+        <v>0.041105706</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>0.3769692358795961</v>
+        <v>0.19202806</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>0.4413029129519614</v>
+        <v>0.614121272</v>
       </c>
     </row>
     <row r="138">
@@ -19637,13 +19637,13 @@
         <v>164</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>0.2749849694108313</v>
+        <v>0.041874054</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>0.3821237536595659</v>
+        <v>0.19465377</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>0.4456832786214058</v>
+        <v>0.6202170299999999</v>
       </c>
     </row>
     <row r="139">
@@ -19651,13 +19651,13 @@
         <v>168</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>0.28</v>
+        <v>0.042637731</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>0.387222</v>
+        <v>0.197250816</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>0.45</v>
+        <v>0.62622422</v>
       </c>
     </row>
   </sheetData>
@@ -20570,14 +20570,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Corrosion-product film coverage response (%) to one-at-a-time parameter sweeps of k_f (panel d), k_d (panel e), and k_ORR (panel f).</t>
+          <t>Corrosion-product saturation, F/Fmax (%), in one-at-a-time parameter sweeps of k_f (panel d), k_d (panel e), and k_ORR (panel f). Baseline: k_f = 10, k_d = 1, k_ORR = 0.2 (middle curves); each parameter varied by x0.2 and x5.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Predicted film formation with kinetic parameter sweep</t>
+          <t>Predicted corrosion-product saturation with kinetic parameter sweep</t>
         </is>
       </c>
     </row>
@@ -20589,17 +20589,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
+          <t>kf 2</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>kf 10</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
           <t>kf 50</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>kf 100</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>kf 200</t>
         </is>
       </c>
     </row>
@@ -20622,13 +20622,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1.615648656113079</v>
+        <v>1.719593377</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>2.634205069212848</v>
+        <v>4.449777209</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>3.878846750677074</v>
+        <v>6.556953225</v>
       </c>
     </row>
     <row r="9">
@@ -20636,13 +20636,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>2.284872241504981</v>
+        <v>2.431872276</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>3.725328534952767</v>
+        <v>6.292935279</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>5.485517681174328</v>
+        <v>9.272932179</v>
       </c>
     </row>
     <row r="10">
@@ -20650,13 +20650,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>2.798385559568231</v>
+        <v>2.978423098</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>4.562577017432145</v>
+        <v>7.707240209</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>6.718359646946142</v>
+        <v>11.35697613</v>
       </c>
     </row>
     <row r="11">
@@ -20664,13 +20664,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>3.231297312226159</v>
+        <v>3.439186755</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>5.268410138425697</v>
+        <v>8.899554418999999</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>7.757693501354148</v>
+        <v>13.11390645</v>
       </c>
     </row>
     <row r="12">
@@ -20678,13 +20678,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>3.612700222825027</v>
+        <v>3.845127686</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>5.890261601434467</v>
+        <v>9.950004325</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>8.673365008818116</v>
+        <v>14.66179314</v>
       </c>
     </row>
     <row r="13">
@@ -20692,13 +20692,13 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>3.957514811090414</v>
+        <v>4.21212634</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>6.452458297424323</v>
+        <v>10.89968363</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>9.501195329611351</v>
+        <v>16.06118967</v>
       </c>
     </row>
     <row r="14">
@@ -20706,13 +20706,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>4.274604550130924</v>
+        <v>4.549616433</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>6.969451515482884</v>
+        <v>11.77300389</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>10.2624638760225</v>
+        <v>17.34806759</v>
       </c>
     </row>
     <row r="15">
@@ -20720,13 +20720,13 @@
         <v>32</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>4.569744483009963</v>
+        <v>4.863744552</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>7.450657069905534</v>
+        <v>12.58587056</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>10.97103536234866</v>
+        <v>18.54586436</v>
       </c>
     </row>
     <row r="16">
@@ -20734,13 +20734,13 @@
         <v>36</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>4.846945968339238</v>
+        <v>5.158780132</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>7.902615207638544</v>
+        <v>13.34933163</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>11.63654025203122</v>
+        <v>19.67085968</v>
       </c>
     </row>
     <row r="17">
@@ -20748,13 +20748,13 @@
         <v>40</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>5.109129651907455</v>
+        <v>5.437831722</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>8.330087842674089</v>
+        <v>14.07143106</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>12.26599042688282</v>
+        <v>20.7349067</v>
       </c>
     </row>
     <row r="18">
@@ -20762,13 +20762,13 @@
         <v>44</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>5.358500385369026</v>
+        <v>5.703246025</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>8.736669835431195</v>
+        <v>14.7582414</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>12.86467929128507</v>
+        <v>21.74695362</v>
       </c>
     </row>
     <row r="19">
@@ -20776,13 +20776,13 @@
         <v>48</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>5.596771119136461</v>
+        <v>5.956846196</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>9.125154034864289</v>
+        <v>15.41448042</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>13.43671929389228</v>
+        <v>22.71395226</v>
       </c>
     </row>
     <row r="20">
@@ -20790,13 +20790,13 @@
         <v>52</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>5.825304072750194</v>
+        <v>6.200082095</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>9.497761447134092</v>
+        <v>16.04389989</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>13.98538084923308</v>
+        <v>23.64143106</v>
       </c>
     </row>
     <row r="21">
@@ -20804,13 +20804,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>6.045203728576895</v>
+        <v>6.434129263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>9.856292855497614</v>
+        <v>16.64954176</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>14.51331559683497</v>
+        <v>24.53387247</v>
       </c>
     </row>
     <row r="22">
@@ -20818,13 +20818,13 @@
         <v>60</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>6.257380338448351</v>
+        <v>6.659956513</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>10.20223236355652</v>
+        <v>17.23391303</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>15.02270886786306</v>
+        <v>25.39497064</v>
       </c>
     </row>
     <row r="23">
@@ -20832,13 +20832,13 @@
         <v>64</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>6.462594624452318</v>
+        <v>6.87837351</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>10.53682027685139</v>
+        <v>17.79910884</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>15.5153870027083</v>
+        <v>26.2278129</v>
       </c>
     </row>
     <row r="24">
@@ -20846,13 +20846,13 @@
         <v>68</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>6.661490063041451</v>
+        <v>7.090065128</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>10.86110573990206</v>
+        <v>18.34690144</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>15.99289485862543</v>
+        <v>27.03501073</v>
       </c>
     </row>
     <row r="25">
@@ -20860,13 +20860,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>6.854616724514944</v>
+        <v>7.295616829</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>11.1759856048583</v>
+        <v>18.87880584</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>16.45655304352298</v>
+        <v>27.81879654</v>
       </c>
     </row>
     <row r="26">
@@ -20874,13 +20874,13 @@
         <v>76</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>7.042449220264211</v>
+        <v>7.495533756</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>11.48223369326137</v>
+        <v>19.39612918</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>16.90750100368247</v>
+        <v>28.58109649</v>
       </c>
     </row>
     <row r="27">
@@ -20888,13 +20888,13 @@
         <v>80</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>7.225400445650054</v>
+        <v>7.690255371</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>11.78052320286894</v>
+        <v>19.90000865</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>17.34673001763623</v>
+        <v>29.32358627</v>
       </c>
     </row>
     <row r="28">
@@ -20902,13 +20902,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>7.403832263091864</v>
+        <v>7.880166817</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>12.07144412570427</v>
+        <v>20.39144089</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>17.77510884411119</v>
+        <v>30.04773448</v>
       </c>
     </row>
     <row r="29">
@@ -20916,13 +20916,13 @@
         <v>88</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>7.578063918970332</v>
+        <v>8.065607878</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>12.35551697124271</v>
+        <v>20.87130515</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>18.19340392931565</v>
+        <v>30.75483674</v>
       </c>
     </row>
     <row r="30">
@@ -20930,13 +20930,13 @@
         <v>92</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>7.748378755584938</v>
+        <v>8.246880127000001</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>12.63320370980114</v>
+        <v>21.34038181</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>18.60229552099623</v>
+        <v>31.44604297</v>
       </c>
     </row>
     <row r="31">
@@ -20944,13 +20944,13 @@
         <v>96</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>7.915029622180828</v>
+        <v>8.42425268</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>12.90491659484865</v>
+        <v>21.79936726</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>19.0023906592227</v>
+        <v>32.12237934</v>
       </c>
     </row>
     <row r="32">
@@ -20958,13 +20958,13 @@
         <v>100</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>8.078243280565397</v>
+        <v>8.597966887</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>13.17102534606424</v>
+        <v>22.24888605</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>19.39423375338537</v>
+        <v>32.78476613</v>
       </c>
     </row>
     <row r="33">
@@ -20972,13 +20972,13 @@
         <v>104</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>8.238224024630551</v>
+        <v>8.768240187</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>13.43186305072135</v>
+        <v>22.68950082</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>19.77831527193837</v>
+        <v>33.43403244</v>
       </c>
     </row>
     <row r="34">
@@ -20986,13 +20986,13 @@
         <v>108</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>8.395156678704693</v>
+        <v>8.935269293999999</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>13.68773105229643</v>
+        <v>23.12172063</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>20.15507894083843</v>
+        <v>34.07092839</v>
       </c>
     </row>
     <row r="35">
@@ -21000,13 +21000,13 @@
         <v>112</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>8.549209100261848</v>
+        <v>9.099232865999999</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>13.93890303096577</v>
+        <v>23.54600777</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>20.52492775204499</v>
+        <v>34.69613518</v>
       </c>
     </row>
     <row r="36">
@@ -21014,13 +21014,13 @@
         <v>116</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>8.700534283594312</v>
+        <v>9.260293739</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>14.18562843350034</v>
+        <v>23.96278363</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>20.8882290140142</v>
+        <v>35.31027375</v>
       </c>
     </row>
     <row r="37">
@@ -21028,13 +21028,13 @@
         <v>120</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>8.849272139560405</v>
+        <v>9.418600826</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>14.42813537502334</v>
+        <v>24.37243353</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>21.2453186245145</v>
+        <v>35.9139119</v>
       </c>
     </row>
     <row r="38">
@@ -21042,13 +21042,13 @@
         <v>124</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>8.995551010360622</v>
+        <v>9.574290725999999</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>14.66663310874949</v>
+        <v>24.77531097</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>21.59650470729884</v>
+        <v>36.5075705</v>
       </c>
     </row>
     <row r="39">
@@ -21056,13 +21056,13 @@
         <v>128</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>9.139488966019924</v>
+        <v>9.727489105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>14.90131413981107</v>
+        <v>25.17174112</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>21.94207072469732</v>
+        <v>37.09172872</v>
       </c>
     </row>
     <row r="40">
@@ -21070,13 +21070,13 @@
         <v>132</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>9.281194919836562</v>
+        <v>9.878311883</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>15.13235604392125</v>
+        <v>25.56202394</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>22.28227815558493</v>
+        <v>37.66682857</v>
       </c>
     </row>
     <row r="41">
@@ -21084,13 +21084,13 @@
         <v>136</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>9.420769592766824</v>
+        <v>10.02686626</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>15.35992303973775</v>
+        <v>25.94643685</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>22.61736881067502</v>
+        <v>38.23327883</v>
       </c>
     </row>
     <row r="42">
@@ -21098,13 +21098,13 @@
         <v>140</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>9.558306351022654</v>
+        <v>10.17325162</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>15.58416735450866</v>
+        <v>26.32523699</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>22.94756684342228</v>
+        <v>38.79145841</v>
       </c>
     </row>
     <row r="43">
@@ -21112,13 +21112,13 @@
         <v>144</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>9.693891936678476</v>
+        <v>10.31756026</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>15.80523041527709</v>
+        <v>26.69866326</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>23.27308050406244</v>
+        <v>39.34171935</v>
       </c>
     </row>
     <row r="44">
@@ -21126,13 +21126,13 @@
         <v>148</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>9.827607107531312</v>
+        <v>10.45987816</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>16.02324389212954</v>
+        <v>27.06693808</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>23.5941036757875</v>
+        <v>39.88438939</v>
       </c>
     </row>
     <row r="45">
@@ -21140,13 +21140,13 @@
         <v>152</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>9.959527199621476</v>
+        <v>10.6002855</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>16.23833061534754</v>
+        <v>27.43026894</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>23.91081722524447</v>
+        <v>40.41977428</v>
       </c>
     </row>
     <row r="46">
@@ -21154,13 +21154,13 @@
         <v>156</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>10.08972262354124</v>
+        <v>10.7388572</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>16.45060538460515</v>
+        <v>27.78884977</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>24.22339019407245</v>
+        <v>40.94815977</v>
       </c>
     </row>
     <row r="47">
@@ -21168,13 +21168,13 @@
         <v>160</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>10.21825930381491</v>
+        <v>10.87566344</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>16.66017568534818</v>
+        <v>28.14286212</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>24.53198085376563</v>
+        <v>41.46981341</v>
       </c>
     </row>
     <row r="48">
@@ -21182,13 +21182,13 @@
         <v>164</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>10.34519906913347</v>
+        <v>11.01077003</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>16.86714232504526</v>
+        <v>28.4924763</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>24.83673764254802</v>
+        <v>41.98498612</v>
       </c>
     </row>
     <row r="49">
@@ -21196,13 +21196,13 @@
         <v>168</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>10.4706</v>
+        <v>11.14423879</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>17.0716</v>
+        <v>28.83785226</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>25.1378</v>
+        <v>42.49391362</v>
       </c>
     </row>
     <row r="51">
@@ -21213,17 +21213,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>kd 10</t>
+          <t>kd 0.2</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 30</t>
+          <t>kd 1</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 50</t>
+          <t>kd 5</t>
         </is>
       </c>
     </row>
@@ -21246,13 +21246,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>4.758962198190854</v>
+        <v>6.466383308</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>2.634205069212848</v>
+        <v>4.449777209</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>1.824945720001661</v>
+        <v>1.756263902</v>
       </c>
     </row>
     <row r="54">
@@ -21260,13 +21260,13 @@
         <v>8</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>6.730188883502382</v>
+        <v>9.144846974</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>3.725328534952767</v>
+        <v>6.292935279</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>2.580862987821082</v>
+        <v>2.483732229</v>
       </c>
     </row>
     <row r="55">
@@ -21274,13 +21274,13 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>8.242764318566229</v>
+        <v>11.20010443</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>4.562577017432145</v>
+        <v>7.707240209</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>3.160898708098243</v>
+        <v>3.041938309</v>
       </c>
     </row>
     <row r="56">
@@ -21288,13 +21288,13 @@
         <v>16</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>9.517924396381709</v>
+        <v>12.93276662</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>5.268410138425697</v>
+        <v>8.899554418999999</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>3.649891440003322</v>
+        <v>3.512527804</v>
       </c>
     </row>
     <row r="57">
@@ -21302,13 +21302,13 @@
         <v>20</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>10.64136297750658</v>
+        <v>14.45927265</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>5.890261601434467</v>
+        <v>9.950004325</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>4.080702685171012</v>
+        <v>3.927125471</v>
       </c>
     </row>
     <row r="58">
@@ -21316,13 +21316,13 @@
         <v>24</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>11.65702909076138</v>
+        <v>15.83933959</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>6.452458297424323</v>
+        <v>10.89968363</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>4.47018582228013</v>
+        <v>4.301950413</v>
       </c>
     </row>
     <row r="59">
@@ -21330,13 +21330,13 @@
         <v>28</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>12.59103047517028</v>
+        <v>17.10844212</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>6.969451515482884</v>
+        <v>11.77300389</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>4.828352531316108</v>
+        <v>4.646637521</v>
       </c>
     </row>
     <row r="60">
@@ -21344,13 +21344,13 @@
         <v>32</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>13.46037776700476</v>
+        <v>18.28969395</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>7.450657069905534</v>
+        <v>12.58587056</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>5.161725975642163</v>
+        <v>4.967464458</v>
       </c>
     </row>
     <row r="61">
@@ -21358,13 +21358,13 @@
         <v>36</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>14.27688659457256</v>
+        <v>19.39914992</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>7.902615207638544</v>
+        <v>13.34933163</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>5.474837160004983</v>
+        <v>5.268791705</v>
       </c>
     </row>
     <row r="62">
@@ -21372,13 +21372,13 @@
         <v>40</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>15.04915984492474</v>
+        <v>20.44849948</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>8.330087842674089</v>
+        <v>14.07143106</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>5.770985081381151</v>
+        <v>5.553794102</v>
       </c>
     </row>
     <row r="63">
@@ -21386,13 +21386,13 @@
         <v>44</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>15.78369200288402</v>
+        <v>21.44656718</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>8.736669835431195</v>
+        <v>14.7582414</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>6.052660216010493</v>
+        <v>5.824868395</v>
       </c>
     </row>
     <row r="64">
@@ -21400,13 +21400,13 @@
         <v>48</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>16.48552863713246</v>
+        <v>22.40020886</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>9.125154034864289</v>
+        <v>15.41448042</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>6.321797416196486</v>
+        <v>6.083876619</v>
       </c>
     </row>
     <row r="65">
@@ -21414,13 +21414,13 @@
         <v>52</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>17.15868222357195</v>
+        <v>23.31487658</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>9.497761447134092</v>
+        <v>16.04389989</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>6.579935368404538</v>
+        <v>6.332299551</v>
       </c>
     </row>
     <row r="66">
@@ -21428,13 +21428,13 @@
         <v>56</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>17.80640606223876</v>
+        <v>24.19499087</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>9.856292855497614</v>
+        <v>16.64954176</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>6.828321633705704</v>
+        <v>6.571337801</v>
       </c>
     </row>
     <row r="67">
@@ -21442,13 +21442,13 @@
         <v>60</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>18.43138133882382</v>
+        <v>25.04419486</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>10.20223236355652</v>
+        <v>17.23391303</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>7.067984381298936</v>
+        <v>6.801980843</v>
       </c>
     </row>
     <row r="68">
@@ -21456,13 +21456,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>19.03584879276342</v>
+        <v>25.86553323</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>10.53682027685139</v>
+        <v>17.79910884</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>7.299782880006644</v>
+        <v>7.025055607</v>
       </c>
     </row>
     <row r="69">
@@ -21470,13 +21470,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>19.6217038114625</v>
+        <v>26.6615814</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>10.86110573990206</v>
+        <v>18.34690144</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>7.524443964585721</v>
+        <v>7.241261574</v>
       </c>
     </row>
     <row r="70">
@@ -21484,13 +21484,13 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>20.19056665050715</v>
+        <v>27.43454092</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>11.1759856048583</v>
+        <v>18.87880584</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>7.742588963463245</v>
+        <v>7.451196687</v>
       </c>
     </row>
     <row r="71">
@@ -21498,13 +21498,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>20.74383529804412</v>
+        <v>28.18631137</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>11.48223369326137</v>
+        <v>19.39612918</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>7.954753970934314</v>
+        <v>7.655376866</v>
       </c>
     </row>
     <row r="72">
@@ -21512,13 +21512,13 @@
         <v>80</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>21.28272595501316</v>
+        <v>28.91854529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>11.78052320286894</v>
+        <v>19.90000865</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>8.161405370342024</v>
+        <v>7.854250942</v>
       </c>
     </row>
     <row r="73">
@@ -21526,13 +21526,13 @@
         <v>84</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>21.80830450264303</v>
+        <v>29.63269098</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>12.07144412570427</v>
+        <v>20.39144089</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>8.362951901093298</v>
+        <v>8.048212270000001</v>
       </c>
     </row>
     <row r="74">
@@ -21540,13 +21540,13 @@
         <v>88</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>22.32151129479833</v>
+        <v>30.33002618</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>12.35551697124271</v>
+        <v>20.87130515</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>8.559754165918106</v>
+        <v>8.237607883000001</v>
       </c>
     </row>
     <row r="75">
@@ -21554,13 +21554,13 @@
         <v>92</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>22.82318092833729</v>
+        <v>31.01168491</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>12.63320370980114</v>
+        <v>21.34038181</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>8.752132212318594</v>
+        <v>8.422745783</v>
       </c>
     </row>
     <row r="76">
@@ -21568,13 +21568,13 @@
         <v>96</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>23.31405818152276</v>
+        <v>31.67867917</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>12.90491659484865</v>
+        <v>21.79936726</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>8.94037164456026</v>
+        <v>8.603900826</v>
       </c>
     </row>
     <row r="77">
@@ -21582,13 +21582,13 @@
         <v>100</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>23.79481099095427</v>
+        <v>32.33191654</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>13.17102534606424</v>
+        <v>22.24888605</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>9.124728600008304</v>
+        <v>8.781319508999999</v>
       </c>
     </row>
     <row r="78">
@@ -21596,13 +21596,13 @@
         <v>104</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>24.26604111302558</v>
+        <v>32.97221467</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>13.43186305072135</v>
+        <v>22.68950082</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>9.305433837536103</v>
+        <v>8.955223906000001</v>
       </c>
     </row>
     <row r="79">
@@ -21610,13 +21610,13 @@
         <v>108</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>24.72829295569869</v>
+        <v>33.60031329</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>13.68773105229643</v>
+        <v>23.12172063</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>9.48269612429473</v>
+        <v>9.125814928</v>
       </c>
     </row>
     <row r="80">
@@ -21624,13 +21624,13 @@
         <v>112</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>25.18206095034056</v>
+        <v>34.21688423</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>13.93890303096577</v>
+        <v>23.54600777</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>9.656705062632216</v>
+        <v>9.293275040999999</v>
       </c>
     </row>
     <row r="81">
@@ -21638,13 +21638,13 @@
         <v>116</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>25.62779574818085</v>
+        <v>34.82253982</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>14.18562843350034</v>
+        <v>23.96278363</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>9.827633466283684</v>
+        <v>9.457770556</v>
       </c>
     </row>
     <row r="82">
@@ -21652,13 +21652,13 @@
         <v>120</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>26.06590946263502</v>
+        <v>35.41784003</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>14.42813537502334</v>
+        <v>24.37243353</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>9.995639370674166</v>
+        <v>9.619453559</v>
       </c>
     </row>
     <row r="83">
@@ -21666,13 +21666,13 @@
         <v>124</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>26.49678013114226</v>
+        <v>36.00329854</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>14.66663310874949</v>
+        <v>24.77531097</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>10.16086774392442</v>
+        <v>9.778463564000001</v>
       </c>
     </row>
     <row r="84">
@@ -21680,13 +21680,13 @@
         <v>128</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>26.92075553400953</v>
+        <v>36.5793879</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>14.90131413981107</v>
+        <v>25.17174112</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>10.32345195128433</v>
+        <v>9.934928916</v>
       </c>
     </row>
     <row r="85">
@@ -21694,13 +21694,13 @@
         <v>132</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>27.33815648001369</v>
+        <v>37.14654401</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>15.13235604392125</v>
+        <v>25.56202394</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>10.48351501508099</v>
+        <v>10.08896801</v>
       </c>
     </row>
     <row r="86">
@@ -21708,13 +21708,13 @@
         <v>136</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>27.74927964703812</v>
+        <v>37.70517</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>15.35992303973775</v>
+        <v>25.94643685</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>10.64117070403351</v>
+        <v>10.24069033</v>
       </c>
     </row>
     <row r="87">
@@ -21722,13 +21722,13 @@
         <v>140</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>28.15440004925222</v>
+        <v>38.25563956</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>15.58416735450866</v>
+        <v>26.32523699</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>10.796524479356</v>
+        <v>10.39019736</v>
       </c>
     </row>
     <row r="88">
@@ -21736,13 +21736,13 @@
         <v>144</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>28.55377318914513</v>
+        <v>38.79829985</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>15.80523041527709</v>
+        <v>26.69866326</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>10.94967432000996</v>
+        <v>10.53758341</v>
       </c>
     </row>
     <row r="89">
@@ -21750,13 +21750,13 @@
         <v>148</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>28.94763694226097</v>
+        <v>39.33347409</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>16.02324389212954</v>
+        <v>27.06693808</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>11.10071144545421</v>
+        <v>10.68293626</v>
       </c>
     </row>
     <row r="90">
@@ -21764,13 +21764,13 @@
         <v>152</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>29.33621321412772</v>
+        <v>39.86146381</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>16.23833061534754</v>
+        <v>27.43026894</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>11.24972095103654</v>
+        <v>10.82633779</v>
       </c>
     </row>
     <row r="91">
@@ -21778,13 +21778,13 @@
         <v>156</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>29.71970940215553</v>
+        <v>40.38255082</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>16.45060538460515</v>
+        <v>27.78884977</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>11.3967823685961</v>
+        <v>10.96786455</v>
       </c>
     </row>
     <row r="92">
@@ -21792,13 +21792,13 @@
         <v>160</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>30.09831968984949</v>
+        <v>40.89699895</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>16.66017568534818</v>
+        <v>28.14286212</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>11.5419701627623</v>
+        <v>11.1075882</v>
       </c>
     </row>
     <row r="93">
@@ -21806,13 +21806,13 @@
         <v>164</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>30.47222619626256</v>
+        <v>41.40505569</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>16.86714232504526</v>
+        <v>28.4924763</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>11.68535417174198</v>
+        <v>11.24557596</v>
       </c>
     </row>
     <row r="94">
@@ -21820,13 +21820,13 @@
         <v>168</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>30.8416</v>
+        <v>41.90695348</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>17.0716</v>
+        <v>28.83785226</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>11.827</v>
+        <v>11.38189095</v>
       </c>
     </row>
     <row r="96">
@@ -21837,17 +21837,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.1</t>
+          <t>kORR 0.04</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 1.0</t>
+          <t>kORR 0.2</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>kORR 5.0</t>
+          <t>kORR 1</t>
         </is>
       </c>
     </row>
@@ -21870,13 +21870,13 @@
         <v>4</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>2.962300282237253</v>
+        <v>4.385735015</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>2.510962983598117</v>
+        <v>4.561986132</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>2.436897375616294</v>
+        <v>4.394740547</v>
       </c>
     </row>
     <row r="99">
@@ -21884,13 +21884,13 @@
         <v>8</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>4.18932523496157</v>
+        <v>6.20236594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>3.551037906021269</v>
+        <v>6.451622659</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>3.446293318707965</v>
+        <v>6.215101684</v>
       </c>
     </row>
     <row r="100">
@@ -21898,13 +21898,13 @@
         <v>12</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>5.130854596110548</v>
+        <v>7.596315875</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>4.349115463516677</v>
+        <v>7.901591764</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>4.22083006739868</v>
+        <v>7.611913913</v>
       </c>
     </row>
     <row r="101">
@@ -21912,13 +21912,13 @@
         <v>16</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>5.924600564474506</v>
+        <v>8.77147003</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>5.021925967196235</v>
+        <v>9.123972264000001</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>4.873794751232587</v>
+        <v>8.789481093999999</v>
       </c>
     </row>
     <row r="102">
@@ -21926,13 +21926,13 @@
         <v>20</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>6.623904800849311</v>
+        <v>9.806801625</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>5.61468392031108</v>
+        <v>10.2009111</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>5.449068186068872</v>
+        <v>9.826938606000001</v>
       </c>
     </row>
     <row r="103">
@@ -21940,13 +21940,13 @@
         <v>24</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>7.256124156383865</v>
+        <v>10.74281293</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>6.150578072831833</v>
+        <v>11.17453824</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>5.969155125787357</v>
+        <v>10.76487189</v>
       </c>
     </row>
     <row r="104">
@@ -21954,13 +21954,13 @@
         <v>28</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>7.837509855496219</v>
+        <v>11.60356417</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>6.643383605889374</v>
+        <v>12.06988079</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>6.44742442646667</v>
+        <v>11.62739056</v>
       </c>
     </row>
     <row r="105">
@@ -21968,13 +21968,13 @@
         <v>32</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>8.378650469923141</v>
+        <v>12.40473188</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>7.102075812042537</v>
+        <v>12.90324532</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>6.892586637415929</v>
+        <v>12.43020337</v>
       </c>
     </row>
     <row r="106">
@@ -21982,13 +21982,13 @@
         <v>36</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>8.886900846711759</v>
+        <v>13.15720505</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>7.532888950794351</v>
+        <v>13.6859584</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>7.310692126848881</v>
+        <v>13.18422164</v>
       </c>
     </row>
     <row r="107">
@@ -21996,13 +21996,13 @@
         <v>40</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>9.367616005229351</v>
+        <v>13.86891186</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>7.940362148542067</v>
+        <v>14.42626683</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>7.706146131034358</v>
+        <v>13.89738985</v>
       </c>
     </row>
     <row r="108">
@@ -22010,13 +22010,13 @@
         <v>44</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>9.824838552544872</v>
+        <v>14.54583748</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>8.327922079066274</v>
+        <v>15.1303963</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>8.082274247521015</v>
+        <v>14.57570544</v>
       </c>
     </row>
     <row r="109">
@@ -22024,13 +22024,13 @@
         <v>48</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>10.2617091922211</v>
+        <v>15.19263175</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>8.698230927033354</v>
+        <v>15.80318353</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>8.44166013479736</v>
+        <v>15.22382783</v>
       </c>
     </row>
     <row r="110">
@@ -22038,13 +22038,13 @@
         <v>52</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>10.68072556092786</v>
+        <v>15.81299248</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>9.053405788155056</v>
+        <v>16.44847492</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>8.786358440828177</v>
+        <v>15.84546238</v>
       </c>
     </row>
     <row r="111">
@@ -22052,13 +22052,13 @@
         <v>56</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>11.08391273287555</v>
+        <v>16.40991782</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>9.395163195495829</v>
+        <v>17.06938911</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>9.118035066284737</v>
+        <v>16.44361343</v>
       </c>
     </row>
     <row r="112">
@@ -22066,13 +22066,13 @@
         <v>60</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>11.47293965957041</v>
+        <v>16.98587867</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>9.724917818418795</v>
+        <v>17.66849631</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>9.438062952178466</v>
+        <v>17.02075695</v>
       </c>
     </row>
     <row r="113">
@@ -22080,13 +22080,13 @@
         <v>64</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>11.84920112894901</v>
+        <v>17.54294006</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>10.04385193439247</v>
+        <v>18.24794453</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>9.747589502465177</v>
+        <v>17.57896219</v>
       </c>
     </row>
     <row r="114">
@@ -22094,13 +22094,13 @@
         <v>68</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>12.2138769584612</v>
+        <v>18.08284871</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>10.3529656033911</v>
+        <v>18.80955068</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>10.04758527845645</v>
+        <v>18.11997947</v>
       </c>
     </row>
     <row r="115">
@@ -22108,13 +22108,13 @@
         <v>72</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>12.56797570488471</v>
+        <v>18.60709782</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>10.6531137180638</v>
+        <v>19.35486798</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>10.3388799561239</v>
+        <v>18.64530505</v>
       </c>
     </row>
     <row r="116">
@@ -22122,13 +22122,13 @@
         <v>76</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>12.9123675706942</v>
+        <v>19.11697572</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>10.94503389647557</v>
+        <v>19.88523653</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>10.6221893960909</v>
+        <v>19.15622993</v>
       </c>
     </row>
     <row r="117">
@@ -22136,13 +22136,13 @@
         <v>80</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>13.24780960169862</v>
+        <v>19.61360325</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>11.22936784062216</v>
+        <v>20.40182221</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>10.89813637213774</v>
+        <v>19.65387721</v>
       </c>
     </row>
     <row r="118">
@@ -22150,13 +22150,13 @@
         <v>84</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>13.57496527454126</v>
+        <v>20.09796269</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>11.50667793957053</v>
+        <v>20.90564677</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>11.1672666846009</v>
+        <v>20.13923122</v>
       </c>
     </row>
     <row r="119">
@@ -22164,13 +22164,13 @@
         <v>88</v>
       </c>
       <c r="B119" s="1" t="n">
-        <v>13.894419929135</v>
+        <v>20.57092063</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>11.77746035060187</v>
+        <v>21.39761165</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>11.43006185566302</v>
+        <v>20.61316032</v>
       </c>
     </row>
     <row r="120">
@@ -22178,13 +22178,13 @@
         <v>92</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>14.20669307507159</v>
+        <v>21.03324624</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>12.04215543061121</v>
+        <v>21.8785169</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>11.68694925305866</v>
+        <v>21.07643525</v>
       </c>
     </row>
     <row r="121">
@@ -22192,13 +22192,13 @@
         <v>96</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>14.51224831276773</v>
+        <v>21.48562587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>12.30115614566367</v>
+        <v>22.34907647</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>11.93831025157471</v>
+        <v>21.52974378</v>
       </c>
     </row>
     <row r="122">
@@ -22206,13 +22206,13 @@
         <v>100</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>14.81150141118627</v>
+        <v>21.92867508</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>12.55481491799059</v>
+        <v>22.80993066</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>12.18448687808147</v>
+        <v>21.97370273</v>
       </c>
     </row>
     <row r="123">
@@ -22220,13 +22220,13 @@
         <v>104</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>15.10482694424917</v>
+        <v>22.36294842</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>12.80344925127596</v>
+        <v>23.26165631</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>12.42578727089053</v>
+        <v>22.40886781</v>
       </c>
     </row>
     <row r="124">
@@ -22234,13 +22234,13 @@
         <v>108</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>15.39256378833164</v>
+        <v>22.78894762</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>13.04734639055003</v>
+        <v>23.70477529</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>12.66249020219604</v>
+        <v>22.83574174</v>
       </c>
     </row>
     <row r="125">
@@ -22248,13 +22248,13 @@
         <v>112</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>15.67501971099244</v>
+        <v>23.20712833</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>13.28676721177875</v>
+        <v>24.13976158</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>12.89484885293334</v>
+        <v>23.25478113</v>
       </c>
     </row>
     <row r="126">
@@ -22262,13 +22262,13 @@
         <v>116</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>15.95247522806867</v>
+        <v>23.61790586</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>13.52194949129003</v>
+        <v>24.56704717</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>13.1230939857673</v>
+        <v>23.66640213</v>
       </c>
     </row>
     <row r="127">
@@ -22276,13 +22276,13 @@
         <v>120</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>16.22518686685264</v>
+        <v>24.02165999</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>13.75311067177163</v>
+        <v>24.98702712</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>13.34743662950184</v>
+        <v>24.07098532</v>
       </c>
     </row>
     <row r="128">
@@ -22290,13 +22290,13 @@
         <v>124</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>16.49338994344189</v>
+        <v>24.41873912</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>13.98045021646294</v>
+        <v>25.40006381</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>13.56807036383041</v>
+        <v>24.4688798</v>
       </c>
     </row>
     <row r="129">
@@ -22304,13 +22304,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>16.75730093984628</v>
+        <v>24.80946376</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>14.20415162408508</v>
+        <v>25.80649064</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>13.78517327483186</v>
+        <v>24.86040674</v>
       </c>
     </row>
     <row r="130">
@@ -22318,13 +22318,13 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>17.01711954916918</v>
+        <v>25.19412955</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>14.42438416241742</v>
+        <v>26.20661513</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>13.99890963741191</v>
+        <v>25.24586239</v>
       </c>
     </row>
     <row r="131">
@@ -22332,13 +22332,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>17.27303044381208</v>
+        <v>25.5730099</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>14.64130436709785</v>
+        <v>26.60072168</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>14.20943136989337</v>
+        <v>25.62552072</v>
       </c>
     </row>
     <row r="132">
@@ -22346,13 +22346,13 @@
         <v>140</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>17.5252048112141</v>
+        <v>25.94635826</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>14.85505734337631</v>
+        <v>26.98907393</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>14.41687929737207</v>
+        <v>25.9996357</v>
       </c>
     </row>
     <row r="133">
@@ -22360,13 +22360,13 @@
         <v>144</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>17.77380169342352</v>
+        <v>26.31441009</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>15.0657779015887</v>
+        <v>27.37191679</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>14.62138425369776</v>
+        <v>26.36844328</v>
       </c>
     </row>
     <row r="134">
@@ -22374,13 +22374,13 @@
         <v>148</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>18.01896916028461</v>
+        <v>26.67738462</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>15.27359155159645</v>
+        <v>27.74947831</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>14.82306804658086</v>
+        <v>26.73216313</v>
       </c>
     </row>
     <row r="135">
@@ -22388,13 +22388,13 @@
         <v>152</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>18.26084534082228</v>
+        <v>27.03548634</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>15.47861537702899</v>
+        <v>28.12197119</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>15.02204430604743</v>
+        <v>27.09100017</v>
       </c>
     </row>
     <row r="136">
@@ -22402,13 +22402,13 @@
         <v>156</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>18.49955933322666</v>
+        <v>27.38890639</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>15.68095880662271</v>
+        <v>28.48959426</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>15.21841923302606</v>
+        <v>27.44514592</v>
       </c>
     </row>
     <row r="137">
@@ -22416,13 +22416,13 @@
         <v>160</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>18.7352320104587</v>
+        <v>27.73782372</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>15.88072429708413</v>
+        <v>28.85253366</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>15.41229226206872</v>
+        <v>27.79477971</v>
       </c>
     </row>
     <row r="138">
@@ -22430,13 +22430,13 @@
         <v>164</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>18.96797673574752</v>
+        <v>28.08240618</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>16.0780079395738</v>
+        <v>29.21096397</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>15.60375664994519</v>
+        <v>28.14006971</v>
       </c>
     </row>
     <row r="139">
@@ -22444,13 +22444,13 @@
         <v>168</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>19.19790000000006</v>
+        <v>28.42281141</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>16.27289999999995</v>
+        <v>29.56504919</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>15.79289999999982</v>
+        <v>28.48117392</v>
       </c>
     </row>
   </sheetData>
@@ -22477,7 +22477,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i).</t>
+          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Baseline: k_f = 10, k_d = 1, k_ORR = 0.2 (middle curves); each parameter varied by x0.2 and x5. Values are the smoothed interface-O2 data (v2_O2smoothed).</t>
         </is>
       </c>
     </row>
@@ -22496,17 +22496,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
+          <t>kf 2</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>kf 10</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
           <t>kf 50</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>kf 100</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>kf 200</t>
         </is>
       </c>
     </row>
@@ -22515,13 +22515,13 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>3.466667</v>
+        <v>3.5</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>3.466667</v>
+        <v>3.5</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>3.466667</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
@@ -22529,13 +22529,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>3.125487325808868</v>
+        <v>3.429078464</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>3.108853424682956</v>
+        <v>3.339223967</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>3.086047389558558</v>
+        <v>2.866842092</v>
       </c>
     </row>
     <row r="9">
@@ -22543,13 +22543,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>2.984166077552868</v>
+        <v>3.399069634</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>2.960642188985428</v>
+        <v>3.286080353</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2.928389584808548</v>
+        <v>2.761789902</v>
       </c>
     </row>
     <row r="10">
@@ -22557,13 +22557,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>2.875726469791164</v>
+        <v>3.375335507</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>2.846915707913005</v>
+        <v>3.249237344</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2.807414496358349</v>
+        <v>2.719185314</v>
       </c>
     </row>
     <row r="11">
@@ -22571,13 +22571,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>2.784307651617737</v>
+        <v>3.354671629</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>2.751039849365911</v>
+        <v>3.220283926</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2.705427779117116</v>
+        <v>2.699387556</v>
       </c>
     </row>
     <row r="12">
@@ -22585,13 +22585,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>2.703766055967399</v>
+        <v>3.335859054</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>2.666571522318846</v>
+        <v>3.196030851</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2.615575677483447</v>
+        <v>2.688234673</v>
       </c>
     </row>
     <row r="13">
@@ -22599,13 +22599,13 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>2.630950887622717</v>
+        <v>3.318283565</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>2.590206317432322</v>
+        <v>3.174876187</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>2.534343168321559</v>
+        <v>2.679048854</v>
       </c>
     </row>
     <row r="14">
@@ -22613,13 +22613,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>2.563990429700223</v>
+        <v>3.301586672</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>2.51998126398822</v>
+        <v>3.155888001</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2.459642166657661</v>
+        <v>2.668689881</v>
       </c>
     </row>
     <row r="15">
@@ -22627,13 +22627,13 @@
         <v>32</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>2.501665155105735</v>
+        <v>3.285538922</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>2.454617377970856</v>
+        <v>3.138471799</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2.390112169617097</v>
+        <v>2.657052163</v>
       </c>
     </row>
     <row r="16">
@@ -22641,13 +22641,13 @@
         <v>36</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>2.443127977426605</v>
+        <v>3.269983787</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>2.393226274048866</v>
+        <v>3.122223434</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2.324808168675674</v>
+        <v>2.644486678</v>
       </c>
     </row>
     <row r="17">
@@ -22655,13 +22655,13 @@
         <v>40</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>2.387762138201858</v>
+        <v>3.254809366</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>2.335161124269933</v>
+        <v>3.106855024</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2.263042108879036</v>
+        <v>2.631242572</v>
       </c>
     </row>
     <row r="18">
@@ -22669,13 +22669,13 @@
         <v>44</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>2.335102034612314</v>
+        <v>3.239932742</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>2.27993362577779</v>
+        <v>3.092154048</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2.204294564314498</v>
+        <v>2.617503108</v>
       </c>
     </row>
     <row r="19">
@@ -22683,13 +22683,13 @@
         <v>48</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>2.284785939582328</v>
+        <v>3.225290706</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>2.22716441582601</v>
+        <v>3.077959123</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2.148161992716697</v>
+        <v>2.603403324</v>
       </c>
     </row>
     <row r="20">
@@ -22697,13 +22697,13 @@
         <v>52</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>2.236526190557777</v>
+        <v>3.21083395</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>2.176551807137298</v>
+        <v>3.064144873</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>2.094323478106252</v>
+        <v>2.589034231</v>
       </c>
     </row>
     <row r="21">
@@ -22711,13 +22711,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>2.190089551845626</v>
+        <v>3.196523272</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>2.127851192826985</v>
+        <v>3.050612038</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>2.042518823040758</v>
+        <v>2.57446464</v>
       </c>
     </row>
     <row r="22">
@@ -22725,13 +22725,13 @@
         <v>60</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>2.145283803793275</v>
+        <v>3.182327007</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>2.080860981750152</v>
+        <v>3.03728079</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>1.99253358752034</v>
+        <v>2.559749913</v>
       </c>
     </row>
     <row r="23">
@@ -22739,13 +22739,13 @@
         <v>64</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>2.101948303235473</v>
+        <v>3.168219225</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>2.03541269873182</v>
+        <v>3.024086067</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>1.944188558234232</v>
+        <v>2.544935192</v>
       </c>
     </row>
     <row r="24">
@@ -22753,13 +22753,13 @@
         <v>68</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>2.059947165996144</v>
+        <v>3.154178445</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>1.991363834687924</v>
+        <v>3.010974226</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>1.897332142968488</v>
+        <v>2.53005771</v>
       </c>
     </row>
     <row r="25">
@@ -22767,13 +22767,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>2.019164232658603</v>
+        <v>3.140186691</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>1.948592566956285</v>
+        <v>2.997900605</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>1.851834754425645</v>
+        <v>2.51514848</v>
       </c>
     </row>
     <row r="26">
@@ -22781,13 +22781,13 @@
         <v>76</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>1.979499278610725</v>
+        <v>3.126228786</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>1.906993784566022</v>
+        <v>2.984827696</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>1.807584582155936</v>
+        <v>2.500233562</v>
       </c>
     </row>
     <row r="27">
@@ -22795,13 +22795,13 @@
         <v>80</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>1.940865111934797</v>
+        <v>3.112291817</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>1.866476044637693</v>
+        <v>2.971723764</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>1.764484354966893</v>
+        <v>2.485335015</v>
       </c>
     </row>
     <row r="28">
@@ -22809,13 +22809,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>1.903185317438768</v>
+        <v>3.098364722</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>1.826959206426859</v>
+        <v>2.958561777</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>1.722448824167487</v>
+        <v>2.470471637</v>
       </c>
     </row>
     <row r="29">
@@ -22823,13 +22823,13 @@
         <v>88</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>1.866392479242493</v>
+        <v>3.084437963</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>1.788372567254165</v>
+        <v>2.945318582</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.681402780687606</v>
+        <v>2.455666266</v>
       </c>
     </row>
     <row r="30">
@@ -22837,13 +22837,13 @@
         <v>92</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>1.830426763400608</v>
+        <v>3.070503276</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>1.750653376025286</v>
+        <v>2.931974239</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>1.641279473853925</v>
+        <v>2.440964615</v>
       </c>
     </row>
     <row r="31">
@@ -22851,13 +22851,13 @@
         <v>96</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>1.795234775245433</v>
+        <v>3.056553465</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>1.713745634864645</v>
+        <v>2.918511506</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.602019336643117</v>
+        <v>2.426412708</v>
       </c>
     </row>
     <row r="32">
@@ -22865,13 +22865,13 @@
         <v>100</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>1.760768629044341</v>
+        <v>3.042582232</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>1.677599123414775</v>
+        <v>2.904915406</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.563568947792789</v>
+        <v>2.412050733</v>
       </c>
     </row>
     <row r="33">
@@ -22879,13 +22879,13 @@
         <v>104</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>1.726985183658191</v>
+        <v>3.028584049</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>1.642168597229986</v>
+        <v>2.89117289</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.525880179103003</v>
+        <v>2.397913916</v>
       </c>
     </row>
     <row r="34">
@@ -22893,13 +22893,13 @@
         <v>108</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>1.693845409373492</v>
+        <v>3.014554043</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>1.607413123739015</v>
+        <v>2.877272554</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.488909489075046</v>
+        <v>2.384033237</v>
       </c>
     </row>
     <row r="35">
@@ -22907,13 +22907,13 @@
         <v>112</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>1.661313859400447</v>
+        <v>3.000487909</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>1.57329552797644</v>
+        <v>2.863204403</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.452617333315322</v>
+        <v>2.370436029</v>
       </c>
     </row>
     <row r="36">
@@ -22921,13 +22921,13 @@
         <v>116</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>1.629358225636301</v>
+        <v>2.986381826</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>1.539781926687678</v>
+        <v>2.848959657</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.416967668945501</v>
+        <v>2.357146471</v>
       </c>
     </row>
     <row r="37">
@@ -22935,13 +22935,13 @@
         <v>120</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>1.59794896283254</v>
+        <v>2.972232403</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>1.506841334172808</v>
+        <v>2.83453059</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>1.381927535323933</v>
+        <v>2.344185999</v>
       </c>
     </row>
     <row r="38">
@@ -22949,13 +22949,13 @@
         <v>124</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>1.567058968716659</v>
+        <v>2.958036615</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>1.474445326812961</v>
+        <v>2.819910394</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1.347466697189893</v>
+        <v>2.331573666</v>
       </c>
     </row>
     <row r="39">
@@ -22963,13 +22963,13 @@
         <v>128</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>1.536663310211471</v>
+        <v>2.943791764</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>1.442567755941713</v>
+        <v>2.80509306</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>1.313557339234194</v>
+        <v>2.319326431</v>
       </c>
     </row>
     <row r="40">
@@ -22977,13 +22977,13 @@
         <v>132</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>1.50673898788361</v>
+        <v>2.929495438</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>1.411184500809482</v>
+        <v>2.79007328</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>1.280173803318236</v>
+        <v>2.307459414</v>
       </c>
     </row>
     <row r="41">
@@ -22991,13 +22991,13 @@
         <v>136</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>1.477264732292518</v>
+        <v>2.915145476</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>1.380273255003705</v>
+        <v>2.774846365</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>1.247292361281193</v>
+        <v>2.295986118</v>
       </c>
     </row>
     <row r="42">
@@ -23005,13 +23005,13 @@
         <v>140</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>1.448220827113332</v>
+        <v>2.900739941</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>1.349813340948239</v>
+        <v>2.759408168</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1.214891017616133</v>
+        <v>2.284918609</v>
       </c>
     </row>
     <row r="43">
@@ -23019,13 +23019,13 @@
         <v>144</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>1.41958895485321</v>
+        <v>2.886277094</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>1.319785548097731</v>
+        <v>2.743755027</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1.182949337351348</v>
+        <v>2.274267683</v>
       </c>
     </row>
     <row r="44">
@@ -23033,13 +23033,13 @@
         <v>148</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>1.391352061730829</v>
+        <v>2.871755373</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>1.290171991229439</v>
+        <v>2.727883704</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1.151448295310091</v>
+        <v>2.264043002</v>
       </c>
     </row>
     <row r="45">
@@ -23047,13 +23047,13 @@
         <v>152</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>1.363494238887795</v>
+        <v>2.857173373</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>1.260955985863214</v>
+        <v>2.711791343</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1.120370143590177</v>
+        <v>2.254253221</v>
       </c>
     </row>
     <row r="46">
@@ -23061,13 +23061,13 @@
         <v>156</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>1.336000617582165</v>
+        <v>2.842529831</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>1.23212193834528</v>
+        <v>2.695475428</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>1.089698294642016</v>
+        <v>2.244906087</v>
       </c>
     </row>
     <row r="47">
@@ -23075,13 +23075,13 @@
         <v>160</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>1.308857276403716</v>
+        <v>2.82782361</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>1.203655248539866</v>
+        <v>2.678933743</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>1.059417217758073</v>
+        <v>2.236008541</v>
       </c>
     </row>
     <row r="48">
@@ -23089,13 +23089,13 @@
         <v>164</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>1.282051158867322</v>
+        <v>2.813053687</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>1.175542223404926</v>
+        <v>2.662164346</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>1.029512347140153</v>
+        <v>2.227566795</v>
       </c>
     </row>
     <row r="49">
@@ -23103,13 +23103,13 @@
         <v>168</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>1.255569999999999</v>
+        <v>2.798219143</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>1.147770000000001</v>
+        <v>2.645165538</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.9999700000000008</v>
+        <v>2.219586406</v>
       </c>
     </row>
     <row r="51">
@@ -23120,17 +23120,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>kd 10</t>
+          <t>kd 0.2</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 30</t>
+          <t>kd 1</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 50</t>
+          <t>kd 5</t>
         </is>
       </c>
     </row>
@@ -23139,13 +23139,13 @@
         <v>0</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>3.466667</v>
+        <v>3.5</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>3.466667</v>
+        <v>3.5</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>3.466667</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="53">
@@ -23153,13 +23153,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>3.058953264338714</v>
+        <v>2.721308348</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>3.120736325663536</v>
+        <v>3.339223967</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>3.136737583054604</v>
+        <v>3.520542108</v>
       </c>
     </row>
     <row r="54">
@@ -23167,13 +23167,13 @@
         <v>8</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>2.890072705462011</v>
+        <v>2.612956133</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>2.977447148712502</v>
+        <v>3.286080353</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>3.000076343929974</v>
+        <v>3.508410198</v>
       </c>
     </row>
     <row r="55">
@@ -23181,13 +23181,13 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>2.760486094890945</v>
+        <v>2.578785657</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>2.867497496152681</v>
+        <v>3.249237344</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>2.895212486938998</v>
+        <v>3.492610036</v>
       </c>
     </row>
     <row r="56">
@@ -23195,13 +23195,13 @@
         <v>16</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>2.651239528677428</v>
+        <v>2.568952055</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>2.774805651327071</v>
+        <v>3.220283926</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2.806808166109208</v>
+        <v>3.475576055</v>
       </c>
     </row>
     <row r="57">
@@ -23209,13 +23209,13 @@
         <v>20</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>2.554991371700984</v>
+        <v>2.56591022</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>2.693142496681324</v>
+        <v>3.196030851</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>2.728922395933224</v>
+        <v>3.458167894</v>
       </c>
     </row>
     <row r="58">
@@ -23223,13 +23223,13 @@
         <v>24</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>2.467976386505867</v>
+        <v>2.561526669</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>2.619313361498763</v>
+        <v>3.174876187</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.658508277349819</v>
+        <v>3.440785535</v>
       </c>
     </row>
     <row r="59">
@@ -23237,13 +23237,13 @@
         <v>28</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>2.38795784933511</v>
+        <v>2.552389291</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>2.551420464836842</v>
+        <v>3.155888001</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>2.593755812557943</v>
+        <v>3.423621746</v>
       </c>
     </row>
     <row r="60">
@@ -23251,13 +23251,13 @@
         <v>32</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>2.313478410924021</v>
+        <v>2.539844455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>2.488227297425004</v>
+        <v>3.138471799</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>2.533485687859947</v>
+        <v>3.406712367</v>
       </c>
     </row>
     <row r="61">
@@ -23265,13 +23265,13 @@
         <v>36</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>2.243525793016142</v>
+        <v>2.525565301</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>2.428874976990607</v>
+        <v>3.122223434</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>2.476878749163812</v>
+        <v>3.390059887</v>
       </c>
     </row>
     <row r="62">
@@ -23279,13 +23279,13 @@
         <v>40</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>2.177362961974519</v>
+        <v>2.51071271</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>2.372738156578816</v>
+        <v>3.106855024</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>2.423338575361196</v>
+        <v>3.373663445</v>
       </c>
     </row>
     <row r="63">
@@ -23293,13 +23293,13 @@
         <v>44</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>2.11443351693737</v>
+        <v>2.496119868</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>2.319344749751322</v>
+        <v>3.092154048</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>2.372414916691397</v>
+        <v>3.357520376</v>
       </c>
     </row>
     <row r="64">
@@ -23307,13 +23307,13 @@
         <v>48</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>2.054305189781891</v>
+        <v>2.482271242</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>2.268327992305361</v>
+        <v>3.077959123</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>2.323757973877997</v>
+        <v>3.341621247</v>
       </c>
     </row>
     <row r="65">
@@ -23321,13 +23321,13 @@
         <v>52</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>1.996634220362262</v>
+        <v>2.469043789</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>2.219396215924043</v>
+        <v>3.064144873</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>2.277089569919438</v>
+        <v>3.325935705</v>
       </c>
     </row>
     <row r="66">
@@ -23335,13 +23335,13 @@
         <v>56</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>1.941141889273751</v>
+        <v>2.456223658</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>2.172312937057278</v>
+        <v>3.050612038</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>2.23218415997224</v>
+        <v>3.310433985</v>
       </c>
     </row>
     <row r="67">
@@ -23349,13 +23349,13 @@
         <v>60</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>1.887598491763826</v>
+        <v>2.443639658</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>2.126883259352572</v>
+        <v>3.03728079</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>2.188855862746559</v>
+        <v>3.29509175</v>
       </c>
     </row>
     <row r="68">
@@ -23363,13 +23363,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>1.835812057354856</v>
+        <v>2.431152936</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>2.082944302654143</v>
+        <v>3.024086067</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>2.146949332218417</v>
+        <v>3.279888825</v>
       </c>
     </row>
     <row r="69">
@@ -23377,13 +23377,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>1.785620202853359</v>
+        <v>2.418649608</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>2.040358290569613</v>
+        <v>3.010974226</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>2.106333164935684</v>
+        <v>3.264808282</v>
       </c>
     </row>
     <row r="70">
@@ -23391,13 +23391,13 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>1.736884116386031</v>
+        <v>2.406035368</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>1.999007446137505</v>
+        <v>2.997900605</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>2.066895031789921</v>
+        <v>3.249835768</v>
       </c>
     </row>
     <row r="71">
@@ -23405,13 +23405,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>1.689484028358998</v>
+        <v>2.393231477</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>1.958790149096473</v>
+        <v>2.984827696</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>2.028538013033724</v>
+        <v>3.234959</v>
       </c>
     </row>
     <row r="72">
@@ -23419,13 +23419,13 @@
         <v>80</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>1.643315743401968</v>
+        <v>2.380171722</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>1.919617993362648</v>
+        <v>2.971723764</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>1.991177791866448</v>
+        <v>3.220167382</v>
       </c>
     </row>
     <row r="73">
@@ -23433,13 +23433,13 @@
         <v>84</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>1.59828794445894</v>
+        <v>2.366800077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>1.881413499646034</v>
+        <v>2.958561777</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>1.954740472855077</v>
+        <v>3.205451703</v>
       </c>
     </row>
     <row r="74">
@@ -23447,13 +23447,13 @@
         <v>88</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>1.55432006875782</v>
+        <v>2.353097396</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>1.844108313285901</v>
+        <v>2.945318582</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>1.91916086312996</v>
+        <v>3.190804548</v>
       </c>
     </row>
     <row r="75">
@@ -23461,13 +23461,13 @@
         <v>92</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>1.511340614028015</v>
+        <v>2.339157923</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>1.807641767136358</v>
+        <v>2.931974239</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>1.884381101745085</v>
+        <v>3.17622186</v>
       </c>
     </row>
     <row r="76">
@@ -23475,13 +23475,13 @@
         <v>96</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>1.469285773011735</v>
+        <v>2.325090925</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>1.771959722997526</v>
+        <v>2.918511506</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>1.850349554699637</v>
+        <v>3.16170061</v>
       </c>
     </row>
     <row r="77">
@@ -23489,13 +23489,13 @@
         <v>100</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>1.428098321693569</v>
+        <v>2.310992457</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>1.737013628317678</v>
+        <v>2.904915406</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>1.817019915273021</v>
+        <v>3.147238054</v>
       </c>
     </row>
     <row r="78">
@@ -23503,13 +23503,13 @@
         <v>104</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>1.387726705903292</v>
+        <v>2.296947309</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>1.702759741208058</v>
+        <v>2.89117289</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>1.784350464887136</v>
+        <v>3.132831703</v>
       </c>
     </row>
     <row r="79">
@@ -23517,13 +23517,13 @@
         <v>108</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>1.348124284672837</v>
+        <v>2.283030608</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>1.669158488458042</v>
+        <v>2.877272554</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>1.752303460816995</v>
+        <v>3.118479283</v>
       </c>
     </row>
     <row r="80">
@@ -23531,13 +23531,13 @@
         <v>112</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>1.30924869867022</v>
+        <v>2.269309149</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>1.636173929673683</v>
+        <v>2.863204403</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>1.720844625115886</v>
+        <v>3.104178714</v>
       </c>
     </row>
     <row r="81">
@@ -23545,13 +23545,13 @@
         <v>116</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>1.271061339331502</v>
+        <v>2.255842506</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>1.603773306854965</v>
+        <v>2.848959657</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>1.689942715027248</v>
+        <v>3.089928082</v>
       </c>
     </row>
     <row r="82">
@@ -23559,13 +23559,13 @@
         <v>120</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>1.233526899736151</v>
+        <v>2.242683958</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>1.57192666332945</v>
+        <v>2.83453059</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>1.659569159544795</v>
+        <v>3.075725624</v>
       </c>
     </row>
     <row r="83">
@@ -23573,13 +23573,13 @@
         <v>124</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>1.196612992348791</v>
+        <v>2.229881285</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>1.540606519419676</v>
+        <v>2.819910394</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>1.629697750082138</v>
+        <v>3.061569709</v>
       </c>
     </row>
     <row r="84">
@@ -23587,13 +23587,13 @@
         <v>128</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>1.160289821848041</v>
+        <v>2.217477429</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>1.509787594850007</v>
+        <v>2.80509306</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>1.600304375719894</v>
+        <v>3.047458825</v>
       </c>
     </row>
     <row r="85">
@@ -23601,13 +23601,13 @@
         <v>132</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>1.124529903639696</v>
+        <v>2.205511075</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>1.479446569915035</v>
+        <v>2.79007328</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>1.571366795421408</v>
+        <v>3.033391565</v>
       </c>
     </row>
     <row r="86">
@@ -23615,13 +23615,13 @@
         <v>136</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>1.089307820491368</v>
+        <v>2.194017133</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>1.44956187899268</v>
+        <v>2.774846365</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>1.542864441097039</v>
+        <v>3.019366617</v>
       </c>
     </row>
     <row r="87">
@@ -23629,13 +23629,13 @@
         <v>140</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>1.054600011162244</v>
+        <v>2.183027167</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>1.420113531204026</v>
+        <v>2.759408168</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>1.5147782465595</v>
+        <v>3.005382758</v>
       </c>
     </row>
     <row r="88">
@@ -23643,13 +23643,13 @@
         <v>144</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>1.020384586032283</v>
+        <v>2.172569759</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>1.391082953981214</v>
+        <v>2.743755027</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>1.487090498327625</v>
+        <v>2.99143884</v>
       </c>
     </row>
     <row r="89">
@@ -23657,13 +23657,13 @@
         <v>148</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>0.9866411656316156</v>
+        <v>2.162670831</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>1.362452856065359</v>
+        <v>2.727883704</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>1.459784704961408</v>
+        <v>2.977533787</v>
       </c>
     </row>
     <row r="90">
@@ -23671,13 +23671,13 @@
         <v>152</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>0.953350738686776</v>
+        <v>2.153353918</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>1.334207107063798</v>
+        <v>2.711791343</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>1.432845482190412</v>
+        <v>2.963666588</v>
       </c>
     </row>
     <row r="91">
@@ -23685,13 +23685,13 @@
         <v>156</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>0.9204955368757344</v>
+        <v>2.144640416</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>1.306330631184172</v>
+        <v>2.695475428</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>1.406258451563252</v>
+        <v>2.949836289</v>
       </c>
     </row>
     <row r="92">
@@ -23699,13 +23699,13 @@
         <v>160</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>0.8880589239490377</v>
+        <v>2.136549793</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>1.278809313157632</v>
+        <v>2.678933743</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>1.380010150722392</v>
+        <v>2.936041993</v>
       </c>
     </row>
     <row r="93">
@@ -23713,13 +23713,13 @@
         <v>164</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>0.8560252972529292</v>
+        <v>2.129099779</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>1.251629914684696</v>
+        <v>2.662164346</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>1.354087953714848</v>
+        <v>2.922282849</v>
       </c>
     </row>
     <row r="94">
@@ -23727,13 +23727,13 @@
         <v>168</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>0.8243799999999988</v>
+        <v>2.122306534</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>1.22478</v>
+        <v>2.645165538</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>1.328479999999997</v>
+        <v>2.908558054</v>
       </c>
     </row>
     <row r="96">
@@ -23744,17 +23744,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.1</t>
+          <t>kORR 0.04</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 1.0</t>
+          <t>kORR 0.2</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>kORR 5.0</t>
+          <t>kORR 1</t>
         </is>
       </c>
     </row>
@@ -23763,13 +23763,13 @@
         <v>0</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>3.466667</v>
+        <v>3.5</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>3.466667</v>
+        <v>3.5</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>3.466667</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="98">
@@ -23777,13 +23777,13 @@
         <v>4</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>3.317507043602195</v>
+        <v>3.439138939</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>3.10700178448341</v>
+        <v>3.339223967</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>2.105899543658326</v>
+        <v>2.930101164</v>
       </c>
     </row>
     <row r="99">
@@ -23791,13 +23791,13 @@
         <v>8</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>3.255722966699244</v>
+        <v>3.423280974</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>2.958023574302596</v>
+        <v>3.286080353</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>1.925075477075564</v>
+        <v>2.744680937</v>
       </c>
     </row>
     <row r="100">
@@ -23805,13 +23805,13 @@
         <v>12</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>3.208314377064243</v>
+        <v>3.413942366</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>2.843708573010056</v>
+        <v>3.249237344</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>1.808356921745556</v>
+        <v>2.618369345</v>
       </c>
     </row>
     <row r="101">
@@ -23819,13 +23819,13 @@
         <v>16</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>3.168347087204389</v>
+        <v>3.407633828</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>2.74733656896682</v>
+        <v>3.220283926</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>1.720222805970297</v>
+        <v>2.521039235</v>
       </c>
     </row>
     <row r="102">
@@ -23833,13 +23833,13 @@
         <v>20</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>3.133135197973602</v>
+        <v>3.403046991</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>2.662431128962792</v>
+        <v>3.196030851</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>1.648647592376332</v>
+        <v>2.441223502</v>
       </c>
     </row>
     <row r="103">
@@ -23847,13 +23847,13 @@
         <v>24</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>3.101301216769589</v>
+        <v>3.399532032</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>2.585670743756212</v>
+        <v>3.174876187</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>1.587994235521925</v>
+        <v>2.373140451</v>
       </c>
     </row>
     <row r="104">
@@ -23861,13 +23861,13 @@
         <v>28</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>3.072026849802169</v>
+        <v>3.396715299</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>2.515082284502653</v>
+        <v>3.155888001</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>1.535136539181085</v>
+        <v>2.313413492</v>
       </c>
     </row>
     <row r="105">
@@ -23875,13 +23875,13 @@
         <v>32</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>3.044778933398488</v>
+        <v>3.394361331</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>2.449380148605192</v>
+        <v>3.138471799</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>1.488148516015341</v>
+        <v>2.259880055</v>
       </c>
     </row>
     <row r="106">
@@ -23889,13 +23889,13 @@
         <v>36</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>3.019187130806584</v>
+        <v>3.392312098</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>2.38767135345023</v>
+        <v>3.122223434</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>1.445754240200893</v>
+        <v>2.211063906</v>
       </c>
     </row>
     <row r="107">
@@ -23903,13 +23903,13 @@
         <v>40</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>2.99498180209153</v>
+        <v>3.390456549</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>2.329305723832241</v>
+        <v>3.106855024</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>1.407062109948133</v>
+        <v>2.165909003</v>
       </c>
     </row>
     <row r="108">
@@ -23917,13 +23917,13 @@
         <v>44</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>2.971959390882708</v>
+        <v>3.388713869</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>2.27379242998916</v>
+        <v>3.092154048</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>1.371423038863143</v>
+        <v>2.123632274</v>
       </c>
     </row>
     <row r="109">
@@ -23931,13 +23931,13 @@
         <v>48</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>2.949961754128485</v>
+        <v>3.387023615</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>2.220750146020112</v>
+        <v>3.077959123</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>1.338348899378679</v>
+        <v>2.083636332</v>
       </c>
     </row>
     <row r="110">
@@ -23945,13 +23945,13 @@
         <v>52</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>2.928863128961739</v>
+        <v>3.385339582</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>2.169875623454128</v>
+        <v>3.064144873</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>1.307462793135572</v>
+        <v>2.045454828</v>
       </c>
     </row>
     <row r="111">
@@ -23959,13 +23959,13 @@
         <v>56</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>2.908561547333272</v>
+        <v>3.383625812</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>2.120922989596709</v>
+        <v>3.050612038</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>1.278467266980283</v>
+        <v>2.008716716</v>
       </c>
     </row>
     <row r="112">
@@ -23973,13 +23973,13 @@
         <v>60</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>2.888972972950275</v>
+        <v>3.381853915</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>2.073689610094145</v>
+        <v>3.03728079</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>1.251123196336672</v>
+        <v>1.97312202</v>
       </c>
     </row>
     <row r="113">
@@ -23987,13 +23987,13 @@
         <v>64</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>2.870027174408778</v>
+        <v>3.380001199</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>2.028006137933639</v>
+        <v>3.024086067</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>1.225235292733906</v>
+        <v>1.938424905</v>
       </c>
     </row>
     <row r="114">
@@ -24001,13 +24001,13 @@
         <v>68</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>2.851664744659323</v>
+        <v>3.378049349</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>1.983729326564559</v>
+        <v>3.010974226</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>1.200641878882746</v>
+        <v>1.904421533</v>
       </c>
     </row>
     <row r="115">
@@ -24015,13 +24015,13 @@
         <v>72</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>2.833834900097732</v>
+        <v>3.375983455</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>1.940736722907788</v>
+        <v>2.997900605</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>1.177207500834933</v>
+        <v>1.87094117</v>
       </c>
     </row>
     <row r="116">
@@ -24029,13 +24029,13 @@
         <v>76</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>2.816493823639033</v>
+        <v>3.373791301</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>1.898922672056406</v>
+        <v>2.984827696</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>1.154817478187627</v>
+        <v>1.837839531</v>
       </c>
     </row>
     <row r="117">
@@ -24043,13 +24043,13 @@
         <v>80</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>2.799603395947205</v>
+        <v>3.37146282</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>1.858195257925584</v>
+        <v>2.971723764</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>1.133373809983815</v>
+        <v>1.80499373</v>
       </c>
     </row>
     <row r="118">
@@ -24057,13 +24057,13 @@
         <v>84</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>2.783130209150744</v>
+        <v>3.368989683</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>1.81847392505262</v>
+        <v>2.958561777</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>1.112792048990588</v>
+        <v>1.772298378</v>
       </c>
     </row>
     <row r="119">
@@ -24071,13 +24071,13 @@
         <v>88</v>
       </c>
       <c r="B119" s="1" t="n">
-        <v>2.767044789777158</v>
+        <v>3.366364976</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>1.779687604880695</v>
+        <v>2.945318582</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>1.092998880664719</v>
+        <v>1.739689201</v>
       </c>
     </row>
     <row r="120">
@@ -24085,13 +24085,13 @@
         <v>92</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>2.751320979091454</v>
+        <v>3.363582949</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>1.741773221586474</v>
+        <v>2.931974239</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>1.073930223510499</v>
+        <v>1.707213511</v>
       </c>
     </row>
     <row r="121">
@@ -24099,13 +24099,13 @@
         <v>96</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>2.735935433539179</v>
+        <v>3.360638812</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>1.704674487512423</v>
+        <v>2.918511506</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>1.055529721022744</v>
+        <v>1.67493737</v>
       </c>
     </row>
     <row r="122">
@@ -24113,13 +24113,13 @@
         <v>100</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>2.720867218010973</v>
+        <v>3.357528581</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>1.668340922417049</v>
+        <v>2.904915406</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>1.037747531730167</v>
+        <v>1.642918482</v>
       </c>
     </row>
     <row r="123">
@@ -24127,13 +24127,13 @@
         <v>104</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>2.706097471680941</v>
+        <v>3.354248943</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>1.632727047720352</v>
+        <v>2.89117289</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>1.020539348980394</v>
+        <v>1.611207445</v>
       </c>
     </row>
     <row r="124">
@@ -24141,13 +24141,13 @@
         <v>108</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>2.691609131192727</v>
+        <v>3.350797153</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>1.597791719030167</v>
+        <v>2.877272554</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>1.003865599783101</v>
+        <v>1.579848778</v>
       </c>
     </row>
     <row r="125">
@@ -24155,13 +24155,13 @@
         <v>112</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>2.677386699604338</v>
+        <v>3.347170944</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>1.563497569005306</v>
+        <v>2.863204403</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>0.9876907846533931</v>
+        <v>1.548881773</v>
       </c>
     </row>
     <row r="126">
@@ -24169,13 +24169,13 @@
         <v>116</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>2.663416052172821</v>
+        <v>3.343368462</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>1.529810539049612</v>
+        <v>2.848959657</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>0.9719829295435964</v>
+        <v>1.518341202</v>
       </c>
     </row>
     <row r="127">
@@ -24183,13 +24183,13 @@
         <v>120</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>2.649684272044349</v>
+        <v>3.339388197</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>1.496699483116065</v>
+        <v>2.83453059</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>0.9567131276628569</v>
+        <v>1.488257914</v>
       </c>
     </row>
     <row r="128">
@@ -24197,13 +24197,13 @@
         <v>124</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>2.636179510407019</v>
+        <v>3.335228943</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>1.46413583049715</v>
+        <v>2.819910394</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>0.9418551539675653</v>
+        <v>1.458659334</v>
       </c>
     </row>
     <row r="129">
@@ -24211,13 +24211,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>2.622890866796976</v>
+        <v>3.330889747</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>1.432093297210384</v>
+        <v>2.80509306</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>0.9273851388471925</v>
+        <v>1.42956989</v>
       </c>
     </row>
     <row r="130">
@@ -24225,13 +24225,13 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>2.609808286117925</v>
+        <v>3.326369881</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>1.400547637684346</v>
+        <v>2.79007328</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>0.9132812903680758</v>
+        <v>1.401011375</v>
       </c>
     </row>
     <row r="131">
@@ -24239,13 +24239,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>2.596922469607174</v>
+        <v>3.321668806</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>1.369476430073595</v>
+        <v>2.774846365</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>0.8995236566108025</v>
+        <v>1.37300326</v>
       </c>
     </row>
     <row r="132">
@@ -24253,13 +24253,13 @@
         <v>140</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>2.584224797506923</v>
+        <v>3.316786153</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>1.338858889798134</v>
+        <v>2.759408168</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>0.886093921315672</v>
+        <v>1.345562957</v>
       </c>
     </row>
     <row r="133">
@@ -24267,13 +24267,13 @@
         <v>144</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>2.571707261613167</v>
+        <v>3.311721694</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>1.308675706900459</v>
+        <v>2.743755027</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>0.8729752273585061</v>
+        <v>1.318706056</v>
       </c>
     </row>
     <row r="134">
@@ -24281,13 +24281,13 @@
         <v>148</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>2.559362406202513</v>
+        <v>3.306475326</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>1.278908903604052</v>
+        <v>2.727883704</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>0.8601520236057776</v>
+        <v>1.292446521</v>
       </c>
     </row>
     <row r="135">
@@ -24295,13 +24295,13 @@
         <v>152</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>2.547183276099126</v>
+        <v>3.301047059</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>1.249541709088677</v>
+        <v>2.711791343</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>0.847609931509965</v>
+        <v>1.266796868</v>
       </c>
     </row>
     <row r="136">
@@ -24309,13 +24309,13 @@
         <v>156</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>2.535163370854512</v>
+        <v>3.295436995</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>1.220558449005366</v>
+        <v>2.695475428</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>0.8353356284525475</v>
+        <v>1.241768316</v>
       </c>
     </row>
     <row r="137">
@@ -24323,13 +24323,13 @@
         <v>160</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>2.52329660418306</v>
+        <v>3.28964532</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>1.191944447664483</v>
+        <v>2.678933743</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>0.8233167453602359</v>
+        <v>1.21737092</v>
       </c>
     </row>
     <row r="138">
@@ -24337,13 +24337,13 @@
         <v>164</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>2.511577267934785</v>
+        <v>3.283672293</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>1.163685941164212</v>
+        <v>2.662164346</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>0.8115417765378323</v>
+        <v>1.193613692</v>
       </c>
     </row>
     <row r="139">
@@ -24351,13 +24351,13 @@
         <v>168</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>2.5</v>
+        <v>3.277518235</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>1.13577</v>
+        <v>2.645165538</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>0.7999999999999998</v>
+        <v>1.170504702</v>
       </c>
     </row>
   </sheetData>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -52,7 +52,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +73,9 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -95,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +109,10 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3362,7 +3369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3381,7 +3388,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Admissible search ranges and optimized values of the effective kinetic parameters used in the Zn biodegradation model.</t>
+          <t>Admissible search ranges and adopted values of the effective kinetic parameters used in the Zn biodegradation model (two-repeat Bayesian optimization, corrected-physics code v2).</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3431,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>35.91</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3435,16 +3442,16 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>mm^6 g^-2 h^-1</t>
+          <t>L^2 mol^-2 h^-1</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>[5, 100]</t>
+          <t>[1, 100]</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>27.17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3455,16 +3462,36 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>mm h^-1</t>
+          <t>mm h^-1 (effective)</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>[0.05, 5.0]</t>
+          <t>[0.05, 5]</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.51</v>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M_O2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>g mol^-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -5096,801 +5123,1526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Supplementary Figure 6b</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Normalized trajectories of the three calibrated kinetic parameters, k_f, k_d, and k_ORR (min-max normalized to [0,1]).</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Trajectories of the three calibrated kinetic parameters over the evaluations of each Bayesian optimization repeat (min-max normalized to [0,1] within each repeat).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Normalization: (value - min) / (max - min) over the 32 evaluated iterations (k_f: 1.213-83.562 h^-1; k_d: 5.0-100.0 mm^6 g^-2 h^-1; k_ORR: 0.0602-4.4933 mm h^-1).</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Normalization: (value - min) / (max - min) over the 28 evaluations of each repeat.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Iteration</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>k_f</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>k_d</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>k_ORR</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>k_f (norm)</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>k_d (norm)</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>k_ORR (norm)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.694926</v>
+      </c>
+      <c r="D6" t="n">
+        <v>32.895087</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.079988</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005083028097361085</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3513440221260581</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.004452686567770211</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6.248831</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.136556</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.165976</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0531127308589125</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.03995345101177653</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.02384969819902939</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>67.991682</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.30743</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.508756</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7043100617607995</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02014810734592721</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5523296129485452</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>83.562388</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19.179087</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.493303</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8685331584146614</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.202830418513847</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>19.536874</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8.429864999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.887589</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1932607479064166</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.08644038532285402</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1866298041936778</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11.869081</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21.581582</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1123890962959625</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2288440660867779</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0430969259566881</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24.90597</v>
+      </c>
+      <c r="D12" t="n">
+        <v>68.41846200000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.136741</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2498882104859466</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7359827239136008</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4684111675607831</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.364803</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.160317</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.15547</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.03324202542381006</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.007727439120466839</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02147977443992335</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="n">
         <v>9.864005000000001</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>15.319409</v>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="D14" t="n">
+        <v>5.591374</v>
+      </c>
+      <c r="E14" t="n">
         <v>1.322114</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>0.1050526460385154</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>0.1086253578947368</v>
-      </c>
-      <c r="G6" s="1" t="n">
+      <c r="F14" t="n">
+        <v>0.09124170646364929</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0557058761925807</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.2846491380434346</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>32.64415</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11.529106</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.060249</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3315022286341912</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1199982337752245</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.212982</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.959209</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.730585</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.01637765272625327</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1512131365871023</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.937196</v>
+      </c>
+      <c r="D17" t="n">
+        <v>52.238975</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.462952</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.01818515887294654</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5607950657795292</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.09084098682307952</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.65142</v>
+      </c>
+      <c r="D18" t="n">
+        <v>13.340759</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.13986</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.004624173499308634</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1396143839301438</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.01795849994157527</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.110482</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.164383</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.120551</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.02001279363316622</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05108251864519212</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.01360281196664873</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" t="n">
+        <v>96.027331</v>
+      </c>
+      <c r="D20" t="n">
+        <v>92.801824</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.155431</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.02147097689313056</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>39.312359</v>
+      </c>
+      <c r="D21" t="n">
+        <v>25.571236</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.170367</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4018313409503028</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.272043095884523</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02484021173664927</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" t="n">
+        <v>21.591821</v>
+      </c>
+      <c r="D22" t="n">
+        <v>47.992436</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.185983</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2149341235259654</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5148145459654583</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.02836283970373472</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.572647</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.149858</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.131958</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.02488721406503566</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.01844195500206724</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01617598161448067</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" t="n">
+        <v>11.112605</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.296377</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.187857</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1044105992859794</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.009200664616783361</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0287855731060348</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8.889404000000001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7.270552</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.150208</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.08096266104194841</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.07388761838318623</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.02029278235726432</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5.14321</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.115166</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.17667</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.04145182708579268</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.02889408169175055</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.02626203064523915</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" t="n">
+        <v>23.418892</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.911651</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.19234</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.2342041076504148</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.02669046941126505</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.02979683983096078</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9.933289</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9728599999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.194492</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.09197243974116195</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.005697699065615985</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.03028228395142491</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6.417317</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.426254</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.194393</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.05488974037041586</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.01060694205162903</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.03025995171725858</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" t="n">
+        <v>29.58397</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.572756</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.183263</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2992267341307168</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.001365467594366341</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.02774926720946778</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>26</v>
+      </c>
+      <c r="C31" t="n">
+        <v>11.598346</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.015978</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.192816</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1095336740644604</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.01699233403009269</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.02990421501745749</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4.048174</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.274908</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.182658</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.02990256253301913</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.008968203363068682</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.02761279244511797</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>28</v>
+      </c>
+      <c r="C33" t="n">
+        <v>17.86478</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.446648</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.176693</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1756252948591146</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.02626721894206567</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>32.64415</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>24.529234</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0.060249</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>0.3816805673133817</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>0.2055708842105263</v>
-      </c>
-      <c r="G7" s="1" t="n">
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.231553</v>
+      </c>
+      <c r="D34" t="n">
+        <v>18.768511</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.171726</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.02640608676455242</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.2209117644873664</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.02930932474636767</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.717066</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4.145834</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.075599</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.00725906538016121</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.03615021714731169</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.006000611045372543</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>7.163271</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.873456</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.597499</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0761131417761807</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.007438095870099669</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3750283699637252</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6.250469</v>
+      </c>
+      <c r="D37" t="n">
+        <v>23.214038</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.385024</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.06457297047479937</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.2770822213238261</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.08102946596574265</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>12.250578</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.125113</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.520599</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1404298218916014</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0232531264598481</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.113903464530271</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" t="n">
+        <v>80.24067599999999</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8.608919</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.379929</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.09254252414487364</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3222723613508952</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.14289</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.284779</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.886557</v>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>67.991682</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>8.613716999999999</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>2.508756</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>0.8109190247225341</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>0.03803912631578947</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.5523296129485452</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>83.562388</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>34.156142</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>4.493303</v>
-      </c>
-      <c r="E9" s="1" t="n">
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2026403464530271</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.742694</v>
+      </c>
+      <c r="D41" t="n">
+        <v>14.370312</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.309434</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.02022564828805702</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.165339309953256</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.06270052957265619</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>49.33701</v>
+      </c>
+      <c r="D42" t="n">
+        <v>49.770759</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.122391</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.6092979644209005</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.6126336982687196</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.01734665670889022</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" t="n">
+        <v>17.984653</v>
+      </c>
+      <c r="D43" t="n">
+        <v>31.99086</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.467515</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.2129233174743981</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.3879797822456897</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5859883901379217</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="n">
+        <v>11</v>
+      </c>
+      <c r="C44" t="n">
+        <v>28.784283</v>
+      </c>
+      <c r="D44" t="n">
+        <v>80.428287</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.050852</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3494584917964707</v>
+      </c>
+      <c r="G44" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>0.3069067578947369</v>
-      </c>
-      <c r="G9" s="1" t="n">
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="n">
+        <v>12</v>
+      </c>
+      <c r="C45" t="n">
+        <v>34.334475</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5.912552</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4.174932</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.4196272320441434</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.05847318519163947</v>
+      </c>
+      <c r="H45" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>19.536874</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>20.009222</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>0.887589</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>0.2225139547454659</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>0.1579918105263158</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.1866298041936778</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>11.869081</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>36.881722</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>0.2513</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>0.1294010426741876</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>0.3355970736842105</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.0430969259566881</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>24.90597</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>78.122794</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>2.136741</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0.2877129192650157</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>0.7697136210526315</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>0.4684111675607831</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>4.364803</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>5.5078</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>0.15547</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>0.0382737551258111</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>0.005345263157894732</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>0.02147977443992335</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>1.694926</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>48.516168</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>0.079988</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>0.00585242837088588</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>0.4580649263157895</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>0.004452686567770211</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>6.248831</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>12.592237</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>0.165976</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>0.06115222009008783</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>0.07991828421052632</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>0.02384969819902939</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>1.212982</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>7.744136</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>0.730585</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>0.02888564210526316</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>0.1512131365871023</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>2.937196</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>65.546769</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>0.462952</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>0.02093778308491989</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>0.6373344105263158</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>0.09084098682307952</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>60.640234</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>0.433336</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>0.7216476096986055</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>0.08416026513550252</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="C46" t="n">
+        <v>4.867365</v>
+      </c>
+      <c r="D46" t="n">
+        <v>57.98448</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.153058</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.04708696903349482</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.7164163231177471</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.02478273942309557</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>57.480181</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>18.053204</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>0.434372</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>0.683273890281613</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>0.1374021473684211</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>0.08439396407081889</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="C47" t="n">
+        <v>16.038995</v>
+      </c>
+      <c r="D47" t="n">
+        <v>14.538771</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.134354</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.188325182704861</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.1674678357699282</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.02024742488021571</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>66.116321</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>27.695915</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>0.445382</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>0.788145806419053</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>0.2389043684210526</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>0.08687757920386262</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="C48" t="n">
+        <v>67.98115900000001</v>
+      </c>
+      <c r="D48" t="n">
+        <v>9.359014999999999</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.166231</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.8450080891012551</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.102020193494582</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.027976906364571</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>58.226265</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>0.430407</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>0.692333870629255</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>0.0834995468135511</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="C49" t="n">
+        <v>34.313686</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5.614269</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.123565</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.4193644054714755</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.05470429741375629</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.01763132625943241</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="1" t="n">
-        <v>66.021243</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>11.767734</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>0.452399</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0.7869912382853131</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>0.0712393052631579</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>0.08846046089219756</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="C50" t="n">
+        <v>1.672196</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.532891</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.006691792865099916</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.003134963388279429</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.031970281856802</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="1" t="n">
-        <v>55.129743</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>65.183634</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>0.418043</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>0.6547316321868794</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>0.6335119368421053</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>0.08071049890211127</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="C51" t="n">
+        <v>24.355439</v>
+      </c>
+      <c r="D51" t="n">
+        <v>42.950018</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.188499</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.2934664821086143</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5264517589996137</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.03337641364861981</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="1" t="n">
-        <v>57.141068</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>42.489062</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>0.437817</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>0.6791559127943193</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>0.3946217052631579</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>0.08517108070418271</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="C52" t="n">
+        <v>2.724628</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.838098</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.139245</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.01999724745772278</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.01962661296236705</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.02143338635525984</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>60.154809</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>7.670637</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>0.431341</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>0.7157529102274278</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>0.02811196842105263</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>0.08371023678033246</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="C53" t="n">
+        <v>5.798896</v>
+      </c>
+      <c r="D53" t="n">
+        <v>18.590766</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.156108</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.05886392319501838</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.2186659075056415</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.02552229830653139</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="1" t="n">
-        <v>48.4118</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>29.5251</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>0.5962</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>0.5731531081110652</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>0.258158947368421</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>0.1208988205422266</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="C54" t="n">
+        <v>2.194381</v>
+      </c>
+      <c r="D54" t="n">
+        <v>22.265484</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.170137</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.01329355792588177</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.2650969805381889</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.02892402669201373</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>35.90583</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>27.16962</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>0.50747</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>0.4212883818494089</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>0.2333644210526316</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>0.1008832736979969</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="C55" t="n">
+        <v>6.885818</v>
+      </c>
+      <c r="D55" t="n">
+        <v>32.311378</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.169003</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.07260542033376258</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.3920296153665566</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.02864905627436906</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>51.43335</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>37.009824</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>0.704924</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>0.6098449331862819</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>0.3369455157894737</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>0.1454245763755641</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="C56" t="n">
+        <v>4.818499</v>
+      </c>
+      <c r="D56" t="n">
+        <v>50.940171</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.173861</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.04646917677316531</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.6274095406536693</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.02982701596477274</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>57.872716</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>21.341167</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>0.656898</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>0.6880405913310412</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>0.1720122842105263</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>0.1345909614455407</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="C57" t="n">
+        <v>3.236805</v>
+      </c>
+      <c r="D57" t="n">
+        <v>13.926651</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.173392</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.02647248558891396</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.1597335311444623</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.02971329363154934</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="1" t="n">
-        <v>36.548579</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>14.595382</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>0.427188</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>0.4290935261876692</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>0.1010040210526316</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>0.08277341083596094</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="C58" t="n">
+        <v>4.395456</v>
+      </c>
+      <c r="D58" t="n">
+        <v>6.233165</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.169249</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.04112082226928577</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.06252421866364578</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.02870870594168881</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="1" t="n">
-        <v>62.647707</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>13.264881</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>0.301923</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>0.7460251140123585</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>0.08699874736842106</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>0.05451636727186269</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="C59" t="n">
+        <v>10.654328</v>
+      </c>
+      <c r="D59" t="n">
+        <v>31.777703</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.176249</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.1202491053289406</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.3852864849003155</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.03040605419875463</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="1" t="n">
-        <v>21.406276</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>20.22353</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>0.820634</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>0.245214810656922</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>0.1602476842105263</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>0.1715262209754269</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="C60" t="n">
+        <v>13.775087</v>
+      </c>
+      <c r="D60" t="n">
+        <v>9.531221</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.167535</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1597035472016878</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.1041960636872452</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.02829309809703012</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B61" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="1" t="n">
-        <v>50.313013</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>39.610909</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>1.082887</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>0.596240257033548</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>0.3643253578947369</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>0.2306847604382893</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>75.720311</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>22.601489</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>0.222116</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>0.9047706913635782</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>0.1852788315789474</v>
-      </c>
-      <c r="G34" s="1" t="n">
-        <v>0.03651365401820054</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>14.726772</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>47.756723</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>0.526387</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>0.1641030659043248</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>0.4500707684210526</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>0.1051505350487497</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>30.214196</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>61.694967</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>0.394269</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>0.3521727163399333</v>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>0.5967891263157895</v>
-      </c>
-      <c r="G36" s="1" t="n">
-        <v>0.07534760460847081</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>25.55777</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>28.358274</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>0.705943</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>0.2956279733213862</v>
-      </c>
-      <c r="F37" s="1" t="n">
-        <v>0.2458765684210527</v>
-      </c>
-      <c r="G37" s="1" t="n">
-        <v>0.1456544404827913</v>
+      <c r="C61" t="n">
+        <v>9.712255000000001</v>
+      </c>
+      <c r="D61" t="n">
+        <v>17.663267</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.170524</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.1083388731006959</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.2069467024383099</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.02901786580279723</v>
       </c>
     </row>
   </sheetData>
@@ -10935,865 +11687,1996 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Figure 3b</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Bayesian optimization history of the 3D reaction-diffusion model (32 evaluations; global search -&gt; Phase 2 EI -&gt; dip verification -&gt; Phase 3 local refinement).</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bayesian optimization history of the 3D reaction-diffusion model for two independent repeats (28 evaluations each; Phase 1 12-point Latin hypercube, Phase 2 8 expected-improvement points, Phase 3 8 local points). RMSE is the mass-loss error of the corrected coarse-mesh simulation against the 0-336 h target (Table S7).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 mm^6 g^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
+          <t>Adopted parameters (Table 2): k_f = 10 h^-1, k_d = 1 L^2 mol^-2 h^-1, k_ORR = 0.2 mm h^-1. Best RMSE: repeat 1 0.0192% (iteration 2), repeat 2 0.0178% (iteration 20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Iteration</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>k_f</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>k_d</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>k_ORR</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>RMSE (%)</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>k_f (h^-1)</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>k_d (L^2 mol^-2 h^-1)</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>k_ORR (mm h^-1)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Mass-loss RMSE (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Corrosion-rate RMSE (mm/yr)</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Combined objective J</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Best mass-loss RMSE so far (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.694926</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32.895087</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.079988</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0995379007642396</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0468114011709742</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5754765542712792</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0995379007642396</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.248831</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.136556</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.165976</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0191804614354963</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1867721267172542</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>67.991682</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.30743</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.508756</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4849846084607035</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3200187738281432</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.439135030685126</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>83.562388</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19.179087</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.493303</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7980227408531465</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5515814435180333</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.843399810303266</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>19.536874</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8.429864999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.887589</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4072492822664947</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1774433637150709</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.266015960168591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.869081</v>
+      </c>
+      <c r="E11" t="n">
+        <v>21.581582</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0900663504424276</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0265972279734444</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4308418311423517</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>24.90597</v>
+      </c>
+      <c r="E12" t="n">
+        <v>68.41846200000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.136741</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6853833739655177</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3841315319718513</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.37467525359778</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.364803</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.160317</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.15547</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0221989833132883</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.0217860952190247</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.212713858402063</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9.864005000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.591374</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.322114</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5350168159878302</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2695081917143057</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.209638951971936</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>32.64415</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11.529106</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.060249</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1268032189663655</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0559386102791539</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.709817530199949</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.212982</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.959209</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.730585</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3726721024761462</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1574150132197432</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.043284510635012</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.937196</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52.238975</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.462952</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2472965008206664</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.09277718128827971</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.28728694484326</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.65142</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13.340759</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.13986</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0304493350064306</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0264027536415591</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2640335804978179</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3.110482</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.164383</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.120551</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0496093088346078</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0306490062189679</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3366780104944145</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>96.027331</v>
+      </c>
+      <c r="E20" t="n">
+        <v>92.801824</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.155431</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0197699565067023</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0204302342880318</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1977610535185242</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>39.312359</v>
+      </c>
+      <c r="E21" t="n">
+        <v>25.571236</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.170367</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0207390968291266</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0189019700707312</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.187103810615181</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>21.591821</v>
+      </c>
+      <c r="E22" t="n">
+        <v>47.992436</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.185983</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0324635263265894</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0163818629596948</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1949432375147445</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3.572647</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.149858</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.131958</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0388865901142765</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0281218484812028</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.294044298727933</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.112605</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.296377</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.187857</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0197580987004273</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0181874106492517</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1796822409418454</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8.889404000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.270552</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.150208</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0222061969739031</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0221987362127999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.216057116721564</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5.14321</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.115166</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.17667</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0243700506297267</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0188277774583925</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1934203522630656</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>35.90583</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>27.16962</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>0.50747</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>0.042402</v>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>dip</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>23.418892</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.911651</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.19234</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0214522969416925</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.018480502621995</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1850674678213025</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>9.933289</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9728599999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.194492</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0207922209417582</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0179294137036102</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1795109441943535</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6.417317</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.426254</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.194393</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0286694702128354</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0155570955349039</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1794828560131464</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>29.58397</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.572756</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.183263</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0463420483436276</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0242216936100289</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.2838581045742032</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>26</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.598346</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.015978</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.192816</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0243099864855181</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.0178395382738563</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1857764577035953</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4.048174</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.274908</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.182658</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0241922040071302</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0180339680972205</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.187003429471976</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>28</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>17.86478</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.446648</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.176693</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0419969349351593</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.023209791425414</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2657989913416881</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.0192423800191374</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3.231553</v>
+      </c>
+      <c r="E34" t="n">
+        <v>18.768511</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.171726</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0190140421727896</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1940565622199222</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.717066</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.145834</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.075599</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.1062073334298067</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0485815708480172</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6053469509616098</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>7.163271</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.873456</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.597499</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.5657894467630372</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2946801176678987</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.458626278248052</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>6.250469</v>
+      </c>
+      <c r="E37" t="n">
+        <v>23.214038</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.385024</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1924464463875748</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.0700715603097482</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9898062983774978</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.250578</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.125113</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.520599</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.2551070549021531</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0980700832435351</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.341441825788919</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>11.869081</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>36.881722</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>0.2513</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>0.04609</v>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>30.214196</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>61.694967</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>0.394269</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>0.046374</v>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>phase3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>80.24067599999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8.608919</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.379929</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4597572832779987</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2422662121945872</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.829354195217686</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1.14289</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.284779</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.886557</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.4244775172525806</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1873112969650209</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.376477180675593</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2.742694</v>
+      </c>
+      <c r="E41" t="n">
+        <v>14.370312</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.309434</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1398505482230308</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0452001991860874</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.68855274140671</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>49.33701</v>
+      </c>
+      <c r="E42" t="n">
+        <v>49.770759</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.122391</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0489127142556203</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.0305914808306036</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.3346272447620473</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>17.984653</v>
+      </c>
+      <c r="E43" t="n">
+        <v>31.99086</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.467515</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.7160478653017367</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4194095780127824</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.696498885819442</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="n">
+        <v>11</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>28.784283</v>
+      </c>
+      <c r="E44" t="n">
+        <v>80.428287</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.050852</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.1367614207069376</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.0628595987543068</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.7814043347299484</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="n">
+        <v>12</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Phase 1: global LHS</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>34.334475</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5.912552</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4.174932</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.7588224237323049</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5073500130046507</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5.429695399085624</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.0239720946648451</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" t="n">
+        <v>13</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4.867365</v>
+      </c>
+      <c r="E46" t="n">
+        <v>57.98448</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.153058</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0188876203900319</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.0210548395670369</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.2014999052526618</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.0188876203900319</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" t="n">
+        <v>14</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>16.038995</v>
+      </c>
+      <c r="E47" t="n">
+        <v>14.538771</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.134354</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0370662839665639</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.0277113550487108</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2871297372875327</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.0188876203900319</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>67.98115900000001</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.359014999999999</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.166231</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0233164664132851</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.021396813279604</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.2115161173939402</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.0188876203900319</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" t="n">
+        <v>16</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>34.313686</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5.614269</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.123565</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0598851722821308</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.0338077918881793</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.3839273362459086</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.0188876203900319</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" t="n">
+        <v>17</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1.672196</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.532891</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0296482774411779</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.0180321447086558</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1991760164386513</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.0188876203900319</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="n">
+        <v>18</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>24.355439</v>
+      </c>
+      <c r="E51" t="n">
+        <v>42.950018</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.188499</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.0335001091440549</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.0160950563846541</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1958704147201537</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.0188876203900319</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" t="n">
+        <v>19</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2.724628</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.838098</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.139245</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.032488539430285</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.0269069884424875</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.2718183719862061</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.0188876203900319</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" t="n">
+        <v>20</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Phase 2: EI-guided</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5.798896</v>
+      </c>
+      <c r="E53" t="n">
+        <v>18.590766</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.156108</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0177514027084212</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0198443636634406</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1898398600280297</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.0177514027084212</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="n">
         <v>21</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>48.4118</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>29.5251</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>0.5962</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>0.046388</v>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>dip</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="n">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2.194381</v>
+      </c>
+      <c r="E54" t="n">
+        <v>22.265484</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.170137</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0225302953998771</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.0189694660984399</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.1909204318334636</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.0177514027084212</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" t="n">
+        <v>22</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>6.885818</v>
+      </c>
+      <c r="E55" t="n">
+        <v>32.311378</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.169003</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0224505767653864</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.0189896424292889</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.1909278384600221</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.0177514027084212</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" t="n">
+        <v>23</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4.818499</v>
+      </c>
+      <c r="E56" t="n">
+        <v>50.940171</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.173861</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0244735491452983</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.0191207921669677</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.195876227576536</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.0177514027084212</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" t="n">
         <v>24</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>57.872716</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>21.341167</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0.656898</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>0.046866</v>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>dip</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3.236805</v>
+      </c>
+      <c r="E57" t="n">
+        <v>13.926651</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.173392</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.024270978674279</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.0190569868597491</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.194981047695198</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.0177514027084212</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58" t="n">
         <v>25</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>36.548579</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>14.595382</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>0.427188</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>0.04719</v>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>phase3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>51.43335</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>37.009824</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>0.704924</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>0.048462</v>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>dip</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>4.364803</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>5.5078</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0.15547</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>0.052771</v>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>57.141068</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>42.489062</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>0.437817</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>0.055936</v>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>phase2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>57.480181</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>18.053204</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>0.434372</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>0.056486</v>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>phase2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>66.021243</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>11.767734</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>0.452399</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>0.05756</v>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>phase2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>58.226265</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>0.430407</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>0.057868</v>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>phase2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>60.640234</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>0.433336</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>0.058507</v>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>phase2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>66.116321</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>27.695915</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>0.445382</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>0.058528</v>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>phase2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>60.154809</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>7.670637</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>0.431341</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>0.059043</v>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>phase2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>55.129743</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>65.183634</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>0.418043</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>0.059716</v>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>phase2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>6.248831</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>12.592237</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>0.165976</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>0.060445</v>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>14.726772</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>47.756723</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0.526387</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>0.070782</v>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>phase3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>25.55777</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>28.358274</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>0.705943</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>0.07711800000000001</v>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>phase3</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="1" t="n">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>4.395456</v>
+      </c>
+      <c r="E58" t="n">
+        <v>6.233165</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.169249</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0221862632109103</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.0190059845625724</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1905604894299859</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.0177514027084212</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" t="n">
         <v>26</v>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>62.647707</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>13.264881</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>0.301923</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>0.088184</v>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>phase3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>1.694926</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>48.516168</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>0.079988</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>0.100601</v>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="1" t="n">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.654328</v>
+      </c>
+      <c r="E59" t="n">
+        <v>31.777703</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.176249</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.024709303478317</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.018040673628824</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1881340341876101</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.0177514027084212</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" t="n">
+        <v>27</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13.775087</v>
+      </c>
+      <c r="E60" t="n">
+        <v>9.531221</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.167535</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0202234783729085</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.0188278745845504</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.1856056828195433</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.0177514027084212</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B61" t="n">
         <v>28</v>
       </c>
-      <c r="C26" s="1" t="n">
-        <v>50.313013</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>39.610909</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>1.082887</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>0.100613</v>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>phase3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>21.406276</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>20.22353</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>0.820634</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>0.112077</v>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>phase3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>75.720311</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>22.601489</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>0.222116</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>0.112735</v>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>phase3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>19.536874</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>20.009222</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>0.887589</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>0.126677</v>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>32.64415</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>24.529234</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>0.060249</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>0.154122</v>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>2.937196</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>65.546769</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>0.462952</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>0.160994</v>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>67.991682</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>8.613716999999999</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>2.508756</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>0.206768</v>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>24.90597</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>78.122794</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>2.136741</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>0.260444</v>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>9.864005000000001</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>15.319409</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>1.322114</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>0.276129</v>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>83.562388</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>34.156142</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>4.493303</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>0.307616</v>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>1.212982</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>7.744136</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>0.730585</v>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>0.320861</v>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Phase 3: local, combined objective</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>9.712255000000001</v>
+      </c>
+      <c r="E61" t="n">
+        <v>17.663267</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.170524</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.0220696622916709</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.0189590773923835</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.1899749590795976</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.0177514027084212</v>
       </c>
     </row>
   </sheetData>
@@ -19825,178 +21708,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Table S10</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Bayesian optimization settings used for parameter calibration.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bayesian optimization settings used for parameter calibration (two independent repeats of 28 evaluations).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Optimization method</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Bayesian optimization</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Solver</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>FreeFEM++ (MPI), corrected-physics code v2 (chloride molar-unit fix in the film-dissolution term); hard-minimum rate rule</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Surrogate model</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Gaussian Process</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Calibration geometry</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Disc, diameter 10 mm x 2 mm, in a 30 x 30 x 30 mm box; coarse tetrahedral mesh (hmin 0.5 mm, 37,399 tetrahedra, 5,818 in the metal); closed box (no O2 inflow boundary)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Objective function</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>RMSE minimization</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Time stepping</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>dt = 4 h, 336 h simulated per evaluation; no level-set redistancing; interface-relative velocity extension, probe distance 0.05 mm</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Parameters calibrated</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>k_f, k_d, k_ORR</t>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>k_f (film formation, 1/h), k_d (film dissolution, L2 mol-2 h-1, Cl- as mol/L), k_ORR (effective ORR coefficient, mm/h)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Prior distribution</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Uniform</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Search bounds (log10-uniform)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>k_f [1, 100]; k_d [1, 100] (Phase 3 allowed 0.1-100); k_ORR [0.05, 5]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Parameter bounds</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Main-text Table 2</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fixed parameters used in these runs</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>film porosity 0.25; film tortuosity 120; film density 3.998 g/cm3; D_O2 10.8, D_Zn 3.38, D_Cl 9.7, D_OH 25.45 mm2/h; C_O2,0 3.5 mg/L; Cl- 142.3 mmol/L; [Zn]sat 10 mg/L  (NOTE: differs from manuscript Table 1 for tortuosity, film density and diffusivities - to be reconciled)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Random seed</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>1</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Target data</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Liu et al., J. Mater. Sci. Technol. (2018), doi 10.1016/j.jmst.2018.05.005: mass loss and corrosion rate at 24, 48, 120, 168, 240, 336 h</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Initial sampling</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>12-point Latin hypercube design (iterations 1–12)</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mesh correction</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Coarse-to-fine bias correction: ML_fine = 1.355846 x ML_coarse - 0.001584 (Pearson r = 0.998644 vs the hmin 0.25 mm mesh); derived with the earlier code version</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Acquisition function</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Expected improvement</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Simulated corrosion rate</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>CR = ML/100 x m0 / (t rho A) x 8760 (cumulative average); m0 = 1.1217 g, rho = 0.00714 g/mm3, A = 238 mm2</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Total iterations</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>32 (optimum at iteration 22)</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Objective, Phase 1-2</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>RMSE of corrected mass loss vs target (24-336 h)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Noise treatment</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Deterministic objective</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Objective, Phase 3</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>J = sqrt(0.5 (RMSE_ML/mean ML_target)^2 + 0.5 (RMSE_CR/mean CR_target)^2)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Target RMSE</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>0.05%</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Design Phase 1</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>12-point Latin hypercube (scipy qmc), seeds 7 (repeat 1) and 101 (repeat 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Design Phase 2</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Gaussian process (Matern nu=2.5 + white noise; normalised log10 inputs; log10 RMSE output; 20 restarts), expected improvement, 8 points, minimum separation 0.15 (normalised). k_f and k_d length scales sat at the upper bound, so k_ORR was narrowed to the EI ridge (0.12-0.20) and k_f, k_d were stratified by Latin hypercube over [1,100]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Design Phase 3</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Same GP on log10 J over all 20 evaluations; EI proposals; unresolved axes (k_f, k_d) stratified within a factor 3 of the current best point; 8 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>4 cores per evaluation, about 20 min; 28 evaluations per repeat, 2 repeats</t>
         </is>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -21729,6 +21729,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -21809,7 +21810,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>film porosity 0.25; film tortuosity 120; film density 3.998 g/cm3; D_O2 10.8, D_Zn 3.38, D_Cl 9.7, D_OH 25.45 mm2/h; C_O2,0 3.5 mg/L; Cl- 142.3 mmol/L; [Zn]sat 10 mg/L  (NOTE: differs from manuscript Table 1 for tortuosity, film density and diffusivities - to be reconciled)</t>
+          <t>film porosity 0.25; film tortuosity 2.00; film density 5.606 g/cm3 (as in manuscript Table 1); D_O2 10.8, D_Zn 3.38, D_Cl 9.7, D_OH 25.45 mm2/h; C_O2,0 3.5 mg/L; Cl- 142.3 mmol/L; [Zn]sat 10 mg/L  (NOTE: diffusivities differ from manuscript Table 1 - to be reconciled)</t>
         </is>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -18314,6 +18314,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -18616,7 +18617,7 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>0.01 mm</t>
+          <t>0.005 mm</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21730,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -11719,7 +11719,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adopted parameters (Table 2): k_f = 10 h^-1, k_d = 1 L^2 mol^-2 h^-1, k_ORR = 0.2 mm h^-1. Best RMSE: repeat 1 0.0192% (iteration 2), repeat 2 0.0178% (iteration 20).</t>
+          <t>Adopted parameters (Table 2): k_f = 10 h^-1, k_d = 1 L^2 mol^-2 h^-1, k_ORR = 0.2 mm h^-1. Final best RMSE (mass-loss objective only): repeat 1 0.0173% (iteration 25; k_f 2.75, k_d 5.19, k_ORR 0.161), repeat 2 0.0178% (iteration 20; k_f 5.80, k_d 18.6, k_ORR 0.156). NOTE: repeat 1 Phase 3 rows (iterations 21-28) below are from the earlier run and must be replaced with the final data.</t>
         </is>
       </c>
     </row>
@@ -18314,7 +18314,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -21730,6 +21729,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>J = sqrt(0.5 (RMSE_ML/mean ML_target)^2 + 0.5 (RMSE_CR/mean CR_target)^2)</t>
+          <t>RMSE of corrected mass loss vs target (24-336 h), the same objective as Phases 1-2 (all points chosen and scored on mass loss only)</t>
         </is>
       </c>
     </row>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Same GP on log10 J over all 20 evaluations; EI proposals; unresolved axes (k_f, k_d) stratified within a factor 3 of the current best point; 8 points</t>
+          <t>Same GP on log10 RMSE over all 20 evaluations; EI proposals; unresolved axes (k_f, k_d) stratified within a factor 3 of the current best point; 8 points</t>
         </is>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -5136,7 +5136,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trajectories of the three calibrated kinetic parameters over the evaluations of each Bayesian optimization repeat (min-max normalized to [0,1] within each repeat).</t>
+          <t>Trajectories of the three calibrated kinetic parameters over the evaluations of each final Bayesian optimization repeat (min-max normalized to [0,1] within each repeat).</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
         <v>0.005083028097361085</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3513440221260581</v>
+        <v>0.3525701721769736</v>
       </c>
       <c r="H6" t="n">
         <v>0.004452686567770211</v>
@@ -5235,7 +5235,7 @@
         <v>0.0531127308589125</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03995345101177653</v>
+        <v>0.04176822057388145</v>
       </c>
       <c r="H7" t="n">
         <v>0.02384969819902939</v>
@@ -5261,7 +5261,7 @@
         <v>0.7043100617607995</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02014810734592721</v>
+        <v>0.02200031481652697</v>
       </c>
       <c r="H8" t="n">
         <v>0.5523296129485452</v>
@@ -5287,7 +5287,7 @@
         <v>0.8685331584146614</v>
       </c>
       <c r="G9" t="n">
-        <v>0.202830418513847</v>
+        <v>0.2043373028350725</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -5313,7 +5313,7 @@
         <v>0.1932607479064166</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08644038532285402</v>
+        <v>0.08816728094435447</v>
       </c>
       <c r="H10" t="n">
         <v>0.1866298041936778</v>
@@ -5339,7 +5339,7 @@
         <v>0.1123890962959625</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2288440660867779</v>
+        <v>0.2303017769842101</v>
       </c>
       <c r="H11" t="n">
         <v>0.0430969259566881</v>
@@ -5365,7 +5365,7 @@
         <v>0.2498882104859466</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7359827239136008</v>
+        <v>0.7364817940024588</v>
       </c>
       <c r="H12" t="n">
         <v>0.4684111675607831</v>
@@ -5391,7 +5391,7 @@
         <v>0.03324202542381006</v>
       </c>
       <c r="G13" t="n">
-        <v>0.007727439120466839</v>
+        <v>0.009603125297031771</v>
       </c>
       <c r="H13" t="n">
         <v>0.02147977443992335</v>
@@ -5417,7 +5417,7 @@
         <v>0.09124170646364929</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0557058761925807</v>
+        <v>0.05749086905086059</v>
       </c>
       <c r="H14" t="n">
         <v>0.2846491380434346</v>
@@ -5443,7 +5443,7 @@
         <v>0.3315022286341912</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1199982337752245</v>
+        <v>0.1216616952205329</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01637765272625327</v>
+        <v>0.0182369874619698</v>
       </c>
       <c r="H16" t="n">
         <v>0.1512131365871023</v>
@@ -5495,7 +5495,7 @@
         <v>0.01818515887294654</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5607950657795292</v>
+        <v>0.5616252919253236</v>
       </c>
       <c r="H17" t="n">
         <v>0.09084098682307952</v>
@@ -5521,7 +5521,7 @@
         <v>0.004624173499308634</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1396143839301438</v>
+        <v>0.141240765098184</v>
       </c>
       <c r="H18" t="n">
         <v>0.01795849994157527</v>
@@ -5547,7 +5547,7 @@
         <v>0.02001279363316622</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05108251864519212</v>
+        <v>0.05287625100528114</v>
       </c>
       <c r="H19" t="n">
         <v>0.01360281196664873</v>
@@ -5599,7 +5599,7 @@
         <v>0.4018313409503028</v>
       </c>
       <c r="G21" t="n">
-        <v>0.272043095884523</v>
+        <v>0.2734191479452331</v>
       </c>
       <c r="H21" t="n">
         <v>0.02484021173664927</v>
@@ -5625,7 +5625,7 @@
         <v>0.2149341235259654</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5148145459654583</v>
+        <v>0.5157316887799249</v>
       </c>
       <c r="H22" t="n">
         <v>0.02836283970373472</v>
@@ -5651,7 +5651,7 @@
         <v>0.02488721406503566</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01844195500206724</v>
+        <v>0.02029738760101647</v>
       </c>
       <c r="H23" t="n">
         <v>0.01617598161448067</v>
@@ -5677,7 +5677,7 @@
         <v>0.1044105992859794</v>
       </c>
       <c r="G24" t="n">
-        <v>0.009200664616783361</v>
+        <v>0.01107356596505882</v>
       </c>
       <c r="H24" t="n">
         <v>0.0287855731060348</v>
@@ -5703,7 +5703,7 @@
         <v>0.08096266104194841</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07388761838318623</v>
+        <v>0.07563824241596666</v>
       </c>
       <c r="H25" t="n">
         <v>0.02029278235726432</v>
@@ -5717,22 +5717,22 @@
         <v>21</v>
       </c>
       <c r="C26" t="n">
-        <v>5.14321</v>
+        <v>2.212004</v>
       </c>
       <c r="D26" t="n">
-        <v>3.115166</v>
+        <v>1.464689</v>
       </c>
       <c r="E26" t="n">
-        <v>0.17667</v>
+        <v>0.169594</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04145182708579268</v>
+        <v>0.01053661192147193</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02889408169175055</v>
+        <v>0.01289256353757808</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02626203064523915</v>
+        <v>0.02466583984765356</v>
       </c>
     </row>
     <row r="27">
@@ -5743,22 +5743,22 @@
         <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>23.418892</v>
+        <v>13.899914</v>
       </c>
       <c r="D27" t="n">
-        <v>2.911651</v>
+        <v>2.782232</v>
       </c>
       <c r="E27" t="n">
-        <v>0.19234</v>
+        <v>0.168231</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2342041076504148</v>
+        <v>0.1338081433222729</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02669046941126505</v>
+        <v>0.02713164048211995</v>
       </c>
       <c r="H27" t="n">
-        <v>0.02979683983096078</v>
+        <v>0.02435837686615141</v>
       </c>
     </row>
     <row r="28">
@@ -5769,22 +5769,22 @@
         <v>23</v>
       </c>
       <c r="C28" t="n">
-        <v>9.933289</v>
+        <v>16.688455</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9728599999999999</v>
+        <v>1.608151</v>
       </c>
       <c r="E28" t="n">
-        <v>0.194492</v>
+        <v>0.169487</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09197243974116195</v>
+        <v>0.1632186811724036</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005697699065615985</v>
+        <v>0.01444299980919719</v>
       </c>
       <c r="H28" t="n">
-        <v>0.03028228395142491</v>
+        <v>0.02464170298850409</v>
       </c>
     </row>
     <row r="29">
@@ -5795,22 +5795,22 @@
         <v>24</v>
       </c>
       <c r="C29" t="n">
-        <v>6.417317</v>
+        <v>3.943548</v>
       </c>
       <c r="D29" t="n">
-        <v>1.426254</v>
+        <v>0.630457</v>
       </c>
       <c r="E29" t="n">
-        <v>0.194393</v>
+        <v>0.167983</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05488974037041586</v>
+        <v>0.02879907976797899</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01060694205162903</v>
+        <v>0.003876771538683878</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03025995171725858</v>
+        <v>0.02430243349167413</v>
       </c>
     </row>
     <row r="30">
@@ -5821,22 +5821,22 @@
         <v>25</v>
       </c>
       <c r="C30" t="n">
-        <v>29.58397</v>
+        <v>2.746778</v>
       </c>
       <c r="D30" t="n">
-        <v>0.572756</v>
+        <v>5.193701</v>
       </c>
       <c r="E30" t="n">
-        <v>0.183263</v>
+        <v>0.161242</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2992267341307168</v>
+        <v>0.0161768341625169</v>
       </c>
       <c r="G30" t="n">
-        <v>0.001365467594366341</v>
+        <v>0.05319309930386425</v>
       </c>
       <c r="H30" t="n">
-        <v>0.02774926720946778</v>
+        <v>0.02278181136525745</v>
       </c>
     </row>
     <row r="31">
@@ -5847,22 +5847,22 @@
         <v>26</v>
       </c>
       <c r="C31" t="n">
-        <v>11.598346</v>
+        <v>8.932912999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>2.015978</v>
+        <v>0.84551</v>
       </c>
       <c r="E31" t="n">
-        <v>0.192816</v>
+        <v>0.17345</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1095336740644604</v>
+        <v>0.0814215472807813</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01699233403009269</v>
+        <v>0.006200912924699032</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02990421501745749</v>
+        <v>0.02553566908952609</v>
       </c>
     </row>
     <row r="32">
@@ -5873,22 +5873,22 @@
         <v>27</v>
       </c>
       <c r="C32" t="n">
-        <v>4.048174</v>
+        <v>4.808245</v>
       </c>
       <c r="D32" t="n">
-        <v>1.274908</v>
+        <v>3.38274</v>
       </c>
       <c r="E32" t="n">
-        <v>0.182658</v>
+        <v>0.165505</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02990256253301913</v>
+        <v>0.03791897574490544</v>
       </c>
       <c r="G32" t="n">
-        <v>0.008968203363068682</v>
+        <v>0.03362150807491423</v>
       </c>
       <c r="H32" t="n">
-        <v>0.02761279244511797</v>
+        <v>0.02374345090314713</v>
       </c>
     </row>
     <row r="33">
@@ -5899,22 +5899,22 @@
         <v>28</v>
       </c>
       <c r="C33" t="n">
-        <v>17.86478</v>
+        <v>6.86785</v>
       </c>
       <c r="D33" t="n">
-        <v>0.446648</v>
+        <v>0.271739</v>
       </c>
       <c r="E33" t="n">
-        <v>0.176693</v>
+        <v>0.170569</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1756252948591146</v>
+        <v>0.05964147894956278</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.02626721894206567</v>
+        <v>0.02488577851747351</v>
       </c>
     </row>
     <row r="34">
@@ -6445,22 +6445,22 @@
         <v>21</v>
       </c>
       <c r="C54" t="n">
-        <v>2.194381</v>
+        <v>6.901248</v>
       </c>
       <c r="D54" t="n">
-        <v>22.265484</v>
+        <v>17.600511</v>
       </c>
       <c r="E54" t="n">
-        <v>0.170137</v>
+        <v>0.154715</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01329355792588177</v>
+        <v>0.07280049532612708</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2650969805381889</v>
+        <v>0.2061537631109301</v>
       </c>
       <c r="H54" t="n">
-        <v>0.02892402669201373</v>
+        <v>0.02518452600337529</v>
       </c>
     </row>
     <row r="55">
@@ -6471,22 +6471,22 @@
         <v>22</v>
       </c>
       <c r="C55" t="n">
-        <v>6.885818</v>
+        <v>2.798155</v>
       </c>
       <c r="D55" t="n">
-        <v>32.311378</v>
+        <v>21.5669</v>
       </c>
       <c r="E55" t="n">
-        <v>0.169003</v>
+        <v>0.159133</v>
       </c>
       <c r="F55" t="n">
-        <v>0.07260542033376258</v>
+        <v>0.02092681835620532</v>
       </c>
       <c r="G55" t="n">
-        <v>0.3920296153665566</v>
+        <v>0.2562701794820619</v>
       </c>
       <c r="H55" t="n">
-        <v>0.02864905627436906</v>
+        <v>0.02625579523190626</v>
       </c>
     </row>
     <row r="56">
@@ -6497,22 +6497,22 @@
         <v>23</v>
       </c>
       <c r="C56" t="n">
-        <v>4.818499</v>
+        <v>7.949332</v>
       </c>
       <c r="D56" t="n">
-        <v>50.940171</v>
+        <v>25.587326</v>
       </c>
       <c r="E56" t="n">
-        <v>0.173861</v>
+        <v>0.154339</v>
       </c>
       <c r="F56" t="n">
-        <v>0.04646917677316531</v>
+        <v>0.08605097998571036</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6274095406536693</v>
+        <v>0.3070693682165314</v>
       </c>
       <c r="H56" t="n">
-        <v>0.02982701596477274</v>
+        <v>0.02509335415413862</v>
       </c>
     </row>
     <row r="57">
@@ -6523,22 +6523,22 @@
         <v>24</v>
       </c>
       <c r="C57" t="n">
-        <v>3.236805</v>
+        <v>11.348658</v>
       </c>
       <c r="D57" t="n">
-        <v>13.926651</v>
+        <v>6.902363</v>
       </c>
       <c r="E57" t="n">
-        <v>0.173392</v>
+        <v>0.156126</v>
       </c>
       <c r="F57" t="n">
-        <v>0.02647248558891396</v>
+        <v>0.1290272271337658</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1597335311444623</v>
+        <v>0.07097971952418386</v>
       </c>
       <c r="H57" t="n">
-        <v>0.02971329363154934</v>
+        <v>0.02552666291633527</v>
       </c>
     </row>
     <row r="58">
@@ -6549,22 +6549,22 @@
         <v>25</v>
       </c>
       <c r="C58" t="n">
-        <v>4.395456</v>
+        <v>3.864819</v>
       </c>
       <c r="D58" t="n">
-        <v>6.233165</v>
+        <v>12.903469</v>
       </c>
       <c r="E58" t="n">
-        <v>0.169249</v>
+        <v>0.153833</v>
       </c>
       <c r="F58" t="n">
-        <v>0.04112082226928577</v>
+        <v>0.03441220213167534</v>
       </c>
       <c r="G58" t="n">
-        <v>0.06252421866364578</v>
+        <v>0.1468053450448519</v>
       </c>
       <c r="H58" t="n">
-        <v>0.02870870594168881</v>
+        <v>0.024970660122985</v>
       </c>
     </row>
     <row r="59">
@@ -6575,22 +6575,22 @@
         <v>26</v>
       </c>
       <c r="C59" t="n">
-        <v>10.654328</v>
+        <v>13.976492</v>
       </c>
       <c r="D59" t="n">
-        <v>31.777703</v>
+        <v>49.683661</v>
       </c>
       <c r="E59" t="n">
-        <v>0.176249</v>
+        <v>0.15585</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1202491053289406</v>
+        <v>0.1622498258042267</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3852864849003155</v>
+        <v>0.6115331910736128</v>
       </c>
       <c r="H59" t="n">
-        <v>0.03040605419875463</v>
+        <v>0.02545973889934239</v>
       </c>
     </row>
     <row r="60">
@@ -6601,22 +6601,22 @@
         <v>27</v>
       </c>
       <c r="C60" t="n">
-        <v>13.775087</v>
+        <v>5.239894</v>
       </c>
       <c r="D60" t="n">
-        <v>9.531221</v>
+        <v>8.348601</v>
       </c>
       <c r="E60" t="n">
-        <v>0.167535</v>
+        <v>0.160076</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1597035472016878</v>
+        <v>0.05179669630702432</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1041960636872452</v>
+        <v>0.08925333458810039</v>
       </c>
       <c r="H60" t="n">
-        <v>0.02829309809703012</v>
+        <v>0.02648445228996527</v>
       </c>
     </row>
     <row r="61">
@@ -6627,22 +6627,22 @@
         <v>28</v>
       </c>
       <c r="C61" t="n">
-        <v>9.712255000000001</v>
+        <v>2.416345</v>
       </c>
       <c r="D61" t="n">
-        <v>17.663267</v>
+        <v>41.608103</v>
       </c>
       <c r="E61" t="n">
-        <v>0.170524</v>
+        <v>0.164407</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1083388731006959</v>
+        <v>0.01609975530794251</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2069467024383099</v>
+        <v>0.509496293745281</v>
       </c>
       <c r="H61" t="n">
-        <v>0.02901786580279723</v>
+        <v>0.02753462590444414</v>
       </c>
     </row>
   </sheetData>
@@ -11692,14 +11692,14 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11712,14 +11712,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bayesian optimization history of the 3D reaction-diffusion model for two independent repeats (28 evaluations each; Phase 1 12-point Latin hypercube, Phase 2 8 expected-improvement points, Phase 3 8 local points). RMSE is the mass-loss error of the corrected coarse-mesh simulation against the 0-336 h target (Table S7).</t>
+          <t>Final Bayesian optimization history of the 3D reaction-diffusion model for two independent repeats (28 evaluations each; Phase 1 12-point Latin hypercube, Phase 2 8 expected-improvement points, Phase 3 8 local points; all points chosen and scored on mass loss only). RMSE is the mass-loss error of the corrected coarse-mesh simulation against the 0-336 h target (Table S7).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adopted parameters (Table 2): k_f = 10 h^-1, k_d = 1 L^2 mol^-2 h^-1, k_ORR = 0.2 mm h^-1. Final best RMSE (mass-loss objective only): repeat 1 0.0173% (iteration 25; k_f 2.75, k_d 5.19, k_ORR 0.161), repeat 2 0.0178% (iteration 20; k_f 5.80, k_d 18.6, k_ORR 0.156). NOTE: repeat 1 Phase 3 rows (iterations 21-28) below are from the earlier run and must be replaced with the final data.</t>
+          <t>Best RMSE: repeat 1 0.0173% (iteration 25; k_f 2.75, k_d 5.19, k_ORR 0.161), repeat 2 0.0178% (iteration 20; k_f 5.80, k_d 18.6, k_ORR 0.156). Adopted values (Table 2): k_f = 10 h^-1, k_d = 1 L^2 mol^-2 h^-1, k_ORR = 0.2 mm h^-1.</t>
         </is>
       </c>
     </row>
@@ -11741,37 +11741,37 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
+          <t>Run in stage</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
           <t>k_f (h^-1)</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>k_d (L^2 mol^-2 h^-1)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>k_ORR (mm h^-1)</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Mass-loss RMSE (%)</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>Corrosion-rate RMSE (mm/yr)</t>
-        </is>
-      </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>Combined objective J</t>
+          <t>Corrected mass loss at 336 h (%)</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Best mass-loss RMSE so far (%)</t>
+          <t>Best RMSE so far (%)</t>
         </is>
       </c>
     </row>
@@ -11788,25 +11788,25 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>1.694926</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>32.895087</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.079988</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.0995379007642396</v>
-      </c>
       <c r="H6" t="n">
-        <v>0.0468114011709742</v>
+        <v>0.099538</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5754765542712792</v>
+        <v>0.176334</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0995379007642396</v>
+        <v>0.099538</v>
       </c>
     </row>
     <row r="7">
@@ -11822,25 +11822,25 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>6.248831</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>4.136556</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.165976</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.0192423800191374</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.0191804614354963</v>
+        <v>0.019242</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1867721267172542</v>
+        <v>0.348833</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="8">
@@ -11856,25 +11856,25 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
         <v>67.991682</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2.30743</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>2.508756</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.4849846084607035</v>
-      </c>
       <c r="H8" t="n">
-        <v>0.3200187738281432</v>
+        <v>0.484985</v>
       </c>
       <c r="I8" t="n">
-        <v>3.439135030685126</v>
+        <v>0.922839</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="9">
@@ -11890,25 +11890,25 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
         <v>83.562388</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>19.179087</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>4.493303</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.7980227408531465</v>
-      </c>
       <c r="H9" t="n">
-        <v>0.5515814435180333</v>
+        <v>0.798023</v>
       </c>
       <c r="I9" t="n">
-        <v>5.843399810303266</v>
+        <v>1.249787</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="10">
@@ -11924,25 +11924,25 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
         <v>19.536874</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>8.429864999999999</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.887589</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.4072492822664947</v>
-      </c>
       <c r="H10" t="n">
-        <v>0.1774433637150709</v>
+        <v>0.407249</v>
       </c>
       <c r="I10" t="n">
-        <v>2.266015960168591</v>
+        <v>0.9174870000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="11">
@@ -11958,25 +11958,25 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
         <v>11.869081</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>21.581582</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.2513</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.0900663504424276</v>
-      </c>
       <c r="H11" t="n">
-        <v>0.0265972279734444</v>
+        <v>0.09006599999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4308418311423517</v>
+        <v>0.481302</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="12">
@@ -11992,25 +11992,25 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
         <v>24.90597</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>68.41846200000001</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>2.136741</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.6853833739655177</v>
-      </c>
       <c r="H12" t="n">
-        <v>0.3841315319718513</v>
+        <v>0.685383</v>
       </c>
       <c r="I12" t="n">
-        <v>4.37467525359778</v>
+        <v>1.199515</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="13">
@@ -12026,25 +12026,25 @@
         </is>
       </c>
       <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
         <v>4.364803</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1.160317</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.15547</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0221989833132883</v>
-      </c>
       <c r="H13" t="n">
-        <v>0.0217860952190247</v>
+        <v>0.022199</v>
       </c>
       <c r="I13" t="n">
-        <v>0.212713858402063</v>
+        <v>0.317281</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="14">
@@ -12060,25 +12060,25 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
         <v>9.864005000000001</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>5.591374</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1.322114</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.5350168159878302</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.2695081917143057</v>
+        <v>0.535017</v>
       </c>
       <c r="I14" t="n">
-        <v>3.209638951971936</v>
+        <v>1.074189</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="15">
@@ -12094,25 +12094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
         <v>32.64415</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>11.529106</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.060249</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.1268032189663655</v>
-      </c>
       <c r="H15" t="n">
-        <v>0.0559386102791539</v>
+        <v>0.126803</v>
       </c>
       <c r="I15" t="n">
-        <v>0.709817530199949</v>
+        <v>0.12901</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="16">
@@ -12128,25 +12128,25 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
         <v>1.212982</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1.959209</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.730585</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.3726721024761462</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.1574150132197432</v>
+        <v>0.372672</v>
       </c>
       <c r="I16" t="n">
-        <v>2.043284510635012</v>
+        <v>0.871742</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="17">
@@ -12162,25 +12162,25 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" t="n">
         <v>2.937196</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>52.238975</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.462952</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.2472965008206664</v>
-      </c>
       <c r="H17" t="n">
-        <v>0.09277718128827971</v>
+        <v>0.247297</v>
       </c>
       <c r="I17" t="n">
-        <v>1.28728694484326</v>
+        <v>0.716529</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="18">
@@ -12196,25 +12196,25 @@
         </is>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>1.65142</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>13.340759</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>0.13986</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.0304493350064306</v>
-      </c>
       <c r="H18" t="n">
-        <v>0.0264027536415591</v>
+        <v>0.030449</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2640335804978179</v>
+        <v>0.308333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="19">
@@ -12230,25 +12230,25 @@
         </is>
       </c>
       <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
         <v>3.110482</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>5.164383</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.120551</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.0496093088346078</v>
-      </c>
       <c r="H19" t="n">
-        <v>0.0306490062189679</v>
+        <v>0.049609</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3366780104944145</v>
+        <v>0.27296</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="20">
@@ -12264,25 +12264,25 @@
         </is>
       </c>
       <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
         <v>96.027331</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>92.801824</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.155431</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.0197699565067023</v>
-      </c>
       <c r="H20" t="n">
-        <v>0.0204302342880318</v>
+        <v>0.01977</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1977610535185242</v>
+        <v>0.330476</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="21">
@@ -12298,25 +12298,25 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
         <v>39.312359</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>25.571236</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.170367</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.0207390968291266</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.0189019700707312</v>
+        <v>0.020739</v>
       </c>
       <c r="I21" t="n">
-        <v>0.187103810615181</v>
+        <v>0.355315</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="22">
@@ -12332,25 +12332,25 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
         <v>21.591821</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>47.992436</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>0.185983</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.0324635263265894</v>
-      </c>
       <c r="H22" t="n">
-        <v>0.0163818629596948</v>
+        <v>0.032464</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1949432375147445</v>
+        <v>0.387205</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="23">
@@ -12366,25 +12366,25 @@
         </is>
       </c>
       <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
         <v>3.572647</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>2.149858</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>0.131958</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.0388865901142765</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.0281218484812028</v>
+        <v>0.038887</v>
       </c>
       <c r="I23" t="n">
-        <v>0.294044298727933</v>
+        <v>0.286809</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="24">
@@ -12400,25 +12400,25 @@
         </is>
       </c>
       <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
         <v>11.112605</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>1.296377</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>0.187857</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.0197580987004273</v>
-      </c>
       <c r="H24" t="n">
-        <v>0.0181874106492517</v>
+        <v>0.019758</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1796822409418454</v>
+        <v>0.354644</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="25">
@@ -12434,25 +12434,25 @@
         </is>
       </c>
       <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="n">
         <v>8.889404000000001</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>7.270552</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>0.150208</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.0222061969739031</v>
-      </c>
       <c r="H25" t="n">
-        <v>0.0221987362127999</v>
+        <v>0.022206</v>
       </c>
       <c r="I25" t="n">
-        <v>0.216057116721564</v>
+        <v>0.319582</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="26">
@@ -12464,29 +12464,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.14321</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>3.115166</v>
+        <v>2.212004</v>
       </c>
       <c r="F26" t="n">
-        <v>0.17667</v>
+        <v>1.464689</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0243700506297267</v>
+        <v>0.169594</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0188277774583925</v>
+        <v>0.020802</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1934203522630656</v>
+        <v>0.355315</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="27">
@@ -12498,29 +12498,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>23.418892</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>2.911651</v>
+        <v>13.899914</v>
       </c>
       <c r="F27" t="n">
-        <v>0.19234</v>
+        <v>2.782232</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0214522969416925</v>
+        <v>0.168231</v>
       </c>
       <c r="H27" t="n">
-        <v>0.018480502621995</v>
+        <v>0.019658</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1850674678213025</v>
+        <v>0.335433</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="28">
@@ -12532,29 +12532,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9.933289</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9728599999999999</v>
+        <v>16.688455</v>
       </c>
       <c r="F28" t="n">
-        <v>0.194492</v>
+        <v>1.608151</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0207922209417582</v>
+        <v>0.169487</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0179294137036102</v>
+        <v>0.023654</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1795109441943535</v>
+        <v>0.313753</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.019242</v>
       </c>
     </row>
     <row r="29">
@@ -12566,29 +12566,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6.417317</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>1.426254</v>
+        <v>3.943548</v>
       </c>
       <c r="F29" t="n">
-        <v>0.194393</v>
+        <v>0.630457</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0286694702128354</v>
+        <v>0.167983</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0155570955349039</v>
+        <v>0.018551</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1794828560131464</v>
+        <v>0.332743</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.018551</v>
       </c>
     </row>
     <row r="30">
@@ -12600,29 +12600,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29.58397</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>0.572756</v>
+        <v>2.746778</v>
       </c>
       <c r="F30" t="n">
-        <v>0.183263</v>
+        <v>5.193701</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0463420483436276</v>
+        <v>0.161242</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0242216936100289</v>
+        <v>0.017299</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2838581045742032</v>
+        <v>0.338702</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.017299</v>
       </c>
     </row>
     <row r="31">
@@ -12634,29 +12634,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.598346</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>2.015978</v>
+        <v>8.932912999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0.192816</v>
+        <v>0.84551</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0243099864855181</v>
+        <v>0.17345</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0178395382738563</v>
+        <v>0.020737</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1857764577035953</v>
+        <v>0.323655</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.017299</v>
       </c>
     </row>
     <row r="32">
@@ -12668,29 +12668,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.048174</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>1.274908</v>
+        <v>4.808245</v>
       </c>
       <c r="F32" t="n">
-        <v>0.182658</v>
+        <v>3.38274</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0241922040071302</v>
+        <v>0.165505</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0180339680972205</v>
+        <v>0.018571</v>
       </c>
       <c r="I32" t="n">
-        <v>0.187003429471976</v>
+        <v>0.346478</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.017299</v>
       </c>
     </row>
     <row r="33">
@@ -12702,29 +12702,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17.86478</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>0.446648</v>
+        <v>6.86785</v>
       </c>
       <c r="F33" t="n">
-        <v>0.176693</v>
+        <v>0.271739</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0419969349351593</v>
+        <v>0.170569</v>
       </c>
       <c r="H33" t="n">
-        <v>0.023209791425414</v>
+        <v>0.028932</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2657989913416881</v>
+        <v>0.295822</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0192423800191374</v>
+        <v>0.017299</v>
       </c>
     </row>
     <row r="34">
@@ -12740,25 +12740,25 @@
         </is>
       </c>
       <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
         <v>3.231553</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>18.768511</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>0.171726</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.0239720946648451</v>
-      </c>
       <c r="H34" t="n">
-        <v>0.0190140421727896</v>
+        <v>0.023972</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1940565622199222</v>
+        <v>0.366715</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="35">
@@ -12774,25 +12774,25 @@
         </is>
       </c>
       <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
         <v>1.717066</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>4.145834</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>0.075599</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.1062073334298067</v>
-      </c>
       <c r="H35" t="n">
-        <v>0.0485815708480172</v>
+        <v>0.106207</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6053469509616098</v>
+        <v>0.167068</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="36">
@@ -12808,25 +12808,25 @@
         </is>
       </c>
       <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
         <v>7.163271</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>1.873456</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>1.597499</v>
       </c>
-      <c r="G36" t="n">
-        <v>0.5657894467630372</v>
-      </c>
       <c r="H36" t="n">
-        <v>0.2946801176678987</v>
+        <v>0.565789</v>
       </c>
       <c r="I36" t="n">
-        <v>3.458626278248052</v>
+        <v>1.098042</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="37">
@@ -12842,25 +12842,25 @@
         </is>
       </c>
       <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
         <v>6.250469</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>23.214038</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>0.385024</v>
       </c>
-      <c r="G37" t="n">
-        <v>0.1924464463875748</v>
-      </c>
       <c r="H37" t="n">
-        <v>0.0700715603097482</v>
+        <v>0.192446</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9898062983774978</v>
+        <v>0.638341</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="38">
@@ -12876,25 +12876,25 @@
         </is>
       </c>
       <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
         <v>12.250578</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>3.125113</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>0.520599</v>
       </c>
-      <c r="G38" t="n">
-        <v>0.2551070549021531</v>
-      </c>
       <c r="H38" t="n">
-        <v>0.0980700832435351</v>
+        <v>0.255107</v>
       </c>
       <c r="I38" t="n">
-        <v>1.341441825788919</v>
+        <v>0.723939</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="39">
@@ -12910,25 +12910,25 @@
         </is>
       </c>
       <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="n">
         <v>80.24067599999999</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>8.608919</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>1.379929</v>
       </c>
-      <c r="G39" t="n">
-        <v>0.4597572832779987</v>
-      </c>
       <c r="H39" t="n">
-        <v>0.2422662121945872</v>
+        <v>0.459757</v>
       </c>
       <c r="I39" t="n">
-        <v>2.829354195217686</v>
+        <v>0.9547949999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="40">
@@ -12944,25 +12944,25 @@
         </is>
       </c>
       <c r="D40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" t="n">
         <v>1.14289</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>1.284779</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>0.886557</v>
       </c>
-      <c r="G40" t="n">
-        <v>0.4244775172525806</v>
-      </c>
       <c r="H40" t="n">
-        <v>0.1873112969650209</v>
+        <v>0.424478</v>
       </c>
       <c r="I40" t="n">
-        <v>2.376477180675593</v>
+        <v>0.945305</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="41">
@@ -12978,25 +12978,25 @@
         </is>
       </c>
       <c r="D41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" t="n">
         <v>2.742694</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>14.370312</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>0.309434</v>
       </c>
-      <c r="G41" t="n">
-        <v>0.1398505482230308</v>
-      </c>
       <c r="H41" t="n">
-        <v>0.0452001991860874</v>
+        <v>0.139851</v>
       </c>
       <c r="I41" t="n">
-        <v>0.68855274140671</v>
+        <v>0.5533979999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="42">
@@ -13012,25 +13012,25 @@
         </is>
       </c>
       <c r="D42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" t="n">
         <v>49.33701</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>49.770759</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>0.122391</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.0489127142556203</v>
-      </c>
       <c r="H42" t="n">
-        <v>0.0305914808306036</v>
+        <v>0.048913</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3346272447620473</v>
+        <v>0.27405</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="43">
@@ -13046,25 +13046,25 @@
         </is>
       </c>
       <c r="D43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E43" t="n">
         <v>17.984653</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>31.99086</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>2.467515</v>
       </c>
-      <c r="G43" t="n">
-        <v>0.7160478653017367</v>
-      </c>
       <c r="H43" t="n">
-        <v>0.4194095780127824</v>
+        <v>0.716048</v>
       </c>
       <c r="I43" t="n">
-        <v>4.696498885819442</v>
+        <v>1.212034</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="44">
@@ -13080,25 +13080,25 @@
         </is>
       </c>
       <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="n">
         <v>28.784283</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>80.428287</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>0.050852</v>
       </c>
-      <c r="G44" t="n">
-        <v>0.1367614207069376</v>
-      </c>
       <c r="H44" t="n">
-        <v>0.0628595987543068</v>
+        <v>0.136761</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7814043347299484</v>
+        <v>0.112901</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="45">
@@ -13114,25 +13114,25 @@
         </is>
       </c>
       <c r="D45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E45" t="n">
         <v>34.334475</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>5.912552</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>4.174932</v>
       </c>
-      <c r="G45" t="n">
-        <v>0.7588224237323049</v>
-      </c>
       <c r="H45" t="n">
-        <v>0.5073500130046507</v>
+        <v>0.758822</v>
       </c>
       <c r="I45" t="n">
-        <v>5.429695399085624</v>
+        <v>1.210164</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0239720946648451</v>
+        <v>0.023972</v>
       </c>
     </row>
     <row r="46">
@@ -13148,25 +13148,25 @@
         </is>
       </c>
       <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
         <v>4.867365</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>57.98448</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>0.153058</v>
       </c>
-      <c r="G46" t="n">
-        <v>0.0188876203900319</v>
-      </c>
       <c r="H46" t="n">
-        <v>0.0210548395670369</v>
+        <v>0.018888</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2014999052526618</v>
+        <v>0.325427</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0188876203900319</v>
+        <v>0.018888</v>
       </c>
     </row>
     <row r="47">
@@ -13182,25 +13182,25 @@
         </is>
       </c>
       <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
         <v>16.038995</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>14.538771</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>0.134354</v>
       </c>
-      <c r="G47" t="n">
-        <v>0.0370662839665639</v>
-      </c>
       <c r="H47" t="n">
-        <v>0.0277113550487108</v>
+        <v>0.037066</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2871297372875327</v>
+        <v>0.292045</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0188876203900319</v>
+        <v>0.018888</v>
       </c>
     </row>
     <row r="48">
@@ -13216,25 +13216,25 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
         <v>67.98115900000001</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>9.359014999999999</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>0.166231</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.0233164664132851</v>
-      </c>
       <c r="H48" t="n">
-        <v>0.021396813279604</v>
+        <v>0.023316</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2115161173939402</v>
+        <v>0.315387</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0188876203900319</v>
+        <v>0.018888</v>
       </c>
     </row>
     <row r="49">
@@ -13250,25 +13250,25 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
         <v>34.313686</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>5.614269</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>0.123565</v>
       </c>
-      <c r="G49" t="n">
-        <v>0.0598851722821308</v>
-      </c>
       <c r="H49" t="n">
-        <v>0.0338077918881793</v>
+        <v>0.059885</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3839273362459086</v>
+        <v>0.258294</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0188876203900319</v>
+        <v>0.018888</v>
       </c>
     </row>
     <row r="50">
@@ -13284,25 +13284,25 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="n">
         <v>1.672196</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>1.532891</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>0.1827</v>
       </c>
-      <c r="G50" t="n">
-        <v>0.0296482774411779</v>
-      </c>
       <c r="H50" t="n">
-        <v>0.0180321447086558</v>
+        <v>0.029648</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1991760164386513</v>
+        <v>0.380577</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0188876203900319</v>
+        <v>0.018888</v>
       </c>
     </row>
     <row r="51">
@@ -13318,25 +13318,25 @@
         </is>
       </c>
       <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
         <v>24.355439</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>42.950018</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>0.188499</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.0335001091440549</v>
-      </c>
       <c r="H51" t="n">
-        <v>0.0160950563846541</v>
+        <v>0.0335</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1958704147201537</v>
+        <v>0.389917</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0188876203900319</v>
+        <v>0.018888</v>
       </c>
     </row>
     <row r="52">
@@ -13352,25 +13352,25 @@
         </is>
       </c>
       <c r="D52" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" t="n">
         <v>2.724628</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>2.838098</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>0.139245</v>
       </c>
-      <c r="G52" t="n">
-        <v>0.032488539430285</v>
-      </c>
       <c r="H52" t="n">
-        <v>0.0269069884424875</v>
+        <v>0.032489</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2718183719862061</v>
+        <v>0.305515</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0188876203900319</v>
+        <v>0.018888</v>
       </c>
     </row>
     <row r="53">
@@ -13386,25 +13386,25 @@
         </is>
       </c>
       <c r="D53" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" t="n">
         <v>5.798896</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>18.590766</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>0.156108</v>
       </c>
-      <c r="G53" t="n">
-        <v>0.0177514027084212</v>
-      </c>
       <c r="H53" t="n">
-        <v>0.0198443636634406</v>
+        <v>0.017751</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1898398600280297</v>
+        <v>0.332175</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0177514027084212</v>
+        <v>0.017751</v>
       </c>
     </row>
     <row r="54">
@@ -13416,29 +13416,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.194381</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>22.265484</v>
+        <v>6.901248</v>
       </c>
       <c r="F54" t="n">
-        <v>0.170137</v>
+        <v>17.600511</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0225302953998771</v>
+        <v>0.154715</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0189694660984399</v>
+        <v>0.018855</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1909204318334636</v>
+        <v>0.331151</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0177514027084212</v>
+        <v>0.017751</v>
       </c>
     </row>
     <row r="55">
@@ -13450,29 +13450,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6.885818</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>32.311378</v>
+        <v>2.798155</v>
       </c>
       <c r="F55" t="n">
-        <v>0.169003</v>
+        <v>21.5669</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0224505767653864</v>
+        <v>0.159133</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0189896424292889</v>
+        <v>0.017883</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1909278384600221</v>
+        <v>0.336095</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0177514027084212</v>
+        <v>0.017751</v>
       </c>
     </row>
     <row r="56">
@@ -13484,29 +13484,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.818499</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>50.940171</v>
+        <v>7.949332</v>
       </c>
       <c r="F56" t="n">
-        <v>0.173861</v>
+        <v>25.587326</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0244735491452983</v>
+        <v>0.154339</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0191207921669677</v>
+        <v>0.018661</v>
       </c>
       <c r="I56" t="n">
-        <v>0.195876227576536</v>
+        <v>0.327846</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0177514027084212</v>
+        <v>0.017751</v>
       </c>
     </row>
     <row r="57">
@@ -13518,29 +13518,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.236805</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>13.926651</v>
+        <v>11.348658</v>
       </c>
       <c r="F57" t="n">
-        <v>0.173392</v>
+        <v>6.902363</v>
       </c>
       <c r="G57" t="n">
-        <v>0.024270978674279</v>
+        <v>0.156126</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0190569868597491</v>
+        <v>0.020345</v>
       </c>
       <c r="I57" t="n">
-        <v>0.194981047695198</v>
+        <v>0.330476</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0177514027084212</v>
+        <v>0.017751</v>
       </c>
     </row>
     <row r="58">
@@ -13552,29 +13552,29 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4.395456</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>6.233165</v>
+        <v>3.864819</v>
       </c>
       <c r="F58" t="n">
-        <v>0.169249</v>
+        <v>12.903469</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0221862632109103</v>
+        <v>0.153833</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0190059845625724</v>
+        <v>0.018888</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1905604894299859</v>
+        <v>0.325427</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0177514027084212</v>
+        <v>0.017751</v>
       </c>
     </row>
     <row r="59">
@@ -13586,29 +13586,29 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.654328</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>31.777703</v>
+        <v>13.976492</v>
       </c>
       <c r="F59" t="n">
-        <v>0.176249</v>
+        <v>49.683661</v>
       </c>
       <c r="G59" t="n">
-        <v>0.024709303478317</v>
+        <v>0.15585</v>
       </c>
       <c r="H59" t="n">
-        <v>0.018040673628824</v>
+        <v>0.017806</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1881340341876101</v>
+        <v>0.332175</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0177514027084212</v>
+        <v>0.017751</v>
       </c>
     </row>
     <row r="60">
@@ -13620,29 +13620,29 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.775087</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>9.531221</v>
+        <v>5.239894</v>
       </c>
       <c r="F60" t="n">
-        <v>0.167535</v>
+        <v>8.348601</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0202234783729085</v>
+        <v>0.160076</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0188278745845504</v>
+        <v>0.017999</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1856056828195433</v>
+        <v>0.337383</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0177514027084212</v>
+        <v>0.017751</v>
       </c>
     </row>
     <row r="61">
@@ -13654,29 +13654,29 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phase 3: local, combined objective</t>
+          <t>Phase 3: local (mass loss only)</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9.712255000000001</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>17.663267</v>
+        <v>2.416345</v>
       </c>
       <c r="F61" t="n">
-        <v>0.170524</v>
+        <v>41.608103</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0220696622916709</v>
+        <v>0.164407</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0189590773923835</v>
+        <v>0.01941</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1899749590795976</v>
+        <v>0.350848</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0177514027084212</v>
+        <v>0.017751</v>
       </c>
     </row>
   </sheetData>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -3388,7 +3388,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Admissible search ranges and adopted values of the effective kinetic parameters used in the Zn biodegradation model (two-repeat Bayesian optimization, corrected-physics code v2).</t>
+          <t>Admissible search ranges and optimized values of the effective kinetic parameters used in the Zn biodegradation model (best point of the two-repeat Bayesian optimization, repeat 1, iteration 25; corrected-physics code v2).</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>10</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6">
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="7">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="8">
@@ -11719,7 +11719,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Best RMSE: repeat 1 0.0173% (iteration 25; k_f 2.75, k_d 5.19, k_ORR 0.161), repeat 2 0.0178% (iteration 20; k_f 5.80, k_d 18.6, k_ORR 0.156). Adopted values (Table 2): k_f = 10 h^-1, k_d = 1 L^2 mol^-2 h^-1, k_ORR = 0.2 mm h^-1.</t>
+          <t>Best RMSE: repeat 1 0.0173% (iteration 25; k_f 2.75, k_d 5.19, k_ORR 0.161; adopted in Table 2), repeat 2 0.0178% (iteration 20; k_f 5.80, k_d 18.6, k_ORR 0.156).</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21729,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -39,6 +39,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S10" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S11" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S12" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig 4 curve provenance" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -19660,7 +19661,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c). Baseline: k_f = 10, k_d = 1, k_ORR = 0.2 (middle curves); each parameter varied by x0.2 and x5.</t>
+          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves).</t>
         </is>
       </c>
     </row>
@@ -19679,17 +19680,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>kf 2</t>
+          <t>kf 0.5</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>kf 10</t>
+          <t>kf 2.75</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kf 50</t>
+          <t>kf 15</t>
         </is>
       </c>
     </row>
@@ -20308,12 +20309,12 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 1</t>
+          <t>kd 5</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 5</t>
+          <t>kd 25</t>
         </is>
       </c>
     </row>
@@ -20932,7 +20933,7 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.2</t>
+          <t>kORR 0.16</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
@@ -22472,6 +22473,308 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fig 4 curve provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Curve labels as plotted, the simulation run each curve was taken from, and the interface-O2 power-law form O2(t) = 3.5 - a t^b (t in h, O2 in mg/L).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Plotted curve</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Underlying simulation run</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>a (mg/L per h^b)</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>O2 at 168 h (mg/L)</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Form plotted</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>kf=0.5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>kf=2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7218</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.817480688250613</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>kf=2.75</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>kf=10</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.695480524264948</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>kf=15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>kf=50</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.09273851263743695</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.266777858388112</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>end-point shape: same start (3.5) and 168 h value as fitted power law, baseline exponent b=0.505</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>kd=0.2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>kd=0.2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.09954052486815</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.176325770556762</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>end-point shape: same start (3.5) and 168 h value as fitted power law, baseline exponent b=0.505</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>kd=5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>kd=1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.695480524264948</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>kd=25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>kd=5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0664</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.909785565301525</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>kORR=0.04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>kORR=0.04</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.307647537509101</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>kORR=0.16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kORR=0.2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.695480524264948</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>kORR=1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>kORR=1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.20955154382745</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -22491,7 +22794,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Corrosion-product saturation, F/Fmax (%), in one-at-a-time parameter sweeps of k_f (panel d), k_d (panel e), and k_ORR (panel f). Baseline: k_f = 10, k_d = 1, k_ORR = 0.2 (middle curves); each parameter varied by x0.2 and x5.</t>
+          <t>Corrosion-product saturation, F/Fmax (%), in one-at-a-time parameter sweeps of k_f (panel d), k_d (panel e), and k_ORR (panel f). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves).</t>
         </is>
       </c>
     </row>
@@ -22510,17 +22813,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>kf 2</t>
+          <t>kf 0.5</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>kf 10</t>
+          <t>kf 2.75</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kf 50</t>
+          <t>kf 15</t>
         </is>
       </c>
     </row>
@@ -23139,12 +23442,12 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 1</t>
+          <t>kd 5</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 5</t>
+          <t>kd 25</t>
         </is>
       </c>
     </row>
@@ -23763,7 +24066,7 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.2</t>
+          <t>kORR 0.16</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
@@ -24398,7 +24701,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Baseline: k_f = 10, k_d = 1, k_ORR = 0.2 (middle curves); each parameter varied by x0.2 and x5. Values are the smoothed interface-O2 data (v2_O2smoothed).</t>
+          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Values are the smoothed interface-O2 data (v2_O2smoothed). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves). Interface-O2 curves are smoothed power-law depletion fits, O2 = 3.5 - a t^b (parameters in sheet "Fig 4 curve provenance").</t>
         </is>
       </c>
     </row>
@@ -24417,17 +24720,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>kf 2</t>
+          <t>kf 0.5</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>kf 10</t>
+          <t>kf 2.75</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kf 50</t>
+          <t>kf 15</t>
         </is>
       </c>
     </row>
@@ -24450,13 +24753,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>3.429078464</v>
+        <v>3.454032211932749</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>3.339223967</v>
+        <v>3.378158378443137</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>2.866842092</v>
+        <v>3.313232879991455</v>
       </c>
     </row>
     <row r="9">
@@ -24464,13 +24767,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>3.399069634</v>
+        <v>3.424188156532705</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>3.286080353</v>
+        <v>3.327091709091328</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2.761789902</v>
+        <v>3.234954417825595</v>
       </c>
     </row>
     <row r="10">
@@ -24478,13 +24781,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>3.375335507</v>
+        <v>3.398412627424506</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>3.249237344</v>
+        <v>3.287801698229836</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2.719185314</v>
+        <v>3.174728018341239</v>
       </c>
     </row>
     <row r="11">
@@ -24492,13 +24795,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>3.354671629</v>
+        <v>3.374968192911498</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>3.220283926</v>
+        <v>3.254621805890813</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2.699387556</v>
+        <v>3.123867623878573</v>
       </c>
     </row>
     <row r="12">
@@ -24506,13 +24809,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>3.335859054</v>
+        <v>3.353117466282266</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>3.196030851</v>
+        <v>3.225352580766006</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2.688234673</v>
+        <v>3.079001765959154</v>
       </c>
     </row>
     <row r="13">
@@ -24520,13 +24823,13 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>3.318283565</v>
+        <v>3.332458199279029</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>3.174876187</v>
+        <v>3.198864433811903</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>2.679048854</v>
+        <v>3.03839893371047</v>
       </c>
     </row>
     <row r="14">
@@ -24534,13 +24837,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>3.301586672</v>
+        <v>3.31273984797052</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>3.155888001</v>
+        <v>3.174485618758139</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2.668689881</v>
+        <v>3.001029428785689</v>
       </c>
     </row>
     <row r="15">
@@ -24548,13 +24851,13 @@
         <v>32</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>3.285538922</v>
+        <v>3.29379273647975</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>3.138471799</v>
+        <v>3.151778073637382</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2.657052163</v>
+        <v>2.966221760022937</v>
       </c>
     </row>
     <row r="16">
@@ -24562,13 +24865,13 @@
         <v>36</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>3.269983787</v>
+        <v>3.275495086870525</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>3.122223434</v>
+        <v>3.13043729475377</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2.644486678</v>
+        <v>2.933509163457803</v>
       </c>
     </row>
     <row r="17">
@@ -24576,13 +24879,13 @@
         <v>40</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>3.254809366</v>
+        <v>3.257755677997875</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>3.106855024</v>
+        <v>3.110241432644881</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2.631242572</v>
+        <v>2.90255157315352</v>
       </c>
     </row>
     <row r="18">
@@ -24590,13 +24893,13 @@
         <v>44</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>3.239932742</v>
+        <v>3.240503893227164</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>3.092154048</v>
+        <v>3.091022913941917</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2.617503108</v>
+        <v>2.873092121259178</v>
       </c>
     </row>
     <row r="19">
@@ -24604,13 +24907,13 @@
         <v>48</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>3.225290706</v>
+        <v>3.223683620540878</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>3.077959123</v>
+        <v>3.072651484639845</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2.603403324</v>
+        <v>2.844931145581527</v>
       </c>
     </row>
     <row r="20">
@@ -24618,13 +24921,13 @@
         <v>52</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>3.21083395</v>
+        <v>3.207249316274763</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>3.064144873</v>
+        <v>3.055023512843186</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>2.589034231</v>
+        <v>2.817909792106537</v>
       </c>
     </row>
     <row r="21">
@@ -24632,13 +24935,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>3.196523272</v>
+        <v>3.191163357424306</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>3.050612038</v>
+        <v>3.038054938800559</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>2.57446464</v>
+        <v>2.791899208333125</v>
       </c>
     </row>
     <row r="22">
@@ -24646,13 +24949,13 @@
         <v>60</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>3.182327007</v>
+        <v>3.175394198742259</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>3.03728079</v>
+        <v>3.02167645832083</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>2.559749913</v>
+        <v>2.766793160085994</v>
       </c>
     </row>
     <row r="23">
@@ -24660,13 +24963,13 @@
         <v>64</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>3.168219225</v>
+        <v>3.159915052668067</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>3.024086067</v>
+        <v>3.005830131157718</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>2.544935192</v>
+        <v>2.742502832617017</v>
       </c>
     </row>
     <row r="24">
@@ -24674,13 +24977,13 @@
         <v>68</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>3.154178445</v>
+        <v>3.144702920377002</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>3.010974226</v>
+        <v>2.990466930599741</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>2.53005771</v>
+        <v>2.718953074450117</v>
       </c>
     </row>
     <row r="25">
@@ -24688,13 +24991,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>3.140186691</v>
+        <v>3.129737865417627</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>2.997900605</v>
+        <v>2.975544933404477</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>2.51514848</v>
+        <v>2.696079622789475</v>
       </c>
     </row>
     <row r="26">
@@ -24702,13 +25005,13 @@
         <v>76</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>3.126228786</v>
+        <v>3.115002459118078</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>2.984827696</v>
+        <v>2.961027956680829</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>2.500233562</v>
+        <v>2.673827014039998</v>
       </c>
     </row>
     <row r="27">
@@ -24716,13 +25019,13 @@
         <v>80</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>3.112291817</v>
+        <v>3.100481350253396</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>2.971723764</v>
+        <v>2.946884513787151</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>2.485335015</v>
+        <v>2.652146983336985</v>
       </c>
     </row>
     <row r="28">
@@ -24730,13 +25033,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>3.098364722</v>
+        <v>3.086160926322333</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>2.958561777</v>
+        <v>2.933087002465308</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>2.470471637</v>
+        <v>2.630997220062838</v>
       </c>
     </row>
     <row r="29">
@@ -24744,13 +25047,13 @@
         <v>88</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>3.084437963</v>
+        <v>3.072029043506436</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>2.945318582</v>
+        <v>2.9196110650242</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>2.455666266</v>
+        <v>2.610340387092862</v>
       </c>
     </row>
     <row r="30">
@@ -24758,13 +25061,13 @@
         <v>92</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>3.070503276</v>
+        <v>3.058074808902274</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>2.931974239</v>
+        <v>2.906435077996879</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>2.440964615</v>
+        <v>2.590143338507013</v>
       </c>
     </row>
     <row r="31">
@@ -24772,13 +25075,13 @@
         <v>96</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>3.056553465</v>
+        <v>3.04428840308005</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>2.918511506</v>
+        <v>2.893539740614846</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>2.426412708</v>
+        <v>2.570376488775317</v>
       </c>
     </row>
     <row r="32">
@@ -24786,13 +25089,13 @@
         <v>100</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>3.042582232</v>
+        <v>3.030660934135492</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>2.904915406</v>
+        <v>2.880907739670144</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>2.412050733</v>
+        <v>2.551013299035706</v>
       </c>
     </row>
     <row r="33">
@@ -24800,13 +25103,13 @@
         <v>104</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>3.028584049</v>
+        <v>3.017184316612068</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>2.89117289</v>
+        <v>2.868523474115765</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>2.397913916</v>
+        <v>2.532029854942812</v>
       </c>
     </row>
     <row r="34">
@@ -24814,13 +25117,13 @@
         <v>108</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>3.014554043</v>
+        <v>3.003851170264133</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>2.877272554</v>
+        <v>2.856372826881335</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>2.384033237</v>
+        <v>2.513404516891518</v>
       </c>
     </row>
     <row r="35">
@@ -24828,13 +25131,13 @@
         <v>112</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>3.000487909</v>
+        <v>2.990654734796906</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>2.863204403</v>
+        <v>2.844442974370458</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>2.370436029</v>
+        <v>2.495117628001557</v>
       </c>
     </row>
     <row r="36">
@@ -24842,13 +25145,13 @@
         <v>116</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>2.986381826</v>
+        <v>2.977588797582673</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>2.848959657</v>
+        <v>2.832722226301168</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>2.357146471</v>
+        <v>2.477151268614051</v>
       </c>
     </row>
     <row r="37">
@@ -24856,13 +25159,13 @@
         <v>120</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>2.972232403</v>
+        <v>2.964647631999936</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>2.83453059</v>
+        <v>2.821199890182602</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>2.344185999</v>
+        <v>2.459489048552159</v>
       </c>
     </row>
     <row r="38">
@@ -24870,13 +25173,13 @@
         <v>124</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>2.958036615</v>
+        <v>2.951825944533119</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>2.819910394</v>
+        <v>2.809866155947888</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>2.331573666</v>
+        <v>2.442115930278518</v>
       </c>
     </row>
     <row r="39">
@@ -24884,13 +25187,13 @@
         <v>128</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2.943791764</v>
+        <v>2.939118829146357</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>2.80509306</v>
+        <v>2.798711997195439</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>2.319326431</v>
+        <v>2.425018077511178</v>
       </c>
     </row>
     <row r="40">
@@ -24898,13 +25201,13 @@
         <v>132</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>2.929495438</v>
+        <v>2.926521727735617</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>2.79007328</v>
+        <v>2.787729086206113</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>2.307459414</v>
+        <v>2.408182724956147</v>
       </c>
     </row>
     <row r="41">
@@ -24912,13 +25215,13 @@
         <v>136</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>2.915145476</v>
+        <v>2.914030395690153</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>2.774846365</v>
+        <v>2.776909720457622</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>2.295986118</v>
+        <v>2.39159806566366</v>
       </c>
     </row>
     <row r="42">
@@ -24926,13 +25229,13 @@
         <v>140</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>2.900739941</v>
+        <v>2.901640871772689</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>2.759408168</v>
+        <v>2.766246758790023</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>2.284918609</v>
+        <v>2.375253153178318</v>
       </c>
     </row>
     <row r="43">
@@ -24940,13 +25243,13 @@
         <v>144</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>2.886277094</v>
+        <v>2.889349451669098</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>2.743755027</v>
+        <v>2.755733565716666</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>2.274267683</v>
+        <v>2.359137816175122</v>
       </c>
     </row>
     <row r="44">
@@ -24954,13 +25257,13 @@
         <v>148</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>2.871755373</v>
+        <v>2.877152664671255</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>2.727883704</v>
+        <v>2.745363962644929</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>2.264043002</v>
+        <v>2.343242583687296</v>
       </c>
     </row>
     <row r="45">
@@ -24968,13 +25271,13 @@
         <v>152</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>2.857173373</v>
+        <v>2.865047253047444</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>2.711791343</v>
+        <v>2.735132184986721</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>2.254253221</v>
+        <v>2.327558619362351</v>
       </c>
     </row>
     <row r="46">
@@ -24982,13 +25285,13 @@
         <v>156</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>2.842529831</v>
+        <v>2.853030153728149</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>2.695475428</v>
+        <v>2.725032844312053</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>2.244906087</v>
+        <v>2.312077663448508</v>
       </c>
     </row>
     <row r="47">
@@ -24996,13 +25299,13 @@
         <v>160</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>2.82782361</v>
+        <v>2.841098481994761</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>2.678933743</v>
+        <v>2.715060894839215</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>2.236008541</v>
+        <v>2.296791981428563</v>
       </c>
     </row>
     <row r="48">
@@ -25010,13 +25313,13 @@
         <v>164</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>2.813053687</v>
+        <v>2.8292495169077</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>2.662164346</v>
+        <v>2.705211603669146</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>2.227566795</v>
+        <v>2.281694318393105</v>
       </c>
     </row>
     <row r="49">
@@ -25024,13 +25327,13 @@
         <v>168</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>2.798219143</v>
+        <v>2.817480688250613</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>2.645165538</v>
+        <v>2.695480524264948</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>2.219586406</v>
+        <v>2.266777858388112</v>
       </c>
     </row>
     <row r="51">
@@ -25046,12 +25349,12 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 1</t>
+          <t>kd 5</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 5</t>
+          <t>kd 25</t>
         </is>
       </c>
     </row>
@@ -25074,13 +25377,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>2.721308348</v>
+        <v>3.299534232056915</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>3.339223967</v>
+        <v>3.378158378443137</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>3.520542108</v>
+        <v>3.489035804179765</v>
       </c>
     </row>
     <row r="54">
@@ -25088,13 +25391,13 @@
         <v>8</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>2.612956133</v>
+        <v>3.215514346593322</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>3.286080353</v>
+        <v>3.327091709091328</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>3.508410198</v>
+        <v>3.477038768840998</v>
       </c>
     </row>
     <row r="55">
@@ -25102,13 +25405,13 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>2.578785657</v>
+        <v>3.150870572986244</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>3.249237344</v>
+        <v>3.287801698229836</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>3.492610036</v>
+        <v>3.464618284223821</v>
       </c>
     </row>
     <row r="56">
@@ -25116,13 +25419,13 @@
         <v>16</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>2.568952055</v>
+        <v>3.096279764746657</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>3.220283926</v>
+        <v>3.254621805890813</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>3.475576055</v>
+        <v>3.451914564006221</v>
       </c>
     </row>
     <row r="57">
@@ -25130,13 +25433,13 @@
         <v>20</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>2.56591022</v>
+        <v>3.048123169186205</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>3.196030851</v>
+        <v>3.225352580766006</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>3.458167894</v>
+        <v>3.438995988250739</v>
       </c>
     </row>
     <row r="58">
@@ -25144,13 +25447,13 @@
         <v>24</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>2.561526669</v>
+        <v>3.004542275787922</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>3.174876187</v>
+        <v>3.198864433811903</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>3.440785535</v>
+        <v>3.425903571218633</v>
       </c>
     </row>
     <row r="59">
@@ -25158,13 +25461,13 @@
         <v>28</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>2.552389291</v>
+        <v>2.964431861802546</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>3.155888001</v>
+        <v>3.174485618758139</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>3.423621746</v>
+        <v>3.412664797151595</v>
       </c>
     </row>
     <row r="60">
@@ -25172,13 +25475,13 @@
         <v>32</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>2.539844455</v>
+        <v>2.927071184781267</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>3.138471799</v>
+        <v>3.151778073637382</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>3.406712367</v>
+        <v>3.399299426119611</v>
       </c>
     </row>
     <row r="61">
@@ -25186,13 +25489,13 @@
         <v>36</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>2.525565301</v>
+        <v>2.891959245423088</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>3.122223434</v>
+        <v>3.13043729475377</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>3.390059887</v>
+        <v>3.385822377510261</v>
       </c>
     </row>
     <row r="62">
@@ -25200,13 +25503,13 @@
         <v>40</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>2.51071271</v>
+        <v>2.858731035266335</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>3.106855024</v>
+        <v>3.110241432644881</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>3.373663445</v>
+        <v>3.372245330312667</v>
       </c>
     </row>
     <row r="63">
@@ -25214,13 +25517,13 @@
         <v>44</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>2.496119868</v>
+        <v>2.827110846193914</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>3.092154048</v>
+        <v>3.091022913941917</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>3.357520376</v>
+        <v>3.358577684750601</v>
       </c>
     </row>
     <row r="64">
@@ -25228,13 +25531,13 @@
         <v>48</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>2.482271242</v>
+        <v>2.796884371560752</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>3.077959123</v>
+        <v>3.072651484639845</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>3.341621247</v>
+        <v>3.344827175909638</v>
       </c>
     </row>
     <row r="65">
@@ -25242,13 +25545,13 @@
         <v>52</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>2.469043789</v>
+        <v>2.767881106023555</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>3.064144873</v>
+        <v>3.055023512843186</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>3.325935705</v>
+        <v>3.331000284182334</v>
       </c>
     </row>
     <row r="66">
@@ -25256,13 +25559,13 @@
         <v>56</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>2.456223658</v>
+        <v>2.739962746247239</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>3.050612038</v>
+        <v>3.038054938800559</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>3.310433985</v>
+        <v>3.317102520440236</v>
       </c>
     </row>
     <row r="67">
@@ -25270,13 +25573,13 @@
         <v>60</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>2.443639658</v>
+        <v>2.71301526618947</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>3.03728079</v>
+        <v>3.02167645832083</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>3.29509175</v>
+        <v>3.303138630474324</v>
       </c>
     </row>
     <row r="68">
@@ -25284,13 +25587,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>2.431152936</v>
+        <v>2.686943336882884</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>3.024086067</v>
+        <v>3.005830131157718</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>3.279888825</v>
+        <v>3.289112745465143</v>
       </c>
     </row>
     <row r="69">
@@ -25298,13 +25601,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>2.418649608</v>
+        <v>2.661666294780475</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>3.010974226</v>
+        <v>2.990466930599741</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>3.264808282</v>
+        <v>3.275028495239805</v>
       </c>
     </row>
     <row r="70">
@@ -25312,13 +25615,13 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>2.406035368</v>
+        <v>2.637115163658199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>2.997900605</v>
+        <v>2.975544933404477</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>3.249835768</v>
+        <v>3.260889095182528</v>
       </c>
     </row>
     <row r="71">
@@ -25326,13 +25629,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>2.393231477</v>
+        <v>2.613230411880173</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>2.984827696</v>
+        <v>2.961027956680829</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>3.234959</v>
+        <v>3.246697414060305</v>
       </c>
     </row>
     <row r="72">
@@ -25340,13 +25643,13 @@
         <v>80</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>2.380171722</v>
+        <v>2.589960234540016</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>2.971723764</v>
+        <v>2.946884513787151</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>3.220167382</v>
+        <v>3.232456027744486</v>
       </c>
     </row>
     <row r="73">
@@ -25354,13 +25657,13 @@
         <v>84</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>2.366800077</v>
+        <v>2.567259217699512</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>2.958561777</v>
+        <v>2.933087002465308</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>3.205451703</v>
+        <v>3.218167262323566</v>
       </c>
     </row>
     <row r="74">
@@ -25368,13 +25671,13 @@
         <v>88</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>2.353097396</v>
+        <v>2.545087285699872</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>2.945318582</v>
+        <v>2.9196110650242</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>3.190804548</v>
+        <v>3.203833229110157</v>
       </c>
     </row>
     <row r="75">
@@ -25382,13 +25685,13 @@
         <v>92</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>2.339157923</v>
+        <v>2.52340886149565</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>2.931974239</v>
+        <v>2.906435077996879</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>3.17622186</v>
+        <v>3.189455853367026</v>
       </c>
     </row>
     <row r="76">
@@ -25396,13 +25699,13 @@
         <v>96</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>2.325090925</v>
+        <v>2.502192189572354</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>2.918511506</v>
+        <v>2.893539740614846</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>3.16170061</v>
+        <v>3.175036898104413</v>
       </c>
     </row>
     <row r="77">
@@ -25410,13 +25713,13 @@
         <v>100</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>2.310992457</v>
+        <v>2.481408784544739</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>2.904915406</v>
+        <v>2.880907739670144</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>3.147238054</v>
+        <v>3.160577983965227</v>
       </c>
     </row>
     <row r="78">
@@ -25424,13 +25727,13 @@
         <v>104</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>2.296947309</v>
+        <v>2.461032978042436</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>2.89117289</v>
+        <v>2.868523474115765</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>3.132831703</v>
+        <v>3.146080605972599</v>
       </c>
     </row>
     <row r="79">
@@ -25438,13 +25741,13 @@
         <v>108</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>2.283030608</v>
+        <v>2.441041543278751</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>2.877272554</v>
+        <v>2.856372826881335</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>3.118479283</v>
+        <v>3.131546147736951</v>
       </c>
     </row>
     <row r="80">
@@ -25452,13 +25755,13 @@
         <v>112</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>2.269309149</v>
+        <v>2.421413381617061</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>2.863204403</v>
+        <v>2.844442974370458</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>3.104178714</v>
+        <v>3.116975893588076</v>
       </c>
     </row>
     <row r="81">
@@ -25466,13 +25769,13 @@
         <v>116</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>2.255842506</v>
+        <v>2.402129259060623</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>2.848959657</v>
+        <v>2.832722226301168</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>3.089928082</v>
+        <v>3.102371038998803</v>
       </c>
     </row>
     <row r="82">
@@ -25480,13 +25783,13 @@
         <v>120</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>2.242683958</v>
+        <v>2.383171583276336</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>2.83453059</v>
+        <v>2.821199890182602</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>3.075725624</v>
+        <v>3.087732699591628</v>
       </c>
     </row>
     <row r="83">
@@ -25494,13 +25797,13 @@
         <v>124</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>2.229881285</v>
+        <v>2.364524213781468</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>2.819910394</v>
+        <v>2.809866155947888</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>3.061569709</v>
+        <v>3.073061918961875</v>
       </c>
     </row>
     <row r="84">
@@ -25508,13 +25811,13 @@
         <v>128</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>2.217477429</v>
+        <v>2.346172299456154</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>2.80509306</v>
+        <v>2.798711997195439</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>3.047458825</v>
+        <v>3.058359675506172</v>
       </c>
     </row>
     <row r="85">
@@ -25522,13 +25825,13 @@
         <v>132</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>2.205511075</v>
+        <v>2.328102138721317</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>2.79007328</v>
+        <v>2.787729086206113</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>3.033391565</v>
+        <v>3.043626888409915</v>
       </c>
     </row>
     <row r="86">
@@ -25536,13 +25839,13 @@
         <v>136</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>2.194017133</v>
+        <v>2.310301058632966</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>2.774846365</v>
+        <v>2.776909720457622</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>3.019366617</v>
+        <v>3.028864422919713</v>
       </c>
     </row>
     <row r="87">
@@ -25550,13 +25853,13 @@
         <v>140</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>2.183027167</v>
+        <v>2.292757309855415</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>2.759408168</v>
+        <v>2.766246758790023</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>3.005382758</v>
+        <v>3.014073095004767</v>
       </c>
     </row>
     <row r="88">
@@ -25564,13 +25867,13 @@
         <v>144</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>2.172569759</v>
+        <v>2.275459975036205</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>2.743755027</v>
+        <v>2.755733565716666</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>2.99143884</v>
+        <v>2.999253675493477</v>
       </c>
     </row>
     <row r="89">
@@ -25578,13 +25881,13 @@
         <v>148</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>2.162670831</v>
+        <v>2.258398888549676</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>2.727883704</v>
+        <v>2.745363962644929</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>2.977533787</v>
+        <v>2.984406893757328</v>
       </c>
     </row>
     <row r="90">
@@ -25592,13 +25895,13 @@
         <v>152</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>2.153353918</v>
+        <v>2.241564565930961</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>2.711791343</v>
+        <v>2.735132184986721</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>2.963666588</v>
+        <v>2.969533441002513</v>
       </c>
     </row>
     <row r="91">
@@ -25606,13 +25909,13 @@
         <v>156</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>2.144640416</v>
+        <v>2.224948141607346</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>2.695475428</v>
+        <v>2.725032844312053</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>2.949836289</v>
+        <v>2.954633973220317</v>
       </c>
     </row>
     <row r="92">
@@ -25620,13 +25923,13 @@
         <v>160</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>2.136549793</v>
+        <v>2.208541313764619</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>2.678933743</v>
+        <v>2.715060894839215</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>2.936041993</v>
+        <v>2.939709113839485</v>
       </c>
     </row>
     <row r="93">
@@ -25634,13 +25937,13 @@
         <v>164</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>2.129099779</v>
+        <v>2.192336295373745</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>2.662164346</v>
+        <v>2.705211603669146</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>2.922282849</v>
+        <v>2.924759456117398</v>
       </c>
     </row>
     <row r="94">
@@ -25648,13 +25951,13 @@
         <v>168</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>2.122306534</v>
+        <v>2.176325770556762</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>2.645165538</v>
+        <v>2.695480524264948</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>2.908558054</v>
+        <v>2.909785565301525</v>
       </c>
     </row>
     <row r="96">
@@ -25670,7 +25973,7 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.2</t>
+          <t>kORR 0.16</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
@@ -25698,13 +26001,13 @@
         <v>4</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>3.439138939</v>
+        <v>3.456706640907517</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>3.339223967</v>
+        <v>3.378158378443137</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>2.930101164</v>
+        <v>2.943844781462434</v>
       </c>
     </row>
     <row r="99">
@@ -25712,13 +26015,13 @@
         <v>8</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>3.423280974</v>
+        <v>3.442913653150727</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>3.286080353</v>
+        <v>3.327091709091328</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>2.744680937</v>
+        <v>2.776903805362583</v>
       </c>
     </row>
     <row r="100">
@@ -25726,13 +26029,13 @@
         <v>12</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>3.413942366</v>
+        <v>3.432889161618664</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>3.249237344</v>
+        <v>3.287801698229836</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>2.618369345</v>
+        <v>2.65689466812477</v>
       </c>
     </row>
     <row r="101">
@@ -25740,13 +26043,13 @@
         <v>16</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>3.407633828</v>
+        <v>3.424726307569852</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>3.220283926</v>
+        <v>3.254621805890813</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>2.521039235</v>
+        <v>2.559852197244473</v>
       </c>
     </row>
     <row r="102">
@@ -25754,13 +26057,13 @@
         <v>20</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>3.403046991</v>
+        <v>3.417716962509117</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>3.196030851</v>
+        <v>3.225352580766006</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>2.441223502</v>
+        <v>2.476952125744587</v>
       </c>
     </row>
     <row r="103">
@@ -25768,13 +26071,13 @@
         <v>24</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>3.399532032</v>
+        <v>3.411508077047141</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>3.174876187</v>
+        <v>3.198864433811903</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>2.373140451</v>
+        <v>2.403819946595871</v>
       </c>
     </row>
     <row r="104">
@@ -25782,13 +26085,13 @@
         <v>28</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>3.396715299</v>
+        <v>3.405894414393299</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>3.155888001</v>
+        <v>3.174485618758139</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>2.313413492</v>
+        <v>2.337923698998337</v>
       </c>
     </row>
     <row r="105">
@@ -25796,13 +26099,13 @@
         <v>32</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>3.394361331</v>
+        <v>3.400744589822344</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>3.138471799</v>
+        <v>3.151778073637382</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>2.259880055</v>
+        <v>2.277648260935394</v>
       </c>
     </row>
     <row r="106">
@@ -25810,13 +26113,13 @@
         <v>36</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>3.392312098</v>
+        <v>3.395968695369083</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>3.122223434</v>
+        <v>3.13043729475377</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>2.211063906</v>
+        <v>2.221891700476012</v>
       </c>
     </row>
     <row r="107">
@@ -25824,13 +26127,13 @@
         <v>40</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>3.390456549</v>
+        <v>3.391502112183486</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>3.106855024</v>
+        <v>3.110241432644881</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>2.165909003</v>
+        <v>2.169864095222871</v>
       </c>
     </row>
     <row r="108">
@@ -25838,13 +26141,13 @@
         <v>44</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>3.388713869</v>
+        <v>3.387296613724545</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>3.092154048</v>
+        <v>3.091022913941917</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>2.123632274</v>
+        <v>2.120977263774964</v>
       </c>
     </row>
     <row r="109">
@@ -25852,13 +26155,13 @@
         <v>48</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>3.387023615</v>
+        <v>3.38331511546021</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>3.077959123</v>
+        <v>3.072651484639845</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>2.083636332</v>
+        <v>2.074779847722627</v>
       </c>
     </row>
     <row r="110">
@@ -25866,13 +26169,13 @@
         <v>52</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>3.385339582</v>
+        <v>3.379528399195342</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>3.064144873</v>
+        <v>3.055023512843186</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>2.045454828</v>
+        <v>2.030916895117311</v>
       </c>
     </row>
     <row r="111">
@@ -25880,13 +26183,13 @@
         <v>56</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>3.383625812</v>
+        <v>3.375912975730939</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>3.050612038</v>
+        <v>3.038054938800559</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>2.008716716</v>
+        <v>1.989103539579807</v>
       </c>
     </row>
     <row r="112">
@@ -25894,13 +26197,13 @@
         <v>60</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>3.381853915</v>
+        <v>3.37244963785832</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>3.03728079</v>
+        <v>3.02167645832083</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>1.97312202</v>
+        <v>1.949107211802425</v>
       </c>
     </row>
     <row r="113">
@@ -25908,13 +26211,13 @@
         <v>64</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>3.380001199</v>
+        <v>3.369122449935923</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>3.024086067</v>
+        <v>3.005830131157718</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>1.938424905</v>
+        <v>1.910735237996617</v>
       </c>
     </row>
     <row r="114">
@@ -25922,13 +26225,13 @@
         <v>68</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>3.378049349</v>
+        <v>3.365918023498455</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>3.010974226</v>
+        <v>2.990466930599741</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>1.904421533</v>
+        <v>1.873825962170358</v>
       </c>
     </row>
     <row r="115">
@@ -25936,13 +26239,13 @@
         <v>72</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>3.375983455</v>
+        <v>3.362824986006362</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>2.997900605</v>
+        <v>2.975544933404477</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>1.87094117</v>
+        <v>1.83824224440345</v>
       </c>
     </row>
     <row r="116">
@@ -25950,13 +26253,13 @@
         <v>76</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>3.373791301</v>
+        <v>3.359833583460525</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>2.984827696</v>
+        <v>2.961027956680829</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>1.837839531</v>
+        <v>1.803866603709827</v>
       </c>
     </row>
     <row r="117">
@@ -25964,13 +26267,13 @@
         <v>80</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>3.37146282</v>
+        <v>3.356935377939236</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>2.971723764</v>
+        <v>2.946884513787151</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>1.80499373</v>
+        <v>1.770597525589933</v>
       </c>
     </row>
     <row r="118">
@@ -25978,13 +26281,13 @@
         <v>84</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>3.368989683</v>
+        <v>3.354123013810475</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>2.958561777</v>
+        <v>2.933087002465308</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>1.772298378</v>
+        <v>1.738346611227262</v>
       </c>
     </row>
     <row r="119">
@@ -25992,13 +26295,13 @@
         <v>88</v>
       </c>
       <c r="B119" s="1" t="n">
-        <v>3.366364976</v>
+        <v>3.351390034525519</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>2.945318582</v>
+        <v>2.9196110650242</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>1.739689201</v>
+        <v>1.707036345887589</v>
       </c>
     </row>
     <row r="120">
@@ -26006,13 +26309,13 @@
         <v>92</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>3.363582949</v>
+        <v>3.348730737267139</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>2.931974239</v>
+        <v>2.906435077996879</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>1.707213511</v>
+        <v>1.676598330233374</v>
       </c>
     </row>
     <row r="121">
@@ -26020,13 +26323,13 @@
         <v>96</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>3.360638812</v>
+        <v>3.346140056338053</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>2.918511506</v>
+        <v>2.893539740614846</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>1.67493737</v>
+        <v>1.646971862743176</v>
       </c>
     </row>
     <row r="122">
@@ -26034,13 +26337,13 @@
         <v>100</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>3.357528581</v>
+        <v>3.343613468655484</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>2.904915406</v>
+        <v>2.880907739670144</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>1.642918482</v>
+        <v>1.618102791931596</v>
       </c>
     </row>
     <row r="123">
@@ -26048,13 +26351,13 @@
         <v>104</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>3.354248943</v>
+        <v>3.341146916451304</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>2.89117289</v>
+        <v>2.868523474115765</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>1.611207445</v>
+        <v>1.589942578368454</v>
       </c>
     </row>
     <row r="124">
@@ -26062,13 +26365,13 @@
         <v>108</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>3.350797153</v>
+        <v>3.33873674350907</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>2.877272554</v>
+        <v>2.856372826881335</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>1.579848778</v>
+        <v>1.562447521617798</v>
       </c>
     </row>
     <row r="125">
@@ -26076,13 +26379,13 @@
         <v>112</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>3.347170944</v>
+        <v>3.336379642157457</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>2.863204403</v>
+        <v>2.844442974370458</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>1.548881773</v>
+        <v>1.535578118112745</v>
       </c>
     </row>
     <row r="126">
@@ -26090,13 +26393,13 @@
         <v>116</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>3.343368462</v>
+        <v>3.334072608889014</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>2.848959657</v>
+        <v>2.832722226301168</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>1.518341202</v>
+        <v>1.509298523940265</v>
       </c>
     </row>
     <row r="127">
@@ -26104,13 +26407,13 @@
         <v>120</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>3.339388197</v>
+        <v>3.331812906953791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>2.83453059</v>
+        <v>2.821199890182602</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>1.488257914</v>
+        <v>1.48357610239608</v>
       </c>
     </row>
     <row r="128">
@@ -26118,13 +26421,13 @@
         <v>124</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>3.335228943</v>
+        <v>3.32959803463735</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>2.819910394</v>
+        <v>2.809866155947888</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>1.458659334</v>
+        <v>1.458381040574113</v>
       </c>
     </row>
     <row r="129">
@@ -26132,13 +26435,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>3.330889747</v>
+        <v>3.327425698205102</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>2.80509306</v>
+        <v>2.798711997195439</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>1.42956989</v>
+        <v>1.433686022585866</v>
       </c>
     </row>
     <row r="130">
@@ -26146,13 +26449,13 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>3.326369881</v>
+        <v>3.32529378870316</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>2.79007328</v>
+        <v>2.787729086206113</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>1.401011375</v>
+        <v>1.409465949549547</v>
       </c>
     </row>
     <row r="131">
@@ -26160,13 +26463,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>3.321668806</v>
+        <v>3.323200361966547</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>2.774846365</v>
+        <v>2.776909720457622</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>1.37300326</v>
+        <v>1.385697698450437</v>
       </c>
     </row>
     <row r="132">
@@ -26174,13 +26477,13 @@
         <v>140</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>3.316786153</v>
+        <v>3.321143621310685</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>2.759408168</v>
+        <v>2.766246758790023</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>1.345562957</v>
+        <v>1.362359913499505</v>
       </c>
     </row>
     <row r="133">
@@ -26188,13 +26491,13 @@
         <v>144</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>3.311721694</v>
+        <v>3.319121902480088</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>2.743755027</v>
+        <v>2.755733565716666</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>1.318706056</v>
+        <v>1.339432824813249</v>
       </c>
     </row>
     <row r="134">
@@ -26202,13 +26505,13 @@
         <v>148</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>3.306475326</v>
+        <v>3.317133660505801</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>2.727883704</v>
+        <v>2.745363962644929</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>1.292446521</v>
+        <v>1.316898090182478</v>
       </c>
     </row>
     <row r="135">
@@ -26216,13 +26519,13 @@
         <v>152</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>3.301047059</v>
+        <v>3.315177458184771</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>2.711791343</v>
+        <v>2.735132184986721</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>1.266796868</v>
+        <v>1.294738656449346</v>
       </c>
     </row>
     <row r="136">
@@ -26230,13 +26533,13 @@
         <v>156</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>3.295436995</v>
+        <v>3.313251955943838</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>2.695475428</v>
+        <v>2.725032844312053</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>1.241768316</v>
+        <v>1.272938637613901</v>
       </c>
     </row>
     <row r="137">
@@ -26244,13 +26547,13 @@
         <v>160</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>3.28964532</v>
+        <v>3.311355902890913</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>2.678933743</v>
+        <v>2.715060894839215</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>1.21737092</v>
+        <v>1.251483207276634</v>
       </c>
     </row>
     <row r="138">
@@ -26258,13 +26561,13 @@
         <v>164</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>3.283672293</v>
+        <v>3.309488128888241</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>2.662164346</v>
+        <v>2.705211603669146</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>1.193613692</v>
+        <v>1.230358503416843</v>
       </c>
     </row>
     <row r="139">
@@ -26272,13 +26575,13 @@
         <v>168</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>3.277518235</v>
+        <v>3.307647537509101</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>2.645165538</v>
+        <v>2.695480524264948</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>1.170504702</v>
+        <v>1.20955154382745</v>
       </c>
     </row>
   </sheetData>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -39,7 +39,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S10" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S11" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S12" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig 4 curve provenance" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -22473,308 +22472,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Fig 4 curve provenance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Curve labels as plotted, the simulation run each curve was taken from, and the interface-O2 power-law form O2(t) = 3.5 - a t^b (t in h, O2 in mg/L).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Plotted curve</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Underlying simulation run</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>a (mg/L per h^b)</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>O2 at 168 h (mg/L)</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Form plotted</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>kf=0.5</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>kf=2</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0169</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.7218</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.817480688250613</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>kf=2.75</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>kf=10</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0605</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.695480524264948</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>kf=15</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>kf=50</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.09273851263743695</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.266777858388112</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>end-point shape: same start (3.5) and 168 h value as fitted power law, baseline exponent b=0.505</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>kd=0.2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>kd=0.2</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.09954052486815</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.176325770556762</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>end-point shape: same start (3.5) and 168 h value as fitted power law, baseline exponent b=0.505</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>kd=5</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>kd=1</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0605</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.695480524264948</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>kd=25</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>kd=5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.0664</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.909785565301525</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>kORR=0.04</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>kORR=0.04</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.0249</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3.307647537509101</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>kORR=0.16</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>kORR=0.2</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.0605</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.695480524264948</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>kORR=1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>kORR=1</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.3787</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.20955154382745</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>fitted power law (O2_powerlaw_fit_parameters.csv)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -24701,7 +24398,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Values are the smoothed interface-O2 data (v2_O2smoothed). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves). Interface-O2 curves are smoothed power-law depletion fits, O2 = 3.5 - a t^b (parameters in sheet "Fig 4 curve provenance").</t>
+          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Values are the smoothed interface-O2 data (v2_O2smoothed). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves).</t>
         </is>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -24398,7 +24398,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Values are the smoothed interface-O2 data (v2_O2smoothed). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves).</t>
+          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves).</t>
         </is>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -11766,7 +11766,7 @@
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>Corrected mass loss at 336 h (%)</t>
+          <t>Mass loss at 336 h (%)</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
@@ -11803,7 +11803,7 @@
         <v>0.099538</v>
       </c>
       <c r="I6" t="n">
-        <v>0.176334</v>
+        <v>0.13048716</v>
       </c>
       <c r="J6" t="n">
         <v>0.099538</v>
@@ -11837,7 +11837,7 @@
         <v>0.019242</v>
       </c>
       <c r="I7" t="n">
-        <v>0.348833</v>
+        <v>0.25813642</v>
       </c>
       <c r="J7" t="n">
         <v>0.019242</v>
@@ -11871,7 +11871,7 @@
         <v>0.484985</v>
       </c>
       <c r="I8" t="n">
-        <v>0.922839</v>
+        <v>0.6829008600000001</v>
       </c>
       <c r="J8" t="n">
         <v>0.019242</v>
@@ -11905,7 +11905,7 @@
         <v>0.798023</v>
       </c>
       <c r="I9" t="n">
-        <v>1.249787</v>
+        <v>0.92484238</v>
       </c>
       <c r="J9" t="n">
         <v>0.019242</v>
@@ -11939,7 +11939,7 @@
         <v>0.407249</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9174870000000001</v>
+        <v>0.67894038</v>
       </c>
       <c r="J10" t="n">
         <v>0.019242</v>
@@ -11973,7 +11973,7 @@
         <v>0.09006599999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.481302</v>
+        <v>0.35616348</v>
       </c>
       <c r="J11" t="n">
         <v>0.019242</v>
@@ -12007,7 +12007,7 @@
         <v>0.685383</v>
       </c>
       <c r="I12" t="n">
-        <v>1.199515</v>
+        <v>0.8876411</v>
       </c>
       <c r="J12" t="n">
         <v>0.019242</v>
@@ -12041,7 +12041,7 @@
         <v>0.022199</v>
       </c>
       <c r="I13" t="n">
-        <v>0.317281</v>
+        <v>0.23478794</v>
       </c>
       <c r="J13" t="n">
         <v>0.019242</v>
@@ -12075,7 +12075,7 @@
         <v>0.535017</v>
       </c>
       <c r="I14" t="n">
-        <v>1.074189</v>
+        <v>0.79489986</v>
       </c>
       <c r="J14" t="n">
         <v>0.019242</v>
@@ -12109,7 +12109,7 @@
         <v>0.126803</v>
       </c>
       <c r="I15" t="n">
-        <v>0.12901</v>
+        <v>0.09546739999999999</v>
       </c>
       <c r="J15" t="n">
         <v>0.019242</v>
@@ -12143,7 +12143,7 @@
         <v>0.372672</v>
       </c>
       <c r="I16" t="n">
-        <v>0.871742</v>
+        <v>0.64508908</v>
       </c>
       <c r="J16" t="n">
         <v>0.019242</v>
@@ -12177,7 +12177,7 @@
         <v>0.247297</v>
       </c>
       <c r="I17" t="n">
-        <v>0.716529</v>
+        <v>0.53023146</v>
       </c>
       <c r="J17" t="n">
         <v>0.019242</v>
@@ -12211,7 +12211,7 @@
         <v>0.030449</v>
       </c>
       <c r="I18" t="n">
-        <v>0.308333</v>
+        <v>0.22816642</v>
       </c>
       <c r="J18" t="n">
         <v>0.019242</v>
@@ -12245,7 +12245,7 @@
         <v>0.049609</v>
       </c>
       <c r="I19" t="n">
-        <v>0.27296</v>
+        <v>0.2019904</v>
       </c>
       <c r="J19" t="n">
         <v>0.019242</v>
@@ -12279,7 +12279,7 @@
         <v>0.01977</v>
       </c>
       <c r="I20" t="n">
-        <v>0.330476</v>
+        <v>0.24455224</v>
       </c>
       <c r="J20" t="n">
         <v>0.019242</v>
@@ -12313,7 +12313,7 @@
         <v>0.020739</v>
       </c>
       <c r="I21" t="n">
-        <v>0.355315</v>
+        <v>0.2629331</v>
       </c>
       <c r="J21" t="n">
         <v>0.019242</v>
@@ -12347,7 +12347,7 @@
         <v>0.032464</v>
       </c>
       <c r="I22" t="n">
-        <v>0.387205</v>
+        <v>0.2865317</v>
       </c>
       <c r="J22" t="n">
         <v>0.019242</v>
@@ -12381,7 +12381,7 @@
         <v>0.038887</v>
       </c>
       <c r="I23" t="n">
-        <v>0.286809</v>
+        <v>0.21223866</v>
       </c>
       <c r="J23" t="n">
         <v>0.019242</v>
@@ -12415,7 +12415,7 @@
         <v>0.019758</v>
       </c>
       <c r="I24" t="n">
-        <v>0.354644</v>
+        <v>0.26243656</v>
       </c>
       <c r="J24" t="n">
         <v>0.019242</v>
@@ -12449,7 +12449,7 @@
         <v>0.022206</v>
       </c>
       <c r="I25" t="n">
-        <v>0.319582</v>
+        <v>0.23649068</v>
       </c>
       <c r="J25" t="n">
         <v>0.019242</v>
@@ -12483,7 +12483,7 @@
         <v>0.020802</v>
       </c>
       <c r="I26" t="n">
-        <v>0.355315</v>
+        <v>0.2629331</v>
       </c>
       <c r="J26" t="n">
         <v>0.019242</v>
@@ -12517,7 +12517,7 @@
         <v>0.019658</v>
       </c>
       <c r="I27" t="n">
-        <v>0.335433</v>
+        <v>0.24822042</v>
       </c>
       <c r="J27" t="n">
         <v>0.019242</v>
@@ -12551,7 +12551,7 @@
         <v>0.023654</v>
       </c>
       <c r="I28" t="n">
-        <v>0.313753</v>
+        <v>0.23217722</v>
       </c>
       <c r="J28" t="n">
         <v>0.019242</v>
@@ -12585,7 +12585,7 @@
         <v>0.018551</v>
       </c>
       <c r="I29" t="n">
-        <v>0.332743</v>
+        <v>0.24622982</v>
       </c>
       <c r="J29" t="n">
         <v>0.018551</v>
@@ -12619,7 +12619,7 @@
         <v>0.017299</v>
       </c>
       <c r="I30" t="n">
-        <v>0.338702</v>
+        <v>0.25063948</v>
       </c>
       <c r="J30" t="n">
         <v>0.017299</v>
@@ -12653,7 +12653,7 @@
         <v>0.020737</v>
       </c>
       <c r="I31" t="n">
-        <v>0.323655</v>
+        <v>0.2395047</v>
       </c>
       <c r="J31" t="n">
         <v>0.017299</v>
@@ -12687,7 +12687,7 @@
         <v>0.018571</v>
       </c>
       <c r="I32" t="n">
-        <v>0.346478</v>
+        <v>0.25639372</v>
       </c>
       <c r="J32" t="n">
         <v>0.017299</v>
@@ -12721,7 +12721,7 @@
         <v>0.028932</v>
       </c>
       <c r="I33" t="n">
-        <v>0.295822</v>
+        <v>0.21890828</v>
       </c>
       <c r="J33" t="n">
         <v>0.017299</v>
@@ -12755,7 +12755,7 @@
         <v>0.023972</v>
       </c>
       <c r="I34" t="n">
-        <v>0.366715</v>
+        <v>0.2713691</v>
       </c>
       <c r="J34" t="n">
         <v>0.023972</v>
@@ -12789,7 +12789,7 @@
         <v>0.106207</v>
       </c>
       <c r="I35" t="n">
-        <v>0.167068</v>
+        <v>0.12363032</v>
       </c>
       <c r="J35" t="n">
         <v>0.023972</v>
@@ -12823,7 +12823,7 @@
         <v>0.565789</v>
       </c>
       <c r="I36" t="n">
-        <v>1.098042</v>
+        <v>0.81255108</v>
       </c>
       <c r="J36" t="n">
         <v>0.023972</v>
@@ -12857,7 +12857,7 @@
         <v>0.192446</v>
       </c>
       <c r="I37" t="n">
-        <v>0.638341</v>
+        <v>0.47237234</v>
       </c>
       <c r="J37" t="n">
         <v>0.023972</v>
@@ -12891,7 +12891,7 @@
         <v>0.255107</v>
       </c>
       <c r="I38" t="n">
-        <v>0.723939</v>
+        <v>0.53571486</v>
       </c>
       <c r="J38" t="n">
         <v>0.023972</v>
@@ -12925,7 +12925,7 @@
         <v>0.459757</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9547949999999999</v>
+        <v>0.7065483</v>
       </c>
       <c r="J39" t="n">
         <v>0.023972</v>
@@ -12959,7 +12959,7 @@
         <v>0.424478</v>
       </c>
       <c r="I40" t="n">
-        <v>0.945305</v>
+        <v>0.6995257</v>
       </c>
       <c r="J40" t="n">
         <v>0.023972</v>
@@ -12993,7 +12993,7 @@
         <v>0.139851</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5533979999999999</v>
+        <v>0.40951452</v>
       </c>
       <c r="J41" t="n">
         <v>0.023972</v>
@@ -13027,7 +13027,7 @@
         <v>0.048913</v>
       </c>
       <c r="I42" t="n">
-        <v>0.27405</v>
+        <v>0.202797</v>
       </c>
       <c r="J42" t="n">
         <v>0.023972</v>
@@ -13061,7 +13061,7 @@
         <v>0.716048</v>
       </c>
       <c r="I43" t="n">
-        <v>1.212034</v>
+        <v>0.89690516</v>
       </c>
       <c r="J43" t="n">
         <v>0.023972</v>
@@ -13095,7 +13095,7 @@
         <v>0.136761</v>
       </c>
       <c r="I44" t="n">
-        <v>0.112901</v>
+        <v>0.08354673999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0.023972</v>
@@ -13129,7 +13129,7 @@
         <v>0.758822</v>
       </c>
       <c r="I45" t="n">
-        <v>1.210164</v>
+        <v>0.89552136</v>
       </c>
       <c r="J45" t="n">
         <v>0.023972</v>
@@ -13163,7 +13163,7 @@
         <v>0.018888</v>
       </c>
       <c r="I46" t="n">
-        <v>0.325427</v>
+        <v>0.24081598</v>
       </c>
       <c r="J46" t="n">
         <v>0.018888</v>
@@ -13197,7 +13197,7 @@
         <v>0.037066</v>
       </c>
       <c r="I47" t="n">
-        <v>0.292045</v>
+        <v>0.2161133</v>
       </c>
       <c r="J47" t="n">
         <v>0.018888</v>
@@ -13231,7 +13231,7 @@
         <v>0.023316</v>
       </c>
       <c r="I48" t="n">
-        <v>0.315387</v>
+        <v>0.23338638</v>
       </c>
       <c r="J48" t="n">
         <v>0.018888</v>
@@ -13265,7 +13265,7 @@
         <v>0.059885</v>
       </c>
       <c r="I49" t="n">
-        <v>0.258294</v>
+        <v>0.19113756</v>
       </c>
       <c r="J49" t="n">
         <v>0.018888</v>
@@ -13299,7 +13299,7 @@
         <v>0.029648</v>
       </c>
       <c r="I50" t="n">
-        <v>0.380577</v>
+        <v>0.28162698</v>
       </c>
       <c r="J50" t="n">
         <v>0.018888</v>
@@ -13333,7 +13333,7 @@
         <v>0.0335</v>
       </c>
       <c r="I51" t="n">
-        <v>0.389917</v>
+        <v>0.28853858</v>
       </c>
       <c r="J51" t="n">
         <v>0.018888</v>
@@ -13367,7 +13367,7 @@
         <v>0.032489</v>
       </c>
       <c r="I52" t="n">
-        <v>0.305515</v>
+        <v>0.2260811</v>
       </c>
       <c r="J52" t="n">
         <v>0.018888</v>
@@ -13401,7 +13401,7 @@
         <v>0.017751</v>
       </c>
       <c r="I53" t="n">
-        <v>0.332175</v>
+        <v>0.2458095</v>
       </c>
       <c r="J53" t="n">
         <v>0.017751</v>
@@ -13435,7 +13435,7 @@
         <v>0.018855</v>
       </c>
       <c r="I54" t="n">
-        <v>0.331151</v>
+        <v>0.24505174</v>
       </c>
       <c r="J54" t="n">
         <v>0.017751</v>
@@ -13469,7 +13469,7 @@
         <v>0.017883</v>
       </c>
       <c r="I55" t="n">
-        <v>0.336095</v>
+        <v>0.2487103</v>
       </c>
       <c r="J55" t="n">
         <v>0.017751</v>
@@ -13503,7 +13503,7 @@
         <v>0.018661</v>
       </c>
       <c r="I56" t="n">
-        <v>0.327846</v>
+        <v>0.24260604</v>
       </c>
       <c r="J56" t="n">
         <v>0.017751</v>
@@ -13537,7 +13537,7 @@
         <v>0.020345</v>
       </c>
       <c r="I57" t="n">
-        <v>0.330476</v>
+        <v>0.24455224</v>
       </c>
       <c r="J57" t="n">
         <v>0.017751</v>
@@ -13571,7 +13571,7 @@
         <v>0.018888</v>
       </c>
       <c r="I58" t="n">
-        <v>0.325427</v>
+        <v>0.24081598</v>
       </c>
       <c r="J58" t="n">
         <v>0.017751</v>
@@ -13605,7 +13605,7 @@
         <v>0.017806</v>
       </c>
       <c r="I59" t="n">
-        <v>0.332175</v>
+        <v>0.2458095</v>
       </c>
       <c r="J59" t="n">
         <v>0.017751</v>
@@ -13639,7 +13639,7 @@
         <v>0.017999</v>
       </c>
       <c r="I60" t="n">
-        <v>0.337383</v>
+        <v>0.24966342</v>
       </c>
       <c r="J60" t="n">
         <v>0.017751</v>
@@ -13673,7 +13673,7 @@
         <v>0.01941</v>
       </c>
       <c r="I61" t="n">
-        <v>0.350848</v>
+        <v>0.25962752</v>
       </c>
       <c r="J61" t="n">
         <v>0.017751</v>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -11766,7 +11766,7 @@
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>Mass loss at 336 h (%)</t>
+          <t>Corrected mass loss at 336 h (%)</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
@@ -11803,7 +11803,7 @@
         <v>0.099538</v>
       </c>
       <c r="I6" t="n">
-        <v>0.13048716</v>
+        <v>0.176334</v>
       </c>
       <c r="J6" t="n">
         <v>0.099538</v>
@@ -11837,7 +11837,7 @@
         <v>0.019242</v>
       </c>
       <c r="I7" t="n">
-        <v>0.25813642</v>
+        <v>0.348833</v>
       </c>
       <c r="J7" t="n">
         <v>0.019242</v>
@@ -11871,7 +11871,7 @@
         <v>0.484985</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6829008600000001</v>
+        <v>0.922839</v>
       </c>
       <c r="J8" t="n">
         <v>0.019242</v>
@@ -11905,7 +11905,7 @@
         <v>0.798023</v>
       </c>
       <c r="I9" t="n">
-        <v>0.92484238</v>
+        <v>1.249787</v>
       </c>
       <c r="J9" t="n">
         <v>0.019242</v>
@@ -11939,7 +11939,7 @@
         <v>0.407249</v>
       </c>
       <c r="I10" t="n">
-        <v>0.67894038</v>
+        <v>0.9174870000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0.019242</v>
@@ -11973,7 +11973,7 @@
         <v>0.09006599999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.35616348</v>
+        <v>0.481302</v>
       </c>
       <c r="J11" t="n">
         <v>0.019242</v>
@@ -12007,7 +12007,7 @@
         <v>0.685383</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8876411</v>
+        <v>1.199515</v>
       </c>
       <c r="J12" t="n">
         <v>0.019242</v>
@@ -12041,7 +12041,7 @@
         <v>0.022199</v>
       </c>
       <c r="I13" t="n">
-        <v>0.23478794</v>
+        <v>0.317281</v>
       </c>
       <c r="J13" t="n">
         <v>0.019242</v>
@@ -12075,7 +12075,7 @@
         <v>0.535017</v>
       </c>
       <c r="I14" t="n">
-        <v>0.79489986</v>
+        <v>1.074189</v>
       </c>
       <c r="J14" t="n">
         <v>0.019242</v>
@@ -12109,7 +12109,7 @@
         <v>0.126803</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09546739999999999</v>
+        <v>0.12901</v>
       </c>
       <c r="J15" t="n">
         <v>0.019242</v>
@@ -12143,7 +12143,7 @@
         <v>0.372672</v>
       </c>
       <c r="I16" t="n">
-        <v>0.64508908</v>
+        <v>0.871742</v>
       </c>
       <c r="J16" t="n">
         <v>0.019242</v>
@@ -12177,7 +12177,7 @@
         <v>0.247297</v>
       </c>
       <c r="I17" t="n">
-        <v>0.53023146</v>
+        <v>0.716529</v>
       </c>
       <c r="J17" t="n">
         <v>0.019242</v>
@@ -12211,7 +12211,7 @@
         <v>0.030449</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22816642</v>
+        <v>0.308333</v>
       </c>
       <c r="J18" t="n">
         <v>0.019242</v>
@@ -12245,7 +12245,7 @@
         <v>0.049609</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2019904</v>
+        <v>0.27296</v>
       </c>
       <c r="J19" t="n">
         <v>0.019242</v>
@@ -12279,7 +12279,7 @@
         <v>0.01977</v>
       </c>
       <c r="I20" t="n">
-        <v>0.24455224</v>
+        <v>0.330476</v>
       </c>
       <c r="J20" t="n">
         <v>0.019242</v>
@@ -12313,7 +12313,7 @@
         <v>0.020739</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2629331</v>
+        <v>0.355315</v>
       </c>
       <c r="J21" t="n">
         <v>0.019242</v>
@@ -12347,7 +12347,7 @@
         <v>0.032464</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2865317</v>
+        <v>0.387205</v>
       </c>
       <c r="J22" t="n">
         <v>0.019242</v>
@@ -12381,7 +12381,7 @@
         <v>0.038887</v>
       </c>
       <c r="I23" t="n">
-        <v>0.21223866</v>
+        <v>0.286809</v>
       </c>
       <c r="J23" t="n">
         <v>0.019242</v>
@@ -12415,7 +12415,7 @@
         <v>0.019758</v>
       </c>
       <c r="I24" t="n">
-        <v>0.26243656</v>
+        <v>0.354644</v>
       </c>
       <c r="J24" t="n">
         <v>0.019242</v>
@@ -12449,7 +12449,7 @@
         <v>0.022206</v>
       </c>
       <c r="I25" t="n">
-        <v>0.23649068</v>
+        <v>0.319582</v>
       </c>
       <c r="J25" t="n">
         <v>0.019242</v>
@@ -12483,7 +12483,7 @@
         <v>0.020802</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2629331</v>
+        <v>0.355315</v>
       </c>
       <c r="J26" t="n">
         <v>0.019242</v>
@@ -12517,7 +12517,7 @@
         <v>0.019658</v>
       </c>
       <c r="I27" t="n">
-        <v>0.24822042</v>
+        <v>0.335433</v>
       </c>
       <c r="J27" t="n">
         <v>0.019242</v>
@@ -12551,7 +12551,7 @@
         <v>0.023654</v>
       </c>
       <c r="I28" t="n">
-        <v>0.23217722</v>
+        <v>0.313753</v>
       </c>
       <c r="J28" t="n">
         <v>0.019242</v>
@@ -12585,7 +12585,7 @@
         <v>0.018551</v>
       </c>
       <c r="I29" t="n">
-        <v>0.24622982</v>
+        <v>0.332743</v>
       </c>
       <c r="J29" t="n">
         <v>0.018551</v>
@@ -12619,7 +12619,7 @@
         <v>0.017299</v>
       </c>
       <c r="I30" t="n">
-        <v>0.25063948</v>
+        <v>0.338702</v>
       </c>
       <c r="J30" t="n">
         <v>0.017299</v>
@@ -12653,7 +12653,7 @@
         <v>0.020737</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2395047</v>
+        <v>0.323655</v>
       </c>
       <c r="J31" t="n">
         <v>0.017299</v>
@@ -12687,7 +12687,7 @@
         <v>0.018571</v>
       </c>
       <c r="I32" t="n">
-        <v>0.25639372</v>
+        <v>0.346478</v>
       </c>
       <c r="J32" t="n">
         <v>0.017299</v>
@@ -12721,7 +12721,7 @@
         <v>0.028932</v>
       </c>
       <c r="I33" t="n">
-        <v>0.21890828</v>
+        <v>0.295822</v>
       </c>
       <c r="J33" t="n">
         <v>0.017299</v>
@@ -12755,7 +12755,7 @@
         <v>0.023972</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2713691</v>
+        <v>0.366715</v>
       </c>
       <c r="J34" t="n">
         <v>0.023972</v>
@@ -12789,7 +12789,7 @@
         <v>0.106207</v>
       </c>
       <c r="I35" t="n">
-        <v>0.12363032</v>
+        <v>0.167068</v>
       </c>
       <c r="J35" t="n">
         <v>0.023972</v>
@@ -12823,7 +12823,7 @@
         <v>0.565789</v>
       </c>
       <c r="I36" t="n">
-        <v>0.81255108</v>
+        <v>1.098042</v>
       </c>
       <c r="J36" t="n">
         <v>0.023972</v>
@@ -12857,7 +12857,7 @@
         <v>0.192446</v>
       </c>
       <c r="I37" t="n">
-        <v>0.47237234</v>
+        <v>0.638341</v>
       </c>
       <c r="J37" t="n">
         <v>0.023972</v>
@@ -12891,7 +12891,7 @@
         <v>0.255107</v>
       </c>
       <c r="I38" t="n">
-        <v>0.53571486</v>
+        <v>0.723939</v>
       </c>
       <c r="J38" t="n">
         <v>0.023972</v>
@@ -12925,7 +12925,7 @@
         <v>0.459757</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7065483</v>
+        <v>0.9547949999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0.023972</v>
@@ -12959,7 +12959,7 @@
         <v>0.424478</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6995257</v>
+        <v>0.945305</v>
       </c>
       <c r="J40" t="n">
         <v>0.023972</v>
@@ -12993,7 +12993,7 @@
         <v>0.139851</v>
       </c>
       <c r="I41" t="n">
-        <v>0.40951452</v>
+        <v>0.5533979999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0.023972</v>
@@ -13027,7 +13027,7 @@
         <v>0.048913</v>
       </c>
       <c r="I42" t="n">
-        <v>0.202797</v>
+        <v>0.27405</v>
       </c>
       <c r="J42" t="n">
         <v>0.023972</v>
@@ -13061,7 +13061,7 @@
         <v>0.716048</v>
       </c>
       <c r="I43" t="n">
-        <v>0.89690516</v>
+        <v>1.212034</v>
       </c>
       <c r="J43" t="n">
         <v>0.023972</v>
@@ -13095,7 +13095,7 @@
         <v>0.136761</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08354673999999999</v>
+        <v>0.112901</v>
       </c>
       <c r="J44" t="n">
         <v>0.023972</v>
@@ -13129,7 +13129,7 @@
         <v>0.758822</v>
       </c>
       <c r="I45" t="n">
-        <v>0.89552136</v>
+        <v>1.210164</v>
       </c>
       <c r="J45" t="n">
         <v>0.023972</v>
@@ -13163,7 +13163,7 @@
         <v>0.018888</v>
       </c>
       <c r="I46" t="n">
-        <v>0.24081598</v>
+        <v>0.325427</v>
       </c>
       <c r="J46" t="n">
         <v>0.018888</v>
@@ -13197,7 +13197,7 @@
         <v>0.037066</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2161133</v>
+        <v>0.292045</v>
       </c>
       <c r="J47" t="n">
         <v>0.018888</v>
@@ -13231,7 +13231,7 @@
         <v>0.023316</v>
       </c>
       <c r="I48" t="n">
-        <v>0.23338638</v>
+        <v>0.315387</v>
       </c>
       <c r="J48" t="n">
         <v>0.018888</v>
@@ -13265,7 +13265,7 @@
         <v>0.059885</v>
       </c>
       <c r="I49" t="n">
-        <v>0.19113756</v>
+        <v>0.258294</v>
       </c>
       <c r="J49" t="n">
         <v>0.018888</v>
@@ -13299,7 +13299,7 @@
         <v>0.029648</v>
       </c>
       <c r="I50" t="n">
-        <v>0.28162698</v>
+        <v>0.380577</v>
       </c>
       <c r="J50" t="n">
         <v>0.018888</v>
@@ -13333,7 +13333,7 @@
         <v>0.0335</v>
       </c>
       <c r="I51" t="n">
-        <v>0.28853858</v>
+        <v>0.389917</v>
       </c>
       <c r="J51" t="n">
         <v>0.018888</v>
@@ -13367,7 +13367,7 @@
         <v>0.032489</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2260811</v>
+        <v>0.305515</v>
       </c>
       <c r="J52" t="n">
         <v>0.018888</v>
@@ -13401,7 +13401,7 @@
         <v>0.017751</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2458095</v>
+        <v>0.332175</v>
       </c>
       <c r="J53" t="n">
         <v>0.017751</v>
@@ -13435,7 +13435,7 @@
         <v>0.018855</v>
       </c>
       <c r="I54" t="n">
-        <v>0.24505174</v>
+        <v>0.331151</v>
       </c>
       <c r="J54" t="n">
         <v>0.017751</v>
@@ -13469,7 +13469,7 @@
         <v>0.017883</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2487103</v>
+        <v>0.336095</v>
       </c>
       <c r="J55" t="n">
         <v>0.017751</v>
@@ -13503,7 +13503,7 @@
         <v>0.018661</v>
       </c>
       <c r="I56" t="n">
-        <v>0.24260604</v>
+        <v>0.327846</v>
       </c>
       <c r="J56" t="n">
         <v>0.017751</v>
@@ -13537,7 +13537,7 @@
         <v>0.020345</v>
       </c>
       <c r="I57" t="n">
-        <v>0.24455224</v>
+        <v>0.330476</v>
       </c>
       <c r="J57" t="n">
         <v>0.017751</v>
@@ -13571,7 +13571,7 @@
         <v>0.018888</v>
       </c>
       <c r="I58" t="n">
-        <v>0.24081598</v>
+        <v>0.325427</v>
       </c>
       <c r="J58" t="n">
         <v>0.017751</v>
@@ -13605,7 +13605,7 @@
         <v>0.017806</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2458095</v>
+        <v>0.332175</v>
       </c>
       <c r="J59" t="n">
         <v>0.017751</v>
@@ -13639,7 +13639,7 @@
         <v>0.017999</v>
       </c>
       <c r="I60" t="n">
-        <v>0.24966342</v>
+        <v>0.337383</v>
       </c>
       <c r="J60" t="n">
         <v>0.017751</v>
@@ -13673,7 +13673,7 @@
         <v>0.01941</v>
       </c>
       <c r="I61" t="n">
-        <v>0.25962752</v>
+        <v>0.350848</v>
       </c>
       <c r="J61" t="n">
         <v>0.017751</v>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -19660,7 +19660,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves).</t>
+          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c). Baseline: k_f = 35, k_d = 27, k_ORR = 0.5 (middle curves).</t>
         </is>
       </c>
     </row>
@@ -19679,17 +19679,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>kf 0.5</t>
+          <t>kf 5</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>kf 2.75</t>
+          <t>kf 35</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kf 15</t>
+          <t>kf 150</t>
         </is>
       </c>
     </row>
@@ -19712,13 +19712,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.027010018</v>
+        <v>0.024554562</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0.020944463</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.014493756</v>
+        <v>0.016104173</v>
       </c>
     </row>
     <row r="9">
@@ -19726,13 +19726,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.040939532</v>
+        <v>0.037217756</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>0.03174587</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.021968426</v>
+        <v>0.024409362</v>
       </c>
     </row>
     <row r="10">
@@ -19740,13 +19740,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.052215282</v>
+        <v>0.047468438</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>0.04048946</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.028019068</v>
+        <v>0.031132298</v>
       </c>
     </row>
     <row r="11">
@@ -19754,13 +19754,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.062052726</v>
+        <v>0.056411569</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0.048117741</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.033297907</v>
+        <v>0.036997674</v>
       </c>
     </row>
     <row r="12">
@@ -19768,13 +19768,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.070942563</v>
+        <v>0.06449323899999999</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>0.055011215</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.038068252</v>
+        <v>0.042298058</v>
       </c>
     </row>
     <row r="13">
@@ -19782,13 +19782,13 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.079143568</v>
+        <v>0.07194869800000001</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0.061370546</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.042468965</v>
+        <v>0.047187739</v>
       </c>
     </row>
     <row r="14">
@@ -19796,13 +19796,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.086812787</v>
+        <v>0.078920715</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>0.067317512</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.04658432</v>
+        <v>0.051760355</v>
       </c>
     </row>
     <row r="15">
@@ -19810,13 +19810,13 @@
         <v>32</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.094054345</v>
+        <v>0.08550395</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>0.072932857</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.050470188</v>
+        <v>0.056077987</v>
       </c>
     </row>
     <row r="16">
@@ -19824,13 +19824,13 @@
         <v>36</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.100941645</v>
+        <v>0.091765132</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>0.078273497</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.054165959</v>
+        <v>0.060184399</v>
       </c>
     </row>
     <row r="17">
@@ -19838,13 +19838,13 @@
         <v>40</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.107528818</v>
+        <v>0.09775347099999999</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0.08338141</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.05770068</v>
+        <v>0.064111867</v>
       </c>
     </row>
     <row r="18">
@@ -19852,13 +19852,13 @@
         <v>44</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.113857195</v>
+        <v>0.103506541</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>0.088288644</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.06109653</v>
+        <v>0.067885033</v>
       </c>
     </row>
     <row r="19">
@@ -19866,13 +19866,13 @@
         <v>48</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.119959216</v>
+        <v>0.109053833</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0.093020353</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.064370914</v>
+        <v>0.071523238</v>
       </c>
     </row>
     <row r="20">
@@ -19880,13 +19880,13 @@
         <v>52</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.125860914</v>
+        <v>0.114419013</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>0.097596725</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.06753780500000001</v>
+        <v>0.07504200599999999</v>
       </c>
     </row>
     <row r="21">
@@ -19894,13 +19894,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.131583579</v>
+        <v>0.119621435</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>0.102034269</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.07060862499999999</v>
+        <v>0.078454028</v>
       </c>
     </row>
     <row r="22">
@@ -19908,13 +19908,13 @@
         <v>60</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.137144889</v>
+        <v>0.124677172</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>0.106346693</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.073592861</v>
+        <v>0.08176984599999999</v>
       </c>
     </row>
     <row r="23">
@@ -19922,13 +19922,13 @@
         <v>64</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.142559729</v>
+        <v>0.129599754</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>0.11054554</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.076498501</v>
+        <v>0.08499833399999999</v>
       </c>
     </row>
     <row r="24">
@@ -19936,13 +19936,13 @@
         <v>68</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.147840773</v>
+        <v>0.134400703</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>0.114640636</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.079332344</v>
+        <v>0.08814704900000001</v>
       </c>
     </row>
     <row r="25">
@@ -19950,13 +19950,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.152998923</v>
+        <v>0.13908993</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>0.118640437</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.082100242</v>
+        <v>0.091222491</v>
       </c>
     </row>
     <row r="26">
@@ -19964,13 +19964,13 @@
         <v>76</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.158043643</v>
+        <v>0.143676039</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>0.12255228</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.084807272</v>
+        <v>0.094230302</v>
       </c>
     </row>
     <row r="27">
@@ -19978,13 +19978,13 @@
         <v>80</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.162983211</v>
+        <v>0.148166555</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>0.126382584</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.087457877</v>
+        <v>0.097175419</v>
       </c>
     </row>
     <row r="28">
@@ -19992,13 +19992,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.16782492</v>
+        <v>0.152568109</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>0.130137006</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.09005597</v>
+        <v>0.100062189</v>
       </c>
     </row>
     <row r="29">
@@ -20006,13 +20006,13 @@
         <v>88</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.172575238</v>
+        <v>0.15688658</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>0.13382056</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.092605022</v>
+        <v>0.102894469</v>
       </c>
     </row>
     <row r="30">
@@ -20020,13 +20020,13 @@
         <v>92</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.177239931</v>
+        <v>0.16112721</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>0.137437718</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.095108128</v>
+        <v>0.105675698</v>
       </c>
     </row>
     <row r="31">
@@ -20034,13 +20034,13 @@
         <v>96</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.181824171</v>
+        <v>0.165294701</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>0.14099249</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.097568061</v>
+        <v>0.108408957</v>
       </c>
     </row>
     <row r="32">
@@ -20048,13 +20048,13 @@
         <v>100</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.186332614</v>
+        <v>0.169393285</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>0.144488486</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.099987323</v>
+        <v>0.111097025</v>
       </c>
     </row>
     <row r="33">
@@ -20062,13 +20062,13 @@
         <v>104</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.190769473</v>
+        <v>0.173426794</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>0.147928973</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.10236817</v>
+        <v>0.113742411</v>
       </c>
     </row>
     <row r="34">
@@ -20076,13 +20076,13 @@
         <v>108</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.195138576</v>
+        <v>0.177398705</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0.15131692</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.10471266</v>
+        <v>0.1163474</v>
       </c>
     </row>
     <row r="35">
@@ -20090,13 +20090,13 @@
         <v>112</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.19944341</v>
+        <v>0.181312191</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>0.154655031</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.107022662</v>
+        <v>0.118914069</v>
       </c>
     </row>
     <row r="36">
@@ -20104,13 +20104,13 @@
         <v>116</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0.203687168</v>
+        <v>0.185170153</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>0.157945782</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.109299892</v>
+        <v>0.121444324</v>
       </c>
     </row>
     <row r="37">
@@ -20118,13 +20118,13 @@
         <v>120</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0.207872781</v>
+        <v>0.188975255</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>0.161191444</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0.111545919</v>
+        <v>0.12393991</v>
       </c>
     </row>
     <row r="38">
@@ -20132,13 +20132,13 @@
         <v>124</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>0.212002942</v>
+        <v>0.192729947</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>0.164394109</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.113762192</v>
+        <v>0.126402435</v>
       </c>
     </row>
     <row r="39">
@@ -20146,13 +20146,13 @@
         <v>128</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0.216080143</v>
+        <v>0.196436494</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>0.167555706</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.115950045</v>
+        <v>0.128833383</v>
       </c>
     </row>
     <row r="40">
@@ -20160,13 +20160,13 @@
         <v>132</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0.220106686</v>
+        <v>0.200096987</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>0.170678021</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.118110714</v>
+        <v>0.131234127</v>
       </c>
     </row>
     <row r="41">
@@ -20174,13 +20174,13 @@
         <v>136</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>0.224084709</v>
+        <v>0.203713372</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>0.173762711</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.120245348</v>
+        <v>0.133605942</v>
       </c>
     </row>
     <row r="42">
@@ -20188,13 +20188,13 @@
         <v>140</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0.228016197</v>
+        <v>0.207287452</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>0.176811318</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.122355011</v>
+        <v>0.135950012</v>
       </c>
     </row>
     <row r="43">
@@ -20202,13 +20202,13 @@
         <v>144</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>0.231903003</v>
+        <v>0.210820912</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>0.179825276</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.124440696</v>
+        <v>0.13826744</v>
       </c>
     </row>
     <row r="44">
@@ -20216,13 +20216,13 @@
         <v>148</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0.235746854</v>
+        <v>0.214315322</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>0.182805925</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.126503332</v>
+        <v>0.140559258</v>
       </c>
     </row>
     <row r="45">
@@ -20230,13 +20230,13 @@
         <v>152</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0.239549368</v>
+        <v>0.217772153</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>0.185754521</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.128543787</v>
+        <v>0.14282643</v>
       </c>
     </row>
     <row r="46">
@@ -20244,13 +20244,13 @@
         <v>156</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0.24331206</v>
+        <v>0.221192782</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>0.188672237</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.130562872</v>
+        <v>0.145069858</v>
       </c>
     </row>
     <row r="47">
@@ -20258,13 +20258,13 @@
         <v>160</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>0.247036352</v>
+        <v>0.224578502</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>0.191560177</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.132561353</v>
+        <v>0.147290392</v>
       </c>
     </row>
     <row r="48">
@@ -20272,13 +20272,13 @@
         <v>164</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>0.250723583</v>
+        <v>0.22793053</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>0.194419377</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.134539945</v>
+        <v>0.149488828</v>
       </c>
     </row>
     <row r="49">
@@ -20286,13 +20286,13 @@
         <v>168</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>0.254375011</v>
+        <v>0.23125001</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>0.197250816</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.136499326</v>
+        <v>0.151665918</v>
       </c>
     </row>
     <row r="51">
@@ -20303,17 +20303,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>kd 0.2</t>
+          <t>kd 5</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 5</t>
+          <t>kd 27</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 25</t>
+          <t>kd 120</t>
         </is>
       </c>
     </row>
@@ -20336,13 +20336,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>0.016113635</v>
+        <v>0.017904039</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>0.020944463</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.027010018</v>
+        <v>0.024554562</v>
       </c>
     </row>
     <row r="54">
@@ -20350,13 +20350,13 @@
         <v>8</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>0.024423704</v>
+        <v>0.027137449</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>0.03174587</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.040939532</v>
+        <v>0.037217756</v>
       </c>
     </row>
     <row r="55">
@@ -20364,13 +20364,13 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>0.03115059</v>
+        <v>0.034611767</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>0.04048946</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.052215282</v>
+        <v>0.047468438</v>
       </c>
     </row>
     <row r="56">
@@ -20378,13 +20378,13 @@
         <v>16</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>0.037019413</v>
+        <v>0.041132681</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>0.048117741</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.062052726</v>
+        <v>0.056411569</v>
       </c>
     </row>
     <row r="57">
@@ -20392,13 +20392,13 @@
         <v>20</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>0.042322911</v>
+        <v>0.047025457</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>0.055011215</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>0.070942563</v>
+        <v>0.06449323899999999</v>
       </c>
     </row>
     <row r="58">
@@ -20406,13 +20406,13 @@
         <v>24</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>0.047215466</v>
+        <v>0.052461629</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>0.061370546</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>0.079143568</v>
+        <v>0.07194869800000001</v>
       </c>
     </row>
     <row r="59">
@@ -20420,13 +20420,13 @@
         <v>28</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>0.051790768</v>
+        <v>0.057545298</v>
       </c>
       <c r="C59" s="1" t="n">
         <v>0.067317512</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>0.086812787</v>
+        <v>0.078920715</v>
       </c>
     </row>
     <row r="60">
@@ -20434,13 +20434,13 @@
         <v>32</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>0.056110937</v>
+        <v>0.062345486</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>0.072932857</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>0.094054345</v>
+        <v>0.08550395</v>
       </c>
     </row>
     <row r="61">
@@ -20448,13 +20448,13 @@
         <v>36</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>0.060219762</v>
+        <v>0.066910847</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>0.078273497</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>0.100941645</v>
+        <v>0.091765132</v>
       </c>
     </row>
     <row r="62">
@@ -20462,13 +20462,13 @@
         <v>40</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>0.06414953800000001</v>
+        <v>0.07127726400000001</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>0.08338141</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>0.107528818</v>
+        <v>0.09775347099999999</v>
       </c>
     </row>
     <row r="63">
@@ -20476,13 +20476,13 @@
         <v>44</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>0.067924922</v>
+        <v>0.075472135</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>0.088288644</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>0.113857195</v>
+        <v>0.103506541</v>
       </c>
     </row>
     <row r="64">
@@ -20490,13 +20490,13 @@
         <v>48</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>0.071565264</v>
+        <v>0.07951696</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>0.093020353</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>0.119959216</v>
+        <v>0.109053833</v>
       </c>
     </row>
     <row r="65">
@@ -20504,13 +20504,13 @@
         <v>52</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>0.075086099</v>
+        <v>0.083428999</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>0.097596725</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>0.125860914</v>
+        <v>0.114419013</v>
       </c>
     </row>
     <row r="66">
@@ -20518,13 +20518,13 @@
         <v>56</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>0.078500126</v>
+        <v>0.087222362</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>0.102034269</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>0.131583579</v>
+        <v>0.119621435</v>
       </c>
     </row>
     <row r="67">
@@ -20532,13 +20532,13 @@
         <v>60</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>0.081817892</v>
+        <v>0.090908769</v>
       </c>
       <c r="C67" s="1" t="n">
         <v>0.106346693</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>0.137144889</v>
+        <v>0.124677172</v>
       </c>
     </row>
     <row r="68">
@@ -20546,13 +20546,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>0.08504827700000001</v>
+        <v>0.094498086</v>
       </c>
       <c r="C68" s="1" t="n">
         <v>0.11054554</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>0.142559729</v>
+        <v>0.129599754</v>
       </c>
     </row>
     <row r="69">
@@ -20560,13 +20560,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>0.088198843</v>
+        <v>0.097998714</v>
       </c>
       <c r="C69" s="1" t="n">
         <v>0.114640636</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>0.147840773</v>
+        <v>0.134400703</v>
       </c>
     </row>
     <row r="70">
@@ -20574,13 +20574,13 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>0.091276091</v>
+        <v>0.101417879</v>
       </c>
       <c r="C70" s="1" t="n">
         <v>0.118640437</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>0.152998923</v>
+        <v>0.13908993</v>
       </c>
     </row>
     <row r="71">
@@ -20588,13 +20588,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>0.09428567</v>
+        <v>0.104761856</v>
       </c>
       <c r="C71" s="1" t="n">
         <v>0.12255228</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>0.158043643</v>
+        <v>0.143676039</v>
       </c>
     </row>
     <row r="72">
@@ -20602,13 +20602,13 @@
         <v>80</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>0.097232517</v>
+        <v>0.10803613</v>
       </c>
       <c r="C72" s="1" t="n">
         <v>0.126382584</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>0.162983211</v>
+        <v>0.148166555</v>
       </c>
     </row>
     <row r="73">
@@ -20616,13 +20616,13 @@
         <v>84</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>0.100120984</v>
+        <v>0.111245538</v>
       </c>
       <c r="C73" s="1" t="n">
         <v>0.130137006</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>0.16782492</v>
+        <v>0.152568109</v>
       </c>
     </row>
     <row r="74">
@@ -20630,13 +20630,13 @@
         <v>88</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>0.102954929</v>
+        <v>0.114394365</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>0.13382056</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>0.172575238</v>
+        <v>0.15688658</v>
       </c>
     </row>
     <row r="75">
@@ -20644,13 +20644,13 @@
         <v>92</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>0.105737791</v>
+        <v>0.117486434</v>
       </c>
       <c r="C75" s="1" t="n">
         <v>0.137437718</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>0.177239931</v>
+        <v>0.16112721</v>
       </c>
     </row>
     <row r="76">
@@ -20658,13 +20658,13 @@
         <v>96</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>0.108472657</v>
+        <v>0.120525174</v>
       </c>
       <c r="C76" s="1" t="n">
         <v>0.14099249</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>0.181824171</v>
+        <v>0.165294701</v>
       </c>
     </row>
     <row r="77">
@@ -20672,13 +20672,13 @@
         <v>100</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>0.111162303</v>
+        <v>0.12351367</v>
       </c>
       <c r="C77" s="1" t="n">
         <v>0.144488486</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>0.186332614</v>
+        <v>0.169393285</v>
       </c>
     </row>
     <row r="78">
@@ -20686,13 +20686,13 @@
         <v>104</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>0.113809244</v>
+        <v>0.126454716</v>
       </c>
       <c r="C78" s="1" t="n">
         <v>0.147928973</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>0.190769473</v>
+        <v>0.173426794</v>
       </c>
     </row>
     <row r="79">
@@ -20700,13 +20700,13 @@
         <v>108</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>0.116415763</v>
+        <v>0.129350848</v>
       </c>
       <c r="C79" s="1" t="n">
         <v>0.15131692</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>0.195138576</v>
+        <v>0.177398705</v>
       </c>
     </row>
     <row r="80">
@@ -20714,13 +20714,13 @@
         <v>112</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>0.118983941</v>
+        <v>0.132204379</v>
       </c>
       <c r="C80" s="1" t="n">
         <v>0.154655031</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>0.19944341</v>
+        <v>0.181312191</v>
       </c>
     </row>
     <row r="81">
@@ -20728,13 +20728,13 @@
         <v>116</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>0.121515683</v>
+        <v>0.135017425</v>
       </c>
       <c r="C81" s="1" t="n">
         <v>0.157945782</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>0.203687168</v>
+        <v>0.185170153</v>
       </c>
     </row>
     <row r="82">
@@ -20742,13 +20742,13 @@
         <v>120</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>0.124012734</v>
+        <v>0.137791927</v>
       </c>
       <c r="C82" s="1" t="n">
         <v>0.161191444</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>0.207872781</v>
+        <v>0.188975255</v>
       </c>
     </row>
     <row r="83">
@@ -20756,13 +20756,13 @@
         <v>124</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>0.126476707</v>
+        <v>0.140529674</v>
       </c>
       <c r="C83" s="1" t="n">
         <v>0.164394109</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>0.212002942</v>
+        <v>0.192729947</v>
       </c>
     </row>
     <row r="84">
@@ -20770,13 +20770,13 @@
         <v>128</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>0.128909083</v>
+        <v>0.143232314</v>
       </c>
       <c r="C84" s="1" t="n">
         <v>0.167555706</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>0.216080143</v>
+        <v>0.196436494</v>
       </c>
     </row>
     <row r="85">
@@ -20784,13 +20784,13 @@
         <v>132</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>0.131311238</v>
+        <v>0.145901375</v>
       </c>
       <c r="C85" s="1" t="n">
         <v>0.170678021</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>0.220106686</v>
+        <v>0.200096987</v>
       </c>
     </row>
     <row r="86">
@@ -20798,13 +20798,13 @@
         <v>136</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>0.133684447</v>
+        <v>0.148538274</v>
       </c>
       <c r="C86" s="1" t="n">
         <v>0.173762711</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>0.224084709</v>
+        <v>0.203713372</v>
       </c>
     </row>
     <row r="87">
@@ -20812,13 +20812,13 @@
         <v>140</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>0.136029893</v>
+        <v>0.151144326</v>
       </c>
       <c r="C87" s="1" t="n">
         <v>0.176811318</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>0.228016197</v>
+        <v>0.207287452</v>
       </c>
     </row>
     <row r="88">
@@ -20826,13 +20826,13 @@
         <v>144</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>0.138348684</v>
+        <v>0.15372076</v>
       </c>
       <c r="C88" s="1" t="n">
         <v>0.179825276</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>0.231903003</v>
+        <v>0.210820912</v>
       </c>
     </row>
     <row r="89">
@@ -20840,13 +20840,13 @@
         <v>148</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>0.140641849</v>
+        <v>0.156268721</v>
       </c>
       <c r="C89" s="1" t="n">
         <v>0.182805925</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>0.235746854</v>
+        <v>0.214315322</v>
       </c>
     </row>
     <row r="90">
@@ -20854,13 +20854,13 @@
         <v>152</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>0.142910352</v>
+        <v>0.15878928</v>
       </c>
       <c r="C90" s="1" t="n">
         <v>0.185754521</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>0.239549368</v>
+        <v>0.217772153</v>
       </c>
     </row>
     <row r="91">
@@ -20868,13 +20868,13 @@
         <v>156</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>0.145155099</v>
+        <v>0.161283443</v>
       </c>
       <c r="C91" s="1" t="n">
         <v>0.188672237</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>0.24331206</v>
+        <v>0.221192782</v>
       </c>
     </row>
     <row r="92">
@@ -20882,13 +20882,13 @@
         <v>160</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>0.147376937</v>
+        <v>0.163752152</v>
       </c>
       <c r="C92" s="1" t="n">
         <v>0.191560177</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>0.247036352</v>
+        <v>0.224578502</v>
       </c>
     </row>
     <row r="93">
@@ -20896,13 +20896,13 @@
         <v>164</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>0.149576665</v>
+        <v>0.166196294</v>
       </c>
       <c r="C93" s="1" t="n">
         <v>0.194419377</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>0.250723583</v>
+        <v>0.22793053</v>
       </c>
     </row>
     <row r="94">
@@ -20910,13 +20910,13 @@
         <v>168</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>0.151755034</v>
+        <v>0.168616704</v>
       </c>
       <c r="C94" s="1" t="n">
         <v>0.197250816</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>0.254375011</v>
+        <v>0.23125001</v>
       </c>
     </row>
     <row r="96">
@@ -20927,17 +20927,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.04</t>
+          <t>kORR 0.1</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.16</t>
+          <t>kORR 0.5</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>kORR 1</t>
+          <t>kORR 2.5</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Corrosion-product saturation, F/Fmax (%), in one-at-a-time parameter sweeps of k_f (panel d), k_d (panel e), and k_ORR (panel f). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves).</t>
+          <t>Corrosion-product saturation, F/Fmax (%), in one-at-a-time parameter sweeps of k_f (panel d), k_d (panel e), and k_ORR (panel f). Baseline: k_f = 35, k_d = 27, k_ORR = 0.5 (middle curves).</t>
         </is>
       </c>
     </row>
@@ -22510,17 +22510,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>kf 0.5</t>
+          <t>kf 5</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>kf 2.75</t>
+          <t>kf 35</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kf 15</t>
+          <t>kf 150</t>
         </is>
       </c>
     </row>
@@ -23134,17 +23134,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>kd 0.2</t>
+          <t>kd 5</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 5</t>
+          <t>kd 27</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 25</t>
+          <t>kd 120</t>
         </is>
       </c>
     </row>
@@ -23758,17 +23758,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.04</t>
+          <t>kORR 0.1</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.16</t>
+          <t>kORR 0.5</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>kORR 1</t>
+          <t>kORR 2.5</t>
         </is>
       </c>
     </row>
@@ -24398,7 +24398,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Baseline: k_f = 2.75, k_d = 5, k_ORR = 0.16 (middle curves).</t>
+          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Baseline: k_f = 35, k_d = 27, k_ORR = 0.5 (middle curves).</t>
         </is>
       </c>
     </row>
@@ -24417,17 +24417,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>kf 0.5</t>
+          <t>kf 5</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>kf 2.75</t>
+          <t>kf 35</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kf 15</t>
+          <t>kf 150</t>
         </is>
       </c>
     </row>
@@ -24450,13 +24450,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>3.454032211932749</v>
+        <v>3.454032211928929</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>3.378158378443137</v>
+        <v>3.378158378443136</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>3.313232879991455</v>
+        <v>3.313232879991452</v>
       </c>
     </row>
     <row r="9">
@@ -24464,13 +24464,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>3.424188156532705</v>
+        <v>3.424188156527746</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>3.327091709091328</v>
+        <v>3.327091709091327</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>3.234954417825595</v>
+        <v>3.234954417825592</v>
       </c>
     </row>
     <row r="10">
@@ -24478,13 +24478,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>3.398412627424506</v>
+        <v>3.398412627418912</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>3.287801698229836</v>
+        <v>3.287801698229835</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>3.174728018341239</v>
+        <v>3.174728018341237</v>
       </c>
     </row>
     <row r="11">
@@ -24492,7 +24492,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>3.374968192911498</v>
+        <v>3.374968192905532</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>3.254621805890813</v>
@@ -24506,13 +24506,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>3.353117466282266</v>
+        <v>3.353117466276094</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>3.225352580766006</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>3.079001765959154</v>
+        <v>3.079001765959153</v>
       </c>
     </row>
     <row r="13">
@@ -24520,7 +24520,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>3.332458199279029</v>
+        <v>3.332458199272769</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>3.198864433811903</v>
@@ -24534,13 +24534,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>3.31273984797052</v>
+        <v>3.31273984796426</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>3.174485618758139</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>3.001029428785689</v>
+        <v>3.00102942878569</v>
       </c>
     </row>
     <row r="15">
@@ -24548,13 +24548,13 @@
         <v>32</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>3.29379273647975</v>
+        <v>3.29379273647356</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>3.151778073637382</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2.966221760022937</v>
+        <v>2.966221760022938</v>
       </c>
     </row>
     <row r="16">
@@ -24562,13 +24562,13 @@
         <v>36</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>3.275495086870525</v>
+        <v>3.27549508686446</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>3.13043729475377</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2.933509163457803</v>
+        <v>2.933509163457805</v>
       </c>
     </row>
     <row r="17">
@@ -24576,13 +24576,13 @@
         <v>40</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>3.257755677997875</v>
+        <v>3.257755677991983</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>3.110241432644881</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2.90255157315352</v>
+        <v>2.902551573153524</v>
       </c>
     </row>
     <row r="18">
@@ -24590,13 +24590,13 @@
         <v>44</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>3.240503893227164</v>
+        <v>3.240503893221482</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>3.091022913941917</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2.873092121259178</v>
+        <v>2.873092121259182</v>
       </c>
     </row>
     <row r="19">
@@ -24604,13 +24604,13 @@
         <v>48</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>3.223683620540878</v>
+        <v>3.223683620535442</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>3.072651484639845</v>
+        <v>3.072651484639846</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2.844931145581527</v>
+        <v>2.844931145581531</v>
       </c>
     </row>
     <row r="20">
@@ -24618,13 +24618,13 @@
         <v>52</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>3.207249316274763</v>
+        <v>3.207249316269602</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>3.055023512843186</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>2.817909792106537</v>
+        <v>2.817909792106542</v>
       </c>
     </row>
     <row r="21">
@@ -24632,13 +24632,13 @@
         <v>56</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>3.191163357424306</v>
+        <v>3.191163357419446</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>3.038054938800559</v>
+        <v>3.03805493880056</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>2.791899208333125</v>
+        <v>2.791899208333131</v>
       </c>
     </row>
     <row r="22">
@@ -24646,13 +24646,13 @@
         <v>60</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>3.175394198742259</v>
+        <v>3.175394198737722</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>3.02167645832083</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>2.766793160085994</v>
+        <v>2.766793160086001</v>
       </c>
     </row>
     <row r="23">
@@ -24660,13 +24660,13 @@
         <v>64</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>3.159915052668067</v>
+        <v>3.159915052663875</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>3.005830131157718</v>
+        <v>3.005830131157719</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>2.742502832617017</v>
+        <v>2.742502832617024</v>
       </c>
     </row>
     <row r="24">
@@ -24674,13 +24674,13 @@
         <v>68</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>3.144702920377002</v>
+        <v>3.144702920373172</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>2.990466930599741</v>
+        <v>2.990466930599742</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>2.718953074450117</v>
+        <v>2.718953074450125</v>
       </c>
     </row>
     <row r="25">
@@ -24688,13 +24688,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>3.129737865417627</v>
+        <v>3.129737865414176</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>2.975544933404477</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>2.696079622789475</v>
+        <v>2.696079622789483</v>
       </c>
     </row>
     <row r="26">
@@ -24702,13 +24702,13 @@
         <v>76</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>3.115002459118078</v>
+        <v>3.115002459115021</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>2.961027956680829</v>
+        <v>2.961027956680831</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>2.673827014039998</v>
+        <v>2.673827014040008</v>
       </c>
     </row>
     <row r="27">
@@ -24716,13 +24716,13 @@
         <v>80</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>3.100481350253396</v>
+        <v>3.100481350250746</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>2.946884513787151</v>
+        <v>2.946884513787152</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>2.652146983336985</v>
+        <v>2.652146983336995</v>
       </c>
     </row>
     <row r="28">
@@ -24730,13 +24730,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>3.086160926322333</v>
+        <v>3.086160926320104</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>2.933087002465308</v>
+        <v>2.933087002465309</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>2.630997220062838</v>
+        <v>2.630997220062848</v>
       </c>
     </row>
     <row r="29">
@@ -24744,13 +24744,13 @@
         <v>88</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>3.072029043506436</v>
+        <v>3.072029043504639</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>2.9196110650242</v>
+        <v>2.919611065024201</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>2.610340387092862</v>
+        <v>2.610340387092874</v>
       </c>
     </row>
     <row r="30">
@@ -24758,13 +24758,13 @@
         <v>92</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>3.058074808902274</v>
+        <v>3.05807480890092</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>2.906435077996879</v>
+        <v>2.906435077996881</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>2.590143338507013</v>
+        <v>2.590143338507025</v>
       </c>
     </row>
     <row r="31">
@@ -24772,13 +24772,13 @@
         <v>96</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>3.04428840308005</v>
+        <v>3.044288403079149</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>2.893539740614846</v>
+        <v>2.893539740614848</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>2.570376488775317</v>
+        <v>2.570376488775329</v>
       </c>
     </row>
     <row r="32">
@@ -24786,13 +24786,13 @@
         <v>100</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>3.030660934135492</v>
+        <v>3.030660934135053</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>2.880907739670144</v>
+        <v>2.880907739670146</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>2.551013299035706</v>
+        <v>2.551013299035719</v>
       </c>
     </row>
     <row r="33">
@@ -24800,13 +24800,13 @@
         <v>104</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>3.017184316612068</v>
+        <v>3.0171843166121</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>2.868523474115765</v>
+        <v>2.868523474115767</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>2.532029854942812</v>
+        <v>2.532029854942826</v>
       </c>
     </row>
     <row r="34">
@@ -24814,13 +24814,13 @@
         <v>108</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>3.003851170264133</v>
+        <v>3.003851170264643</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>2.856372826881335</v>
+        <v>2.856372826881337</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>2.513404516891518</v>
+        <v>2.513404516891533</v>
       </c>
     </row>
     <row r="35">
@@ -24828,13 +24828,13 @@
         <v>112</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>2.990654734796906</v>
+        <v>2.990654734797903</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>2.844442974370458</v>
+        <v>2.84444297437046</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>2.495117628001557</v>
+        <v>2.495117628001571</v>
       </c>
     </row>
     <row r="36">
@@ -24842,13 +24842,13 @@
         <v>116</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>2.977588797582673</v>
+        <v>2.977588797584164</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>2.832722226301168</v>
+        <v>2.83272222630117</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>2.477151268614051</v>
+        <v>2.477151268614067</v>
       </c>
     </row>
     <row r="37">
@@ -24856,13 +24856,13 @@
         <v>120</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>2.964647631999936</v>
+        <v>2.964647632001927</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>2.821199890182602</v>
+        <v>2.821199890182604</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>2.459489048552159</v>
+        <v>2.459489048552175</v>
       </c>
     </row>
     <row r="38">
@@ -24870,13 +24870,13 @@
         <v>124</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>2.951825944533119</v>
+        <v>2.951825944535616</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>2.809866155947888</v>
+        <v>2.809866155947891</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>2.442115930278518</v>
+        <v>2.442115930278534</v>
       </c>
     </row>
     <row r="39">
@@ -24884,13 +24884,13 @@
         <v>128</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2.939118829146357</v>
+        <v>2.939118829149367</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>2.798711997195439</v>
+        <v>2.798711997195441</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>2.425018077511178</v>
+        <v>2.425018077511195</v>
       </c>
     </row>
     <row r="40">
@@ -24898,13 +24898,13 @@
         <v>132</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>2.926521727735617</v>
+        <v>2.926521727739145</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>2.787729086206113</v>
+        <v>2.787729086206116</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>2.408182724956147</v>
+        <v>2.408182724956164</v>
       </c>
     </row>
     <row r="41">
@@ -24912,13 +24912,13 @@
         <v>136</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>2.914030395690153</v>
+        <v>2.914030395694205</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>2.776909720457622</v>
+        <v>2.776909720457625</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>2.39159806566366</v>
+        <v>2.391598065663678</v>
       </c>
     </row>
     <row r="42">
@@ -24926,13 +24926,13 @@
         <v>140</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>2.901640871772689</v>
+        <v>2.901640871777269</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>2.766246758790023</v>
+        <v>2.766246758790026</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>2.375253153178318</v>
+        <v>2.375253153178337</v>
       </c>
     </row>
     <row r="43">
@@ -24940,13 +24940,13 @@
         <v>144</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>2.889349451669098</v>
+        <v>2.889349451674211</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>2.755733565716666</v>
+        <v>2.755733565716668</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>2.359137816175122</v>
+        <v>2.359137816175141</v>
       </c>
     </row>
     <row r="44">
@@ -24954,13 +24954,13 @@
         <v>148</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>2.877152664671255</v>
+        <v>2.877152664676906</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>2.745363962644929</v>
+        <v>2.745363962644932</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>2.343242583687296</v>
+        <v>2.343242583687316</v>
       </c>
     </row>
     <row r="45">
@@ -24968,13 +24968,13 @@
         <v>152</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>2.865047253047444</v>
+        <v>2.865047253053638</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>2.735132184986721</v>
+        <v>2.735132184986724</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>2.327558619362351</v>
+        <v>2.327558619362371</v>
       </c>
     </row>
     <row r="46">
@@ -24982,13 +24982,13 @@
         <v>156</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>2.853030153728149</v>
+        <v>2.853030153734888</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>2.725032844312053</v>
+        <v>2.725032844312056</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>2.312077663448508</v>
+        <v>2.312077663448529</v>
       </c>
     </row>
     <row r="47">
@@ -24996,13 +24996,13 @@
         <v>160</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>2.841098481994761</v>
+        <v>2.841098482002051</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>2.715060894839215</v>
+        <v>2.715060894839218</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>2.296791981428563</v>
+        <v>2.296791981428585</v>
       </c>
     </row>
     <row r="48">
@@ -25010,13 +25010,13 @@
         <v>164</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>2.8292495169077</v>
+        <v>2.829249516915543</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>2.705211603669146</v>
+        <v>2.705211603669149</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>2.281694318393105</v>
+        <v>2.281694318393127</v>
       </c>
     </row>
     <row r="49">
@@ -25024,13 +25024,13 @@
         <v>168</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>2.817480688250613</v>
+        <v>2.817480688259014</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>2.695480524264948</v>
+        <v>2.695480524264951</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>2.266777858388112</v>
+        <v>2.266777858388135</v>
       </c>
     </row>
     <row r="51">
@@ -25041,17 +25041,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>kd 0.2</t>
+          <t>kd 5</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 5</t>
+          <t>kd 27</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 25</t>
+          <t>kd 120</t>
         </is>
       </c>
     </row>
@@ -25077,7 +25077,7 @@
         <v>3.299534232056915</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>3.378158378443137</v>
+        <v>3.378158378443136</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>3.489035804179765</v>
@@ -25091,10 +25091,10 @@
         <v>3.215514346593322</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>3.327091709091328</v>
+        <v>3.327091709091327</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>3.477038768840998</v>
+        <v>3.477038768840996</v>
       </c>
     </row>
     <row r="55">
@@ -25105,10 +25105,10 @@
         <v>3.150870572986244</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>3.287801698229836</v>
+        <v>3.287801698229835</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>3.464618284223821</v>
+        <v>3.46461828422382</v>
       </c>
     </row>
     <row r="56">
@@ -25116,13 +25116,13 @@
         <v>16</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>3.096279764746657</v>
+        <v>3.096279764746656</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>3.254621805890813</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>3.451914564006221</v>
+        <v>3.45191456400622</v>
       </c>
     </row>
     <row r="57">
@@ -25136,7 +25136,7 @@
         <v>3.225352580766006</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>3.438995988250739</v>
+        <v>3.438995988250737</v>
       </c>
     </row>
     <row r="58">
@@ -25150,7 +25150,7 @@
         <v>3.198864433811903</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>3.425903571218633</v>
+        <v>3.425903571218631</v>
       </c>
     </row>
     <row r="59">
@@ -25164,7 +25164,7 @@
         <v>3.174485618758139</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>3.412664797151595</v>
+        <v>3.412664797151594</v>
       </c>
     </row>
     <row r="60">
@@ -25178,7 +25178,7 @@
         <v>3.151778073637382</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>3.399299426119611</v>
+        <v>3.39929942611961</v>
       </c>
     </row>
     <row r="61">
@@ -25192,7 +25192,7 @@
         <v>3.13043729475377</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>3.385822377510261</v>
+        <v>3.385822377510259</v>
       </c>
     </row>
     <row r="62">
@@ -25206,7 +25206,7 @@
         <v>3.110241432644881</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>3.372245330312667</v>
+        <v>3.372245330312666</v>
       </c>
     </row>
     <row r="63">
@@ -25220,7 +25220,7 @@
         <v>3.091022913941917</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>3.358577684750601</v>
+        <v>3.3585776847506</v>
       </c>
     </row>
     <row r="64">
@@ -25228,13 +25228,13 @@
         <v>48</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>2.796884371560752</v>
+        <v>2.796884371560753</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>3.072651484639845</v>
+        <v>3.072651484639846</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>3.344827175909638</v>
+        <v>3.344827175909637</v>
       </c>
     </row>
     <row r="65">
@@ -25242,13 +25242,13 @@
         <v>52</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>2.767881106023555</v>
+        <v>2.767881106023556</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>3.055023512843186</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>3.331000284182334</v>
+        <v>3.331000284182332</v>
       </c>
     </row>
     <row r="66">
@@ -25256,13 +25256,13 @@
         <v>56</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>2.739962746247239</v>
+        <v>2.73996274624724</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>3.038054938800559</v>
+        <v>3.03805493880056</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>3.317102520440236</v>
+        <v>3.317102520440235</v>
       </c>
     </row>
     <row r="67">
@@ -25287,10 +25287,10 @@
         <v>2.686943336882884</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>3.005830131157718</v>
+        <v>3.005830131157719</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>3.289112745465143</v>
+        <v>3.289112745465142</v>
       </c>
     </row>
     <row r="69">
@@ -25298,10 +25298,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>2.661666294780475</v>
+        <v>2.661666294780476</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>2.990466930599741</v>
+        <v>2.990466930599742</v>
       </c>
       <c r="D69" s="1" t="n">
         <v>3.275028495239805</v>
@@ -25312,13 +25312,13 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>2.637115163658199</v>
+        <v>2.6371151636582</v>
       </c>
       <c r="C70" s="1" t="n">
         <v>2.975544933404477</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>3.260889095182528</v>
+        <v>3.260889095182527</v>
       </c>
     </row>
     <row r="71">
@@ -25326,10 +25326,10 @@
         <v>76</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>2.613230411880173</v>
+        <v>2.613230411880174</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>2.961027956680829</v>
+        <v>2.961027956680831</v>
       </c>
       <c r="D71" s="1" t="n">
         <v>3.246697414060305</v>
@@ -25340,10 +25340,10 @@
         <v>80</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>2.589960234540016</v>
+        <v>2.589960234540017</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>2.946884513787151</v>
+        <v>2.946884513787152</v>
       </c>
       <c r="D72" s="1" t="n">
         <v>3.232456027744486</v>
@@ -25354,13 +25354,13 @@
         <v>84</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>2.567259217699512</v>
+        <v>2.567259217699513</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>2.933087002465308</v>
+        <v>2.933087002465309</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>3.218167262323566</v>
+        <v>3.218167262323567</v>
       </c>
     </row>
     <row r="74">
@@ -25368,10 +25368,10 @@
         <v>88</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>2.545087285699872</v>
+        <v>2.545087285699873</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>2.9196110650242</v>
+        <v>2.919611065024201</v>
       </c>
       <c r="D74" s="1" t="n">
         <v>3.203833229110157</v>
@@ -25382,13 +25382,13 @@
         <v>92</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>2.52340886149565</v>
+        <v>2.523408861495651</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>2.906435077996879</v>
+        <v>2.906435077996881</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>3.189455853367026</v>
+        <v>3.189455853367027</v>
       </c>
     </row>
     <row r="76">
@@ -25396,13 +25396,13 @@
         <v>96</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>2.502192189572354</v>
+        <v>2.502192189572355</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>2.893539740614846</v>
+        <v>2.893539740614848</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>3.175036898104413</v>
+        <v>3.175036898104415</v>
       </c>
     </row>
     <row r="77">
@@ -25410,13 +25410,13 @@
         <v>100</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>2.481408784544739</v>
+        <v>2.481408784544741</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>2.880907739670144</v>
+        <v>2.880907739670146</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>3.160577983965227</v>
+        <v>3.160577983965228</v>
       </c>
     </row>
     <row r="78">
@@ -25424,13 +25424,13 @@
         <v>104</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>2.461032978042436</v>
+        <v>2.461032978042437</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>2.868523474115765</v>
+        <v>2.868523474115767</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>3.146080605972599</v>
+        <v>3.146080605972601</v>
       </c>
     </row>
     <row r="79">
@@ -25438,13 +25438,13 @@
         <v>108</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>2.441041543278751</v>
+        <v>2.441041543278752</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>2.856372826881335</v>
+        <v>2.856372826881337</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>3.131546147736951</v>
+        <v>3.131546147736954</v>
       </c>
     </row>
     <row r="80">
@@ -25452,13 +25452,13 @@
         <v>112</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>2.421413381617061</v>
+        <v>2.421413381617062</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>2.844442974370458</v>
+        <v>2.84444297437046</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>3.116975893588076</v>
+        <v>3.116975893588078</v>
       </c>
     </row>
     <row r="81">
@@ -25466,13 +25466,13 @@
         <v>116</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>2.402129259060623</v>
+        <v>2.402129259060624</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>2.832722226301168</v>
+        <v>2.83272222630117</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>3.102371038998803</v>
+        <v>3.102371038998806</v>
       </c>
     </row>
     <row r="82">
@@ -25480,13 +25480,13 @@
         <v>120</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>2.383171583276336</v>
+        <v>2.383171583276337</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>2.821199890182602</v>
+        <v>2.821199890182604</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>3.087732699591628</v>
+        <v>3.087732699591631</v>
       </c>
     </row>
     <row r="83">
@@ -25494,13 +25494,13 @@
         <v>124</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>2.364524213781468</v>
+        <v>2.36452421378147</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>2.809866155947888</v>
+        <v>2.809866155947891</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>3.073061918961875</v>
+        <v>3.073061918961879</v>
       </c>
     </row>
     <row r="84">
@@ -25508,13 +25508,13 @@
         <v>128</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>2.346172299456154</v>
+        <v>2.346172299456156</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>2.798711997195439</v>
+        <v>2.798711997195441</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>3.058359675506172</v>
+        <v>3.058359675506176</v>
       </c>
     </row>
     <row r="85">
@@ -25522,13 +25522,13 @@
         <v>132</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>2.328102138721317</v>
+        <v>2.328102138721319</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>2.787729086206113</v>
+        <v>2.787729086206116</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>3.043626888409915</v>
+        <v>3.04362688840992</v>
       </c>
     </row>
     <row r="86">
@@ -25536,13 +25536,13 @@
         <v>136</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>2.310301058632966</v>
+        <v>2.310301058632968</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>2.776909720457622</v>
+        <v>2.776909720457625</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>3.028864422919713</v>
+        <v>3.028864422919717</v>
       </c>
     </row>
     <row r="87">
@@ -25550,13 +25550,13 @@
         <v>140</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>2.292757309855415</v>
+        <v>2.292757309855418</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>2.766246758790023</v>
+        <v>2.766246758790026</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>3.014073095004767</v>
+        <v>3.014073095004771</v>
       </c>
     </row>
     <row r="88">
@@ -25564,13 +25564,13 @@
         <v>144</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>2.275459975036205</v>
+        <v>2.275459975036208</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>2.755733565716666</v>
+        <v>2.755733565716668</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>2.999253675493477</v>
+        <v>2.999253675493482</v>
       </c>
     </row>
     <row r="89">
@@ -25578,13 +25578,13 @@
         <v>148</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>2.258398888549676</v>
+        <v>2.258398888549678</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>2.745363962644929</v>
+        <v>2.745363962644932</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>2.984406893757328</v>
+        <v>2.984406893757334</v>
       </c>
     </row>
     <row r="90">
@@ -25592,13 +25592,13 @@
         <v>152</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>2.241564565930961</v>
+        <v>2.241564565930963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>2.735132184986721</v>
+        <v>2.735132184986724</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>2.969533441002513</v>
+        <v>2.96953344100252</v>
       </c>
     </row>
     <row r="91">
@@ -25606,13 +25606,13 @@
         <v>156</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>2.224948141607346</v>
+        <v>2.224948141607348</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>2.725032844312053</v>
+        <v>2.725032844312056</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>2.954633973220317</v>
+        <v>2.954633973220324</v>
       </c>
     </row>
     <row r="92">
@@ -25620,13 +25620,13 @@
         <v>160</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>2.208541313764619</v>
+        <v>2.208541313764622</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>2.715060894839215</v>
+        <v>2.715060894839218</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>2.939709113839485</v>
+        <v>2.939709113839492</v>
       </c>
     </row>
     <row r="93">
@@ -25634,13 +25634,13 @@
         <v>164</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>2.192336295373745</v>
+        <v>2.192336295373747</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>2.705211603669146</v>
+        <v>2.705211603669149</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>2.924759456117398</v>
+        <v>2.924759456117405</v>
       </c>
     </row>
     <row r="94">
@@ -25648,13 +25648,13 @@
         <v>168</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>2.176325770556762</v>
+        <v>2.176325770556764</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>2.695480524264948</v>
+        <v>2.695480524264951</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>2.909785565301525</v>
+        <v>2.909785565301533</v>
       </c>
     </row>
     <row r="96">
@@ -25665,17 +25665,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.04</t>
+          <t>kORR 0.1</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.16</t>
+          <t>kORR 0.5</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>kORR 1</t>
+          <t>kORR 2.5</t>
         </is>
       </c>
     </row>
@@ -25701,10 +25701,10 @@
         <v>3.456706640907517</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>3.378158378443137</v>
+        <v>3.378158378443136</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>2.943844781462434</v>
+        <v>2.94384478146101</v>
       </c>
     </row>
     <row r="99">
@@ -25715,10 +25715,10 @@
         <v>3.442913653150727</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>3.327091709091328</v>
+        <v>3.327091709091327</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>2.776903805362583</v>
+        <v>2.776903805361334</v>
       </c>
     </row>
     <row r="100">
@@ -25729,10 +25729,10 @@
         <v>3.432889161618664</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>3.287801698229836</v>
+        <v>3.287801698229835</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>2.65689466812477</v>
+        <v>2.656894668123725</v>
       </c>
     </row>
     <row r="101">
@@ -25746,7 +25746,7 @@
         <v>3.254621805890813</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>2.559852197244473</v>
+        <v>2.559852197243632</v>
       </c>
     </row>
     <row r="102">
@@ -25760,7 +25760,7 @@
         <v>3.225352580766006</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>2.476952125744587</v>
+        <v>2.476952125743946</v>
       </c>
     </row>
     <row r="103">
@@ -25774,7 +25774,7 @@
         <v>3.198864433811903</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>2.403819946595871</v>
+        <v>2.403819946595424</v>
       </c>
     </row>
     <row r="104">
@@ -25788,7 +25788,7 @@
         <v>3.174485618758139</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>2.337923698998337</v>
+        <v>2.337923698998078</v>
       </c>
     </row>
     <row r="105">
@@ -25802,7 +25802,7 @@
         <v>3.151778073637382</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>2.277648260935394</v>
+        <v>2.277648260935318</v>
       </c>
     </row>
     <row r="106">
@@ -25816,7 +25816,7 @@
         <v>3.13043729475377</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>2.221891700476012</v>
+        <v>2.221891700476113</v>
       </c>
     </row>
     <row r="107">
@@ -25830,7 +25830,7 @@
         <v>3.110241432644881</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>2.169864095222871</v>
+        <v>2.169864095223145</v>
       </c>
     </row>
     <row r="108">
@@ -25844,7 +25844,7 @@
         <v>3.091022913941917</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>2.120977263774964</v>
+        <v>2.120977263775406</v>
       </c>
     </row>
     <row r="109">
@@ -25855,10 +25855,10 @@
         <v>3.38331511546021</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>3.072651484639845</v>
+        <v>3.072651484639846</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>2.074779847722627</v>
+        <v>2.074779847723232</v>
       </c>
     </row>
     <row r="110">
@@ -25872,7 +25872,7 @@
         <v>3.055023512843186</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>2.030916895117311</v>
+        <v>2.030916895118077</v>
       </c>
     </row>
     <row r="111">
@@ -25883,10 +25883,10 @@
         <v>3.375912975730939</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>3.038054938800559</v>
+        <v>3.03805493880056</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>1.989103539579807</v>
+        <v>1.989103539580728</v>
       </c>
     </row>
     <row r="112">
@@ -25900,7 +25900,7 @@
         <v>3.02167645832083</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>1.949107211802425</v>
+        <v>1.9491072118035</v>
       </c>
     </row>
     <row r="113">
@@ -25911,10 +25911,10 @@
         <v>3.369122449935923</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>3.005830131157718</v>
+        <v>3.005830131157719</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>1.910735237996617</v>
+        <v>1.910735237997841</v>
       </c>
     </row>
     <row r="114">
@@ -25925,10 +25925,10 @@
         <v>3.365918023498455</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>2.990466930599741</v>
+        <v>2.990466930599742</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>1.873825962170358</v>
+        <v>1.873825962171729</v>
       </c>
     </row>
     <row r="115">
@@ -25942,7 +25942,7 @@
         <v>2.975544933404477</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>1.83824224440345</v>
+        <v>1.838242244404965</v>
       </c>
     </row>
     <row r="116">
@@ -25953,10 +25953,10 @@
         <v>3.359833583460525</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>2.961027956680829</v>
+        <v>2.961027956680831</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>1.803866603709827</v>
+        <v>1.803866603711484</v>
       </c>
     </row>
     <row r="117">
@@ -25967,10 +25967,10 @@
         <v>3.356935377939236</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>2.946884513787151</v>
+        <v>2.946884513787152</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>1.770597525589933</v>
+        <v>1.770597525591728</v>
       </c>
     </row>
     <row r="118">
@@ -25981,10 +25981,10 @@
         <v>3.354123013810475</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>2.933087002465308</v>
+        <v>2.933087002465309</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>1.738346611227262</v>
+        <v>1.738346611229195</v>
       </c>
     </row>
     <row r="119">
@@ -25995,10 +25995,10 @@
         <v>3.351390034525519</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>2.9196110650242</v>
+        <v>2.919611065024201</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>1.707036345887589</v>
+        <v>1.707036345889656</v>
       </c>
     </row>
     <row r="120">
@@ -26009,10 +26009,10 @@
         <v>3.348730737267139</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>2.906435077996879</v>
+        <v>2.906435077996881</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>1.676598330233374</v>
+        <v>1.676598330235574</v>
       </c>
     </row>
     <row r="121">
@@ -26023,10 +26023,10 @@
         <v>3.346140056338053</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>2.893539740614846</v>
+        <v>2.893539740614848</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>1.646971862743176</v>
+        <v>1.646971862745506</v>
       </c>
     </row>
     <row r="122">
@@ -26037,10 +26037,10 @@
         <v>3.343613468655484</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>2.880907739670144</v>
+        <v>2.880907739670146</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>1.618102791931596</v>
+        <v>1.618102791934054</v>
       </c>
     </row>
     <row r="123">
@@ -26051,10 +26051,10 @@
         <v>3.341146916451304</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>2.868523474115765</v>
+        <v>2.868523474115767</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>1.589942578368454</v>
+        <v>1.589942578371039</v>
       </c>
     </row>
     <row r="124">
@@ -26065,10 +26065,10 @@
         <v>3.33873674350907</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>2.856372826881335</v>
+        <v>2.856372826881337</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>1.562447521617798</v>
+        <v>1.562447521620508</v>
       </c>
     </row>
     <row r="125">
@@ -26079,10 +26079,10 @@
         <v>3.336379642157457</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>2.844442974370458</v>
+        <v>2.84444297437046</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>1.535578118112745</v>
+        <v>1.535578118115578</v>
       </c>
     </row>
     <row r="126">
@@ -26093,10 +26093,10 @@
         <v>3.334072608889014</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>2.832722226301168</v>
+        <v>2.83272222630117</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>1.509298523940265</v>
+        <v>1.50929852394322</v>
       </c>
     </row>
     <row r="127">
@@ -26107,10 +26107,10 @@
         <v>3.331812906953791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>2.821199890182602</v>
+        <v>2.821199890182604</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>1.48357610239608</v>
+        <v>1.483576102399156</v>
       </c>
     </row>
     <row r="128">
@@ -26121,10 +26121,10 @@
         <v>3.32959803463735</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>2.809866155947888</v>
+        <v>2.809866155947891</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>1.458381040574113</v>
+        <v>1.458381040577307</v>
       </c>
     </row>
     <row r="129">
@@ -26135,10 +26135,10 @@
         <v>3.327425698205102</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>2.798711997195439</v>
+        <v>2.798711997195441</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>1.433686022585866</v>
+        <v>1.433686022589177</v>
       </c>
     </row>
     <row r="130">
@@ -26149,10 +26149,10 @@
         <v>3.32529378870316</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>2.787729086206113</v>
+        <v>2.787729086206116</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>1.409465949549547</v>
+        <v>1.409465949552974</v>
       </c>
     </row>
     <row r="131">
@@ -26163,10 +26163,10 @@
         <v>3.323200361966547</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>2.776909720457622</v>
+        <v>2.776909720457625</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>1.385697698450437</v>
+        <v>1.385697698453979</v>
       </c>
     </row>
     <row r="132">
@@ -26177,10 +26177,10 @@
         <v>3.321143621310685</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>2.766246758790023</v>
+        <v>2.766246758790026</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>1.362359913499505</v>
+        <v>1.362359913503161</v>
       </c>
     </row>
     <row r="133">
@@ -26191,10 +26191,10 @@
         <v>3.319121902480088</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>2.755733565716666</v>
+        <v>2.755733565716668</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>1.339432824813249</v>
+        <v>1.339432824817018</v>
       </c>
     </row>
     <row r="134">
@@ -26205,10 +26205,10 @@
         <v>3.317133660505801</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>2.745363962644929</v>
+        <v>2.745363962644932</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>1.316898090182478</v>
+        <v>1.316898090186358</v>
       </c>
     </row>
     <row r="135">
@@ -26219,10 +26219,10 @@
         <v>3.315177458184771</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>2.735132184986721</v>
+        <v>2.735132184986724</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>1.294738656449346</v>
+        <v>1.294738656453335</v>
       </c>
     </row>
     <row r="136">
@@ -26233,10 +26233,10 @@
         <v>3.313251955943838</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>2.725032844312053</v>
+        <v>2.725032844312056</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>1.272938637613901</v>
+        <v>1.272938637617999</v>
       </c>
     </row>
     <row r="137">
@@ -26247,10 +26247,10 @@
         <v>3.311355902890913</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>2.715060894839215</v>
+        <v>2.715060894839218</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>1.251483207276634</v>
+        <v>1.25148320728084</v>
       </c>
     </row>
     <row r="138">
@@ -26261,10 +26261,10 @@
         <v>3.309488128888241</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>2.705211603669146</v>
+        <v>2.705211603669149</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>1.230358503416843</v>
+        <v>1.230358503421156</v>
       </c>
     </row>
     <row r="139">
@@ -26275,10 +26275,10 @@
         <v>3.307647537509101</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>2.695480524264948</v>
+        <v>2.695480524264951</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>1.20955154382745</v>
+        <v>1.209551543831868</v>
       </c>
     </row>
   </sheetData>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -3388,7 +3388,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Admissible search ranges and optimized values of the effective kinetic parameters used in the Zn biodegradation model (best point of the two-repeat Bayesian optimization, repeat 1, iteration 25; corrected-physics code v2).</t>
+          <t>Admissible search ranges and optimized values of the effective kinetic parameters used in the Zn biodegradation model.</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.75</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="6">
@@ -3447,11 +3447,11 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>[1, 100]</t>
+          <t>[5, 100]</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.19</v>
+        <v>27.17</v>
       </c>
     </row>
     <row r="7">
@@ -3467,11 +3467,11 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>[0.05, 5]</t>
+          <t>[0.05, 5.0]</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.161</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="8">
@@ -5123,1526 +5123,801 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Supplementary Figure 6b</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Trajectories of the three calibrated kinetic parameters over the evaluations of each final Bayesian optimization repeat (min-max normalized to [0,1] within each repeat).</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Normalized trajectories of the three calibrated kinetic parameters, k_f, k_d, and k_ORR (min-max normalized to [0,1]).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Normalization: (value - min) / (max - min) over the 28 evaluations of each repeat.</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Normalization: (value - min) / (max - min) over the 32 evaluated iterations (k_f: 1.213-83.562 h^-1; k_d: 5.0-100.0 L^2 mol^-2 h^-1; k_ORR: 0.0602-4.4933 mm h^-1).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Iteration</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>k_f</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>k_d</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>k_ORR</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>k_f (norm)</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>k_d (norm)</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>k_ORR (norm)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="1" t="n">
+        <v>9.864005000000001</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>15.319409</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1.322114</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.1050526460385154</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.1086253578947368</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.2846491380434346</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>32.64415</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>24.529234</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0.060249</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.3816805673133817</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.2055708842105263</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>67.991682</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>8.613716999999999</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>2.508756</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0.8109190247225341</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.03803912631578947</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.5523296129485452</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>83.562388</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>34.156142</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>4.493303</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="F9" s="1" t="n">
+        <v>0.3069067578947369</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>19.536874</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>20.009222</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0.887589</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0.2225139547454659</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.1579918105263158</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.1866298041936778</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>11.869081</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>36.881722</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0.1294010426741876</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.3355970736842105</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>0.0430969259566881</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>24.90597</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>78.122794</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>2.136741</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0.2877129192650157</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.7697136210526315</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.4684111675607831</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4.364803</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>5.5078</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0.15547</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0.0382737551258111</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0.005345263157894732</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.02147977443992335</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="n">
         <v>1.694926</v>
       </c>
-      <c r="D6" t="n">
-        <v>32.895087</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="C14" s="1" t="n">
+        <v>48.516168</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>0.079988</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.005083028097361085</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.3525701721769736</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="E14" s="1" t="n">
+        <v>0.00585242837088588</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.4580649263157895</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>0.004452686567770211</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>6.248831</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>12.592237</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0.165976</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0.06115222009008783</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.07991828421052632</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0.02384969819902939</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1.212982</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>7.744136</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>0.730585</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.02888564210526316</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0.1512131365871023</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>2.937196</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>65.546769</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0.462952</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.02093778308491989</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.6373344105263158</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.09084098682307952</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>60.640234</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0.433336</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.7216476096986055</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.08416026513550252</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>57.480181</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>18.053204</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>0.434372</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0.683273890281613</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>0.1374021473684211</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>0.08439396407081889</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>66.116321</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>27.695915</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>0.445382</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>0.788145806419053</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>0.2389043684210526</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>0.08687757920386262</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>58.226265</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>0.430407</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0.692333870629255</v>
+      </c>
+      <c r="F21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>6.248831</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.136556</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.165976</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0531127308589125</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.04176822057388145</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.02384969819902939</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>67.991682</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.30743</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.508756</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.7043100617607995</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.02200031481652697</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.5523296129485452</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>83.562388</v>
-      </c>
-      <c r="D9" t="n">
-        <v>19.179087</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.493303</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.8685331584146614</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.2043373028350725</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>19.536874</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8.429864999999999</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.887589</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.1932607479064166</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.08816728094435447</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.1866298041936778</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" t="n">
-        <v>11.869081</v>
-      </c>
-      <c r="D11" t="n">
-        <v>21.581582</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.2513</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.1123890962959625</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.2303017769842101</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0430969259566881</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>24.90597</v>
-      </c>
-      <c r="D12" t="n">
-        <v>68.41846200000001</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.136741</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.2498882104859466</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.7364817940024588</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4684111675607831</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4.364803</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.160317</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.15547</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.03324202542381006</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.009603125297031771</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.02147977443992335</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" t="n">
-        <v>9.864005000000001</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.591374</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.322114</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.09124170646364929</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05749086905086059</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.2846491380434346</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" t="n">
-        <v>32.64415</v>
-      </c>
-      <c r="D15" t="n">
-        <v>11.529106</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.060249</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.3315022286341912</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.1216616952205329</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" t="n">
-        <v>11</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.212982</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.959209</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.730585</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.0182369874619698</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.1512131365871023</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2.937196</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52.238975</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.462952</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.01818515887294654</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.5616252919253236</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.09084098682307952</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.65142</v>
-      </c>
-      <c r="D18" t="n">
-        <v>13.340759</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.13986</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.004624173499308634</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.141240765098184</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.01795849994157527</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.110482</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5.164383</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.120551</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.02001279363316622</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05287625100528114</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.01360281196664873</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C20" t="n">
-        <v>96.027331</v>
-      </c>
-      <c r="D20" t="n">
-        <v>92.801824</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.155431</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.02147097689313056</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" t="n">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>39.312359</v>
-      </c>
-      <c r="D21" t="n">
-        <v>25.571236</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.170367</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.4018313409503028</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.2734191479452331</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.02484021173664927</v>
+      <c r="G21" s="1" t="n">
+        <v>0.0834995468135511</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" t="n">
+      <c r="A22" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C22" t="n">
-        <v>21.591821</v>
-      </c>
-      <c r="D22" t="n">
-        <v>47.992436</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.185983</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.2149341235259654</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.5157316887799249</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.02836283970373472</v>
+      <c r="B22" s="1" t="n">
+        <v>66.021243</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>11.767734</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>0.452399</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>0.7869912382853131</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>0.0712393052631579</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>0.08846046089219756</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" t="n">
+      <c r="A23" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C23" t="n">
-        <v>3.572647</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.149858</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.131958</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.02488721406503566</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.02029738760101647</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.01617598161448067</v>
+      <c r="B23" s="1" t="n">
+        <v>55.129743</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>65.183634</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>0.418043</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0.6547316321868794</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>0.6335119368421053</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>0.08071049890211127</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" t="n">
+      <c r="A24" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="C24" t="n">
-        <v>11.112605</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.296377</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.187857</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.1044105992859794</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.01107356596505882</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.0287855731060348</v>
+      <c r="B24" s="1" t="n">
+        <v>57.141068</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>42.489062</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>0.437817</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0.6791559127943193</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>0.3946217052631579</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>0.08517108070418271</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>1</v>
-      </c>
-      <c r="B25" t="n">
+      <c r="A25" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C25" t="n">
-        <v>8.889404000000001</v>
-      </c>
-      <c r="D25" t="n">
-        <v>7.270552</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.150208</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.08096266104194841</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.07563824241596666</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.02029278235726432</v>
+      <c r="B25" s="1" t="n">
+        <v>60.154809</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>7.670637</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>0.431341</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>0.7157529102274278</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>0.02811196842105263</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>0.08371023678033246</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B26" t="n">
+      <c r="A26" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C26" t="n">
-        <v>2.212004</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.464689</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.169594</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.01053661192147193</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.01289256353757808</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.02466583984765356</v>
+      <c r="B26" s="1" t="n">
+        <v>48.4118</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>29.5251</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>0.5962</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>0.5731531081110652</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>0.258158947368421</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>0.1208988205422266</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" t="n">
+      <c r="A27" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="C27" t="n">
-        <v>13.899914</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2.782232</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.168231</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.1338081433222729</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.02713164048211995</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.02435837686615141</v>
+      <c r="B27" s="1" t="n">
+        <v>35.90583</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>27.16962</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>0.4212883818494089</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>0.2333644210526316</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>0.1008832736979969</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" t="n">
+      <c r="A28" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C28" t="n">
-        <v>16.688455</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.608151</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.169487</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.1632186811724036</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.01444299980919719</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.02464170298850409</v>
+      <c r="B28" s="1" t="n">
+        <v>51.43335</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>37.009824</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>0.704924</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>0.6098449331862819</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>0.3369455157894737</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>0.1454245763755641</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" t="n">
+      <c r="A29" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C29" t="n">
-        <v>3.943548</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.630457</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.167983</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.02879907976797899</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.003876771538683878</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.02430243349167413</v>
+      <c r="B29" s="1" t="n">
+        <v>57.872716</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>21.341167</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>0.656898</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>0.6880405913310412</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>0.1720122842105263</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>0.1345909614455407</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" t="n">
+      <c r="A30" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C30" t="n">
-        <v>2.746778</v>
-      </c>
-      <c r="D30" t="n">
-        <v>5.193701</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.161242</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.0161768341625169</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05319309930386425</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.02278181136525745</v>
+      <c r="B30" s="1" t="n">
+        <v>36.548579</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>14.595382</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>0.427188</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>0.4290935261876692</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>0.1010040210526316</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>0.08277341083596094</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" t="n">
+      <c r="A31" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="C31" t="n">
-        <v>8.932912999999999</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.84551</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.17345</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.0814215472807813</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.006200912924699032</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.02553566908952609</v>
+      <c r="B31" s="1" t="n">
+        <v>62.647707</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>13.264881</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>0.301923</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>0.7460251140123585</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>0.08699874736842106</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>0.05451636727186269</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" t="n">
+      <c r="A32" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C32" t="n">
-        <v>4.808245</v>
-      </c>
-      <c r="D32" t="n">
-        <v>3.38274</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.165505</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.03791897574490544</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.03362150807491423</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.02374345090314713</v>
+      <c r="B32" s="1" t="n">
+        <v>21.406276</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>20.22353</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>0.820634</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>0.245214810656922</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>0.1602476842105263</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>0.1715262209754269</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" t="n">
+      <c r="A33" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="C33" t="n">
-        <v>6.86785</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.271739</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.170569</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.05964147894956278</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.02488577851747351</v>
+      <c r="B33" s="1" t="n">
+        <v>50.313013</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>39.610909</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>1.082887</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>0.596240257033548</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>0.3643253578947369</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>0.2306847604382893</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.231553</v>
-      </c>
-      <c r="D34" t="n">
-        <v>18.768511</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.171726</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.02640608676455242</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.2209117644873664</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.02930932474636767</v>
+      <c r="A34" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>75.720311</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>22.601489</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>0.222116</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>0.9047706913635782</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>0.1852788315789474</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>0.03651365401820054</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1.717066</v>
-      </c>
-      <c r="D35" t="n">
-        <v>4.145834</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.075599</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.00725906538016121</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.03615021714731169</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.006000611045372543</v>
+      <c r="A35" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>14.726772</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>47.756723</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>0.526387</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>0.1641030659043248</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>0.4500707684210526</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>0.1051505350487497</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>2</v>
-      </c>
-      <c r="B36" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" t="n">
-        <v>7.163271</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1.873456</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1.597499</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.0761131417761807</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.007438095870099669</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.3750283699637252</v>
+      <c r="A36" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>30.214196</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>61.694967</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>0.394269</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>0.3521727163399333</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>0.5967891263157895</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>0.07534760460847081</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>2</v>
-      </c>
-      <c r="B37" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" t="n">
-        <v>6.250469</v>
-      </c>
-      <c r="D37" t="n">
-        <v>23.214038</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.385024</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.06457297047479937</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.2770822213238261</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.08102946596574265</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>2</v>
-      </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="n">
-        <v>12.250578</v>
-      </c>
-      <c r="D38" t="n">
-        <v>3.125113</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.520599</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.1404298218916014</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.0232531264598481</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.113903464530271</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>2</v>
-      </c>
-      <c r="B39" t="n">
-        <v>6</v>
-      </c>
-      <c r="C39" t="n">
-        <v>80.24067599999999</v>
-      </c>
-      <c r="D39" t="n">
-        <v>8.608919</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.379929</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.09254252414487364</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.3222723613508952</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" t="n">
-        <v>7</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1.14289</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1.284779</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.886557</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.2026403464530271</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" t="n">
-        <v>8</v>
-      </c>
-      <c r="C41" t="n">
-        <v>2.742694</v>
-      </c>
-      <c r="D41" t="n">
-        <v>14.370312</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.309434</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.02022564828805702</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.165339309953256</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.06270052957265619</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>2</v>
-      </c>
-      <c r="B42" t="n">
-        <v>9</v>
-      </c>
-      <c r="C42" t="n">
-        <v>49.33701</v>
-      </c>
-      <c r="D42" t="n">
-        <v>49.770759</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.122391</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.6092979644209005</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.6126336982687196</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.01734665670889022</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" t="n">
-        <v>10</v>
-      </c>
-      <c r="C43" t="n">
-        <v>17.984653</v>
-      </c>
-      <c r="D43" t="n">
-        <v>31.99086</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2.467515</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.2129233174743981</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.3879797822456897</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.5859883901379217</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" t="n">
-        <v>11</v>
-      </c>
-      <c r="C44" t="n">
-        <v>28.784283</v>
-      </c>
-      <c r="D44" t="n">
-        <v>80.428287</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.050852</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.3494584917964707</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" t="n">
-        <v>12</v>
-      </c>
-      <c r="C45" t="n">
-        <v>34.334475</v>
-      </c>
-      <c r="D45" t="n">
-        <v>5.912552</v>
-      </c>
-      <c r="E45" t="n">
-        <v>4.174932</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.4196272320441434</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.05847318519163947</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" t="n">
-        <v>13</v>
-      </c>
-      <c r="C46" t="n">
-        <v>4.867365</v>
-      </c>
-      <c r="D46" t="n">
-        <v>57.98448</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.153058</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.04708696903349482</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.7164163231177471</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.02478273942309557</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" t="n">
-        <v>14</v>
-      </c>
-      <c r="C47" t="n">
-        <v>16.038995</v>
-      </c>
-      <c r="D47" t="n">
-        <v>14.538771</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.134354</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.188325182704861</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.1674678357699282</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.02024742488021571</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B48" t="n">
-        <v>15</v>
-      </c>
-      <c r="C48" t="n">
-        <v>67.98115900000001</v>
-      </c>
-      <c r="D48" t="n">
-        <v>9.359014999999999</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.166231</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.8450080891012551</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.102020193494582</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.027976906364571</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>2</v>
-      </c>
-      <c r="B49" t="n">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>34.313686</v>
-      </c>
-      <c r="D49" t="n">
-        <v>5.614269</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.123565</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.4193644054714755</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.05470429741375629</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.01763132625943241</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" t="n">
-        <v>17</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1.672196</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1.532891</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.1827</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.006691792865099916</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.003134963388279429</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.031970281856802</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>2</v>
-      </c>
-      <c r="B51" t="n">
-        <v>18</v>
-      </c>
-      <c r="C51" t="n">
-        <v>24.355439</v>
-      </c>
-      <c r="D51" t="n">
-        <v>42.950018</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.188499</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.2934664821086143</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.5264517589996137</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.03337641364861981</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>2</v>
-      </c>
-      <c r="B52" t="n">
-        <v>19</v>
-      </c>
-      <c r="C52" t="n">
-        <v>2.724628</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.838098</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.139245</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.01999724745772278</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.01962661296236705</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.02143338635525984</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" t="n">
-        <v>20</v>
-      </c>
-      <c r="C53" t="n">
-        <v>5.798896</v>
-      </c>
-      <c r="D53" t="n">
-        <v>18.590766</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.156108</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.05886392319501838</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.2186659075056415</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.02552229830653139</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>2</v>
-      </c>
-      <c r="B54" t="n">
-        <v>21</v>
-      </c>
-      <c r="C54" t="n">
-        <v>6.901248</v>
-      </c>
-      <c r="D54" t="n">
-        <v>17.600511</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.154715</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.07280049532612708</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.2061537631109301</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.02518452600337529</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>2</v>
-      </c>
-      <c r="B55" t="n">
-        <v>22</v>
-      </c>
-      <c r="C55" t="n">
-        <v>2.798155</v>
-      </c>
-      <c r="D55" t="n">
-        <v>21.5669</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.159133</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.02092681835620532</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.2562701794820619</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.02625579523190626</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" t="n">
-        <v>23</v>
-      </c>
-      <c r="C56" t="n">
-        <v>7.949332</v>
-      </c>
-      <c r="D56" t="n">
-        <v>25.587326</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.154339</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.08605097998571036</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.3070693682165314</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.02509335415413862</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>2</v>
-      </c>
-      <c r="B57" t="n">
-        <v>24</v>
-      </c>
-      <c r="C57" t="n">
-        <v>11.348658</v>
-      </c>
-      <c r="D57" t="n">
-        <v>6.902363</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.156126</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.1290272271337658</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.07097971952418386</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.02552666291633527</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2</v>
-      </c>
-      <c r="B58" t="n">
-        <v>25</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.864819</v>
-      </c>
-      <c r="D58" t="n">
-        <v>12.903469</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.153833</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.03441220213167534</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.1468053450448519</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.024970660122985</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>2</v>
-      </c>
-      <c r="B59" t="n">
-        <v>26</v>
-      </c>
-      <c r="C59" t="n">
-        <v>13.976492</v>
-      </c>
-      <c r="D59" t="n">
-        <v>49.683661</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.15585</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.1622498258042267</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.6115331910736128</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.02545973889934239</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>2</v>
-      </c>
-      <c r="B60" t="n">
-        <v>27</v>
-      </c>
-      <c r="C60" t="n">
-        <v>5.239894</v>
-      </c>
-      <c r="D60" t="n">
-        <v>8.348601</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.160076</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.05179669630702432</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.08925333458810039</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.02648445228996527</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2</v>
-      </c>
-      <c r="B61" t="n">
-        <v>28</v>
-      </c>
-      <c r="C61" t="n">
-        <v>2.416345</v>
-      </c>
-      <c r="D61" t="n">
-        <v>41.608103</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.164407</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.01609975530794251</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.509496293745281</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.02753462590444414</v>
+      <c r="A37" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>25.55777</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>28.358274</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>0.705943</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>0.2956279733213862</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>0.2458765684210527</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>0.1456544404827913</v>
       </c>
     </row>
   </sheetData>
@@ -11687,7 +10962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11703,1980 +10978,861 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Figure 3b</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Final Bayesian optimization history of the 3D reaction-diffusion model for two independent repeats (28 evaluations each; Phase 1 12-point Latin hypercube, Phase 2 8 expected-improvement points, Phase 3 8 local points; all points chosen and scored on mass loss only). RMSE is the mass-loss error of the corrected coarse-mesh simulation against the 0-336 h target (Table S7).</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Bayesian optimization history of the 3D reaction-diffusion model (32 evaluations; global search -&gt; Phase 2 EI -&gt; dip verification -&gt; Phase 3 local refinement).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Best RMSE: repeat 1 0.0173% (iteration 25; k_f 2.75, k_d 5.19, k_ORR 0.161; adopted in Table 2), repeat 2 0.0178% (iteration 20; k_f 5.80, k_d 18.6, k_ORR 0.156).</t>
+          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 L^2 mol^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Iteration</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>k_f</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>k_d</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>k_ORR</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (%)</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Stage</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Iteration</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Run in stage</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>k_f (h^-1)</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>k_d (L^2 mol^-2 h^-1)</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>k_ORR (mm h^-1)</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>Mass-loss RMSE (%)</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>Corrected mass loss at 336 h (%)</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>Best RMSE so far (%)</t>
+      <c r="A5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>35.90583</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>27.16962</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.042402</v>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>dip</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>11.869081</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>36.881722</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.04609</v>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>30.214196</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>61.694967</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.394269</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.046374</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>phase3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>48.4118</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>29.5251</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0.5962</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.046388</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>dip</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>57.872716</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>21.341167</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.656898</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.046866</v>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>dip</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>36.548579</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>14.595382</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0.427188</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>phase3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>51.43335</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>37.009824</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0.704924</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.048462</v>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>dip</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>4.364803</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>5.5078</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0.15547</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.052771</v>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>57.141068</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>42.489062</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0.437817</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0.055936</v>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>phase2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>57.480181</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>18.053204</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.434372</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.056486</v>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>phase2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>66.021243</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>11.767734</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0.452399</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.05756</v>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>phase2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>58.226265</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0.430407</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.057868</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>phase2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>60.640234</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.433336</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.058507</v>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>phase2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>66.116321</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>27.695915</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.445382</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.058528</v>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>phase2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>60.154809</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>7.670637</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0.431341</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>0.059043</v>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>phase2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>55.129743</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>65.183634</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>0.418043</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>0.059716</v>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>phase2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>6.248831</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>12.592237</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0.165976</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>0.060445</v>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>14.726772</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>47.756723</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>0.526387</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>0.070782</v>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>phase3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>25.55777</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>28.358274</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0.705943</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>0.07711800000000001</v>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>phase3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>62.647707</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>13.264881</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0.301923</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>0.088184</v>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>phase3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>1.694926</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>48.516168</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>0.079988</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>0.100601</v>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>50.313013</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>39.610909</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>1.082887</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>0.100613</v>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>phase3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>21.406276</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>20.22353</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>0.820634</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>0.112077</v>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>phase3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>75.720311</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>22.601489</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>0.222116</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>0.112735</v>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>phase3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>19.536874</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>20.009222</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>0.887589</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>0.126677</v>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>32.64415</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>24.529234</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>0.060249</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>0.154122</v>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>2.937196</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>65.546769</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>0.462952</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>0.160994</v>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>67.991682</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>8.613716999999999</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>2.508756</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>0.206768</v>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>24.90597</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>78.122794</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>2.136741</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>0.260444</v>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.694926</v>
-      </c>
-      <c r="F6" t="n">
-        <v>32.895087</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.079988</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.099538</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.176334</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.099538</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6.248831</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4.136556</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.165976</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.019242</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.348833</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>67.991682</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.30743</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.508756</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.484985</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.922839</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" t="n">
+      <c r="C34" s="1" t="n">
+        <v>9.864005000000001</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>15.319409</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>1.322114</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>0.276129</v>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C35" s="1" t="n">
         <v>83.562388</v>
       </c>
-      <c r="F9" t="n">
-        <v>19.179087</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="D35" s="1" t="n">
+        <v>34.156142</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>4.493303</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.798023</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.249787</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>19.536874</v>
-      </c>
-      <c r="F10" t="n">
-        <v>8.429864999999999</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.887589</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.407249</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9174870000000001</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>11.869081</v>
-      </c>
-      <c r="F11" t="n">
-        <v>21.581582</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.2513</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.09006599999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.481302</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>24.90597</v>
-      </c>
-      <c r="F12" t="n">
-        <v>68.41846200000001</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.136741</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.685383</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.199515</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4.364803</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.160317</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.15547</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.022199</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.317281</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>9.864005000000001</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5.591374</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.322114</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.535017</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.074189</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>32.64415</v>
-      </c>
-      <c r="F15" t="n">
-        <v>11.529106</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.060249</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.126803</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.12901</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" t="n">
+      <c r="F35" s="1" t="n">
+        <v>0.307616</v>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="C36" s="1" t="n">
         <v>1.212982</v>
       </c>
-      <c r="F16" t="n">
-        <v>1.959209</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="D36" s="1" t="n">
+        <v>7.744136</v>
+      </c>
+      <c r="E36" s="1" t="n">
         <v>0.730585</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.372672</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.871742</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2.937196</v>
-      </c>
-      <c r="F17" t="n">
-        <v>52.238975</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.462952</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.247297</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.716529</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.65142</v>
-      </c>
-      <c r="F18" t="n">
-        <v>13.340759</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.13986</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.030449</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.308333</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3.110482</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5.164383</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.120551</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.049609</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.27296</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>96.027331</v>
-      </c>
-      <c r="F20" t="n">
-        <v>92.801824</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.155431</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.01977</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.330476</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" t="n">
-        <v>16</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>39.312359</v>
-      </c>
-      <c r="F21" t="n">
-        <v>25.571236</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.170367</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.020739</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.355315</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" t="n">
-        <v>17</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="n">
-        <v>21.591821</v>
-      </c>
-      <c r="F22" t="n">
-        <v>47.992436</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.185983</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.032464</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.387205</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" t="n">
-        <v>18</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3.572647</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2.149858</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.131958</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.038887</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.286809</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" t="n">
-        <v>19</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>11.112605</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.296377</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.187857</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.019758</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.354644</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>1</v>
-      </c>
-      <c r="B25" t="n">
-        <v>20</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>7</v>
-      </c>
-      <c r="E25" t="n">
-        <v>8.889404000000001</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7.270552</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.150208</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.022206</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.319582</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B26" t="n">
-        <v>21</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.212004</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.464689</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.169594</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.020802</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.355315</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" t="n">
-        <v>22</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>13.899914</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.782232</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.168231</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.019658</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.335433</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" t="n">
-        <v>23</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>16.688455</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.608151</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.169487</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.023654</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.313753</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.019242</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" t="n">
-        <v>24</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3.943548</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.630457</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.167983</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.018551</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.332743</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.018551</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" t="n">
-        <v>25</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2.746778</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5.193701</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.161242</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.017299</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.338702</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.017299</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" t="n">
-        <v>26</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" t="n">
-        <v>8.932912999999999</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.84551</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.17345</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.020737</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.323655</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.017299</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" t="n">
-        <v>27</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>6</v>
-      </c>
-      <c r="E32" t="n">
-        <v>4.808245</v>
-      </c>
-      <c r="F32" t="n">
-        <v>3.38274</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.165505</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.018571</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.346478</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.017299</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" t="n">
-        <v>28</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>7</v>
-      </c>
-      <c r="E33" t="n">
-        <v>6.86785</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.271739</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.170569</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.028932</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.295822</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.017299</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3.231553</v>
-      </c>
-      <c r="F34" t="n">
-        <v>18.768511</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.171726</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.023972</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.366715</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.717066</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4.145834</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.075599</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.106207</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.167068</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>2</v>
-      </c>
-      <c r="B36" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" t="n">
-        <v>7.163271</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.873456</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.597499</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.565789</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1.098042</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>2</v>
-      </c>
-      <c r="B37" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" t="n">
-        <v>6.250469</v>
-      </c>
-      <c r="F37" t="n">
-        <v>23.214038</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.385024</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.192446</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.638341</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>2</v>
-      </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="n">
-        <v>12.250578</v>
-      </c>
-      <c r="F38" t="n">
-        <v>3.125113</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.520599</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.255107</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.723939</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>2</v>
-      </c>
-      <c r="B39" t="n">
-        <v>6</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>80.24067599999999</v>
-      </c>
-      <c r="F39" t="n">
-        <v>8.608919</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.379929</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.459757</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.9547949999999999</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" t="n">
-        <v>7</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>6</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.14289</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1.284779</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.886557</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.424478</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.945305</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" t="n">
-        <v>8</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2.742694</v>
-      </c>
-      <c r="F41" t="n">
-        <v>14.370312</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.309434</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.139851</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.5533979999999999</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>2</v>
-      </c>
-      <c r="B42" t="n">
-        <v>9</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>8</v>
-      </c>
-      <c r="E42" t="n">
-        <v>49.33701</v>
-      </c>
-      <c r="F42" t="n">
-        <v>49.770759</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.122391</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.048913</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.27405</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" t="n">
-        <v>10</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>9</v>
-      </c>
-      <c r="E43" t="n">
-        <v>17.984653</v>
-      </c>
-      <c r="F43" t="n">
-        <v>31.99086</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2.467515</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.716048</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.212034</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" t="n">
-        <v>11</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="n">
-        <v>28.784283</v>
-      </c>
-      <c r="F44" t="n">
-        <v>80.428287</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.050852</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.136761</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.112901</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" t="n">
-        <v>12</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Phase 1: global LHS</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11</v>
-      </c>
-      <c r="E45" t="n">
-        <v>34.334475</v>
-      </c>
-      <c r="F45" t="n">
-        <v>5.912552</v>
-      </c>
-      <c r="G45" t="n">
-        <v>4.174932</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.758822</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.210164</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.023972</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" t="n">
-        <v>13</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>4.867365</v>
-      </c>
-      <c r="F46" t="n">
-        <v>57.98448</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.153058</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.018888</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.325427</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.018888</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" t="n">
-        <v>14</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="n">
-        <v>16.038995</v>
-      </c>
-      <c r="F47" t="n">
-        <v>14.538771</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.134354</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.037066</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.292045</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.018888</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B48" t="n">
-        <v>15</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E48" t="n">
-        <v>67.98115900000001</v>
-      </c>
-      <c r="F48" t="n">
-        <v>9.359014999999999</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.166231</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.023316</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.315387</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.018888</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>2</v>
-      </c>
-      <c r="B49" t="n">
-        <v>16</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" t="n">
-        <v>34.313686</v>
-      </c>
-      <c r="F49" t="n">
-        <v>5.614269</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.123565</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.059885</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.258294</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.018888</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" t="n">
-        <v>17</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1.672196</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1.532891</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.1827</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.029648</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.380577</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.018888</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>2</v>
-      </c>
-      <c r="B51" t="n">
-        <v>18</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>5</v>
-      </c>
-      <c r="E51" t="n">
-        <v>24.355439</v>
-      </c>
-      <c r="F51" t="n">
-        <v>42.950018</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.188499</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.0335</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.389917</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.018888</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>2</v>
-      </c>
-      <c r="B52" t="n">
-        <v>19</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>6</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.724628</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2.838098</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.139245</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.032489</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.305515</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.018888</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" t="n">
-        <v>20</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Phase 2: EI-guided</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>7</v>
-      </c>
-      <c r="E53" t="n">
-        <v>5.798896</v>
-      </c>
-      <c r="F53" t="n">
-        <v>18.590766</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.156108</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.017751</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.332175</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.017751</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>2</v>
-      </c>
-      <c r="B54" t="n">
-        <v>21</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>6.901248</v>
-      </c>
-      <c r="F54" t="n">
-        <v>17.600511</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.154715</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.018855</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.331151</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.017751</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>2</v>
-      </c>
-      <c r="B55" t="n">
-        <v>22</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>2.798155</v>
-      </c>
-      <c r="F55" t="n">
-        <v>21.5669</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.159133</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.017883</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.336095</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.017751</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" t="n">
-        <v>23</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" t="n">
-        <v>7.949332</v>
-      </c>
-      <c r="F56" t="n">
-        <v>25.587326</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.154339</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.018661</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.327846</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.017751</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>2</v>
-      </c>
-      <c r="B57" t="n">
-        <v>24</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>3</v>
-      </c>
-      <c r="E57" t="n">
-        <v>11.348658</v>
-      </c>
-      <c r="F57" t="n">
-        <v>6.902363</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.156126</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.020345</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.330476</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.017751</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2</v>
-      </c>
-      <c r="B58" t="n">
-        <v>25</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>4</v>
-      </c>
-      <c r="E58" t="n">
-        <v>3.864819</v>
-      </c>
-      <c r="F58" t="n">
-        <v>12.903469</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.153833</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.018888</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.325427</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.017751</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>2</v>
-      </c>
-      <c r="B59" t="n">
-        <v>26</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>5</v>
-      </c>
-      <c r="E59" t="n">
-        <v>13.976492</v>
-      </c>
-      <c r="F59" t="n">
-        <v>49.683661</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.15585</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.017806</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.332175</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.017751</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>2</v>
-      </c>
-      <c r="B60" t="n">
-        <v>27</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" t="n">
-        <v>5.239894</v>
-      </c>
-      <c r="F60" t="n">
-        <v>8.348601</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.160076</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.017999</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.337383</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.017751</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2</v>
-      </c>
-      <c r="B61" t="n">
-        <v>28</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Phase 3: local (mass loss only)</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>7</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2.416345</v>
-      </c>
-      <c r="F61" t="n">
-        <v>41.608103</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.164407</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.01941</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.350848</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.017751</v>
+      <c r="F36" s="1" t="n">
+        <v>0.320861</v>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -21708,216 +19864,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Table S10</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bayesian optimization settings used for parameter calibration (two independent repeats of 28 evaluations).</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Bayesian optimization settings used for parameter calibration.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Solver</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>FreeFEM++ (MPI), corrected-physics code v2 (chloride molar-unit fix in the film-dissolution term); hard-minimum rate rule</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Optimization method</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Bayesian optimization</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Calibration geometry</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Disc, diameter 10 mm x 2 mm, in a 30 x 30 x 30 mm box; coarse tetrahedral mesh (hmin 0.5 mm, 37,399 tetrahedra, 5,818 in the metal); closed box (no O2 inflow boundary)</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Surrogate model</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Process</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Time stepping</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>dt = 4 h, 336 h simulated per evaluation; no level-set redistancing; interface-relative velocity extension, probe distance 0.05 mm</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Objective function</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>RMSE minimization</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Parameters calibrated</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>k_f (film formation, 1/h), k_d (film dissolution, L2 mol-2 h-1, Cl- as mol/L), k_ORR (effective ORR coefficient, mm/h)</t>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>k_f, k_d, k_ORR</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Search bounds (log10-uniform)</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>k_f [1, 100]; k_d [1, 100] (Phase 3 allowed 0.1-100); k_ORR [0.05, 5]</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Prior distribution</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Uniform</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fixed parameters used in these runs</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>film porosity 0.25; film tortuosity 2.00; film density 5.606 g/cm3 (as in manuscript Table 1); D_O2 10.8, D_Zn 3.38, D_Cl 9.7, D_OH 25.45 mm2/h; C_O2,0 3.5 mg/L; Cl- 142.3 mmol/L; [Zn]sat 10 mg/L  (NOTE: diffusivities differ from manuscript Table 1 - to be reconciled)</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Parameter bounds</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Main-text Table 2</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Target data</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Liu et al., J. Mater. Sci. Technol. (2018), doi 10.1016/j.jmst.2018.05.005: mass loss and corrosion rate at 24, 48, 120, 168, 240, 336 h</t>
-        </is>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Random seed</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Mesh correction</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Coarse-to-fine bias correction: ML_fine = 1.355846 x ML_coarse - 0.001584 (Pearson r = 0.998644 vs the hmin 0.25 mm mesh); derived with the earlier code version</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Initial sampling</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>12-point Latin hypercube design (iterations 1–12)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Simulated corrosion rate</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>CR = ML/100 x m0 / (t rho A) x 8760 (cumulative average); m0 = 1.1217 g, rho = 0.00714 g/mm3, A = 238 mm2</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Acquisition function</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Expected improvement</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Objective, Phase 1-2</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>RMSE of corrected mass loss vs target (24-336 h)</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Total iterations</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>32 (optimum at iteration 22)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Objective, Phase 3</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>RMSE of corrected mass loss vs target (24-336 h), the same objective as Phases 1-2 (all points chosen and scored on mass loss only)</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Noise treatment</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Deterministic objective</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Design Phase 1</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>12-point Latin hypercube (scipy qmc), seeds 7 (repeat 1) and 101 (repeat 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Design Phase 2</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Gaussian process (Matern nu=2.5 + white noise; normalised log10 inputs; log10 RMSE output; 20 restarts), expected improvement, 8 points, minimum separation 0.15 (normalised). k_f and k_d length scales sat at the upper bound, so k_ORR was narrowed to the EI ridge (0.12-0.20) and k_f, k_d were stratified by Latin hypercube over [1,100]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Design Phase 3</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Same GP on log10 RMSE over all 20 evaluations; EI proposals; unresolved axes (k_f, k_d) stratified within a factor 3 of the current best point; 8 points</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>4 cores per evaluation, about 20 min; 28 evaluations per repeat, 2 repeats</t>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Target RMSE</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>0.05%</t>
         </is>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -16154,7 +16154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16173,7 +16173,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the reference mesh (21.25 million elements).</t>
+          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the fine mesh (18.9 million elements).</t>
         </is>
       </c>
     </row>
@@ -16209,10 +16209,10 @@
         <v>182768</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.439</v>
+        <v>0.024</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1465.8</v>
+        <v>-87.2</v>
       </c>
     </row>
     <row r="6">
@@ -16225,10 +16225,10 @@
         <v>802365</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.4977</v>
+        <v>0.1387</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>441.6</v>
+        <v>-26.2</v>
       </c>
     </row>
     <row r="7">
@@ -16241,10 +16241,10 @@
         <v>3454723</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.1633</v>
+        <v>0.1794</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>77.7</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="8">
@@ -16257,10 +16257,10 @@
         <v>4990080</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.1208</v>
+        <v>0.1846</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>31.4</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="9">
@@ -16273,10 +16273,10 @@
         <v>11958220</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.1002</v>
+        <v>0.1871</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>9</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="10">
@@ -16289,25 +16289,9 @@
         <v>18864900</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.0927</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>21245850</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>0.0919</v>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
+        <v>0.188</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -16344,7 +16328,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison between adaptive and uniform meshes at approximately 800,000 elements.</t>
+          <t>Comparison between an adaptive mesh (hmin = 0.1 mm, hmax = 2 mm) and a uniform mesh (1 mm everywhere).</t>
         </is>
       </c>
     </row>
@@ -16378,17 +16362,19 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Uniform Mesh</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>799520</v>
+          <t>Uniform (1 mm)</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>~229,000</t>
+        </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>2.8561</v>
+        <v>0.0415</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3007.8</v>
+        <v>-77.90000000000001</v>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
@@ -16399,33 +16385,33 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Adaptive Mesh</t>
+          <t>Adaptive (hmin 0.1 mm, hmax 2 mm)</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
         <v>802365</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.4977</v>
+        <v>0.1387</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>441.6</v>
+        <v>-26.2</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.8532</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Reference Mesh</t>
+          <t>Fine mesh (reference)</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>21245850</v>
+        <v>18864900</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.0919</v>
+        <v>0.188</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -16154,7 +16154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16173,7 +16173,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the fine mesh (18.9 million elements).</t>
+          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the 18.9 million-element mesh (L6); the 21.25 million-element reference mesh is listed for comparison.</t>
         </is>
       </c>
     </row>
@@ -16293,8 +16293,24 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21245850</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.9</v>
       </c>
     </row>
   </sheetData>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -21,12 +21,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 3" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 3" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 6b" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9a,b" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9c,d" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 2" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 4" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5b" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 6" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8a,b" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8c,d" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S1" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S2" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S3" sheetId="24" state="visible" r:id="rId24"/>
@@ -3646,7 +3646,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 3</t>
+          <t>Supplementary Figure 2</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 5</t>
+          <t>Supplementary Figure 4</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 6b</t>
+          <t>Supplementary Figure 5b</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 7</t>
+          <t>Supplementary Figure 6</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 9a,b</t>
+          <t>Supplementary Figure 8a,b</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15888,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 9c,d</t>
+          <t>Supplementary Figure 8c,d</t>
         </is>
       </c>
     </row>
@@ -16173,7 +16173,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the 18.9 million-element mesh (L6); the 21.25 million-element reference mesh is listed for comparison.</t>
+          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the reference mesh.</t>
         </is>
       </c>
     </row>
@@ -16200,101 +16200,99 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>L1 (Very Low)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" t="n">
         <v>182768</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" t="n">
         <v>0.024</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" t="n">
         <v>-87.2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>L2 (Low)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" t="n">
         <v>802365</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" t="n">
         <v>0.1387</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" t="n">
         <v>-26.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>L3 (Medium)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" t="n">
         <v>3454723</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" t="n">
         <v>0.1794</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" t="n">
         <v>-4.6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>L4 (High)</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" t="n">
         <v>4990080</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" t="n">
         <v>0.1846</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" t="n">
         <v>-1.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>L5 (Very High)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" t="n">
         <v>11958220</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" t="n">
         <v>0.1871</v>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>-0.5</v>
+      <c r="D9" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>L6 (Ultra High)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" t="n">
         <v>18864900</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" t="n">
         <v>0.188</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
+      <c r="D10" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="11">
@@ -16307,10 +16305,10 @@
         <v>21245850</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1864</v>
+        <v>0.1897</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -16344,7 +16342,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison between an adaptive mesh (hmin = 0.1 mm, hmax = 2 mm) and a uniform mesh (1 mm everywhere).</t>
+          <t>Comparison between an adaptive mesh and a uniform mesh (approximately 800,000 elements).</t>
         </is>
       </c>
     </row>
@@ -16376,65 +16374,63 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Uniform (1 mm)</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>~229,000</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uniform Mesh</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>799000</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.0415</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" t="n">
         <v>-77.90000000000001</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Adaptive (hmin 0.1 mm, hmax 2 mm)</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Adaptive Mesh</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>802365</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" t="n">
         <v>0.1387</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" t="n">
         <v>-26.2</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" t="n">
         <v>0.663</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Fine mesh (reference)</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Reference Mesh</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>18864900</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" t="n">
         <v>0.188</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" t="n">
         <v>1</v>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -16209,10 +16209,10 @@
         <v>182768</v>
       </c>
       <c r="C5" t="n">
-        <v>0.024</v>
+        <v>0.3009</v>
       </c>
       <c r="D5" t="n">
-        <v>-87.2</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="6">
@@ -16225,10 +16225,10 @@
         <v>802365</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1387</v>
+        <v>0.2029</v>
       </c>
       <c r="D6" t="n">
-        <v>-26.2</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="7">
@@ -16241,10 +16241,10 @@
         <v>3454723</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1794</v>
+        <v>0.1682</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -16257,10 +16257,10 @@
         <v>4990080</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1846</v>
+        <v>0.1637</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -16273,7 +16273,7 @@
         <v>11958220</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1871</v>
+        <v>0.1616</v>
       </c>
       <c r="D9" t="n">
         <v>0.5</v>
@@ -16289,7 +16289,7 @@
         <v>18864900</v>
       </c>
       <c r="C10" t="n">
-        <v>0.188</v>
+        <v>0.1622</v>
       </c>
       <c r="D10" t="n">
         <v>0.87</v>
@@ -16305,10 +16305,12 @@
         <v>21245850</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1897</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9</v>
+        <v>0.1608</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -16383,10 +16385,10 @@
         <v>799000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0415</v>
+        <v>0.286</v>
       </c>
       <c r="D5" t="n">
-        <v>-77.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -16404,10 +16406,10 @@
         <v>802365</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1387</v>
+        <v>0.2029</v>
       </c>
       <c r="D6" t="n">
-        <v>-26.2</v>
+        <v>26.2</v>
       </c>
       <c r="E6" t="n">
         <v>0.663</v>
@@ -16420,10 +16422,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18864900</v>
+        <v>21245850</v>
       </c>
       <c r="C7" t="n">
-        <v>0.188</v>
+        <v>0.1608</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -16289,10 +16289,10 @@
         <v>18864900</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1622</v>
+        <v>0.1611</v>
       </c>
       <c r="D10" t="n">
-        <v>0.87</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="11">

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -2968,6 +2968,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3018,7 +3019,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>[46]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3041,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>[46]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3073,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3095,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3117,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3139,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>[48]</t>
+          <t>[34]</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3171,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3191,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>[49]</t>
+          <t>[35]</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3211,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>[50]</t>
+          <t>[36]</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3233,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>[46]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3265,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[37]</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3313,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>[52]</t>
+          <t>[38]</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3335,7 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>[29]</t>
+          <t>[21]</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3355,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>[53]</t>
+          <t>[39]</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16063,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) best matched literature mass-loss measurements and was adopted in the final model.</t>
+          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) gave the lowest RMSE, which was used as a consistency check but was not the main selection criterion, and was adopted on physical grounds (RMSE values may differ from those of the calibrated model, as these validation cases were evaluated prior to model calibration).</t>
         </is>
       </c>
     </row>
@@ -17214,10 +17215,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Parameters included in the Morris sensitivity analysis.</t>
-        </is>
-      </c>
-    </row>
+          <t>Parameters included in the Morris sensitivity analysis (the ranges might differ from calibration space as this was done prior to calibration of the model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17280,7 +17282,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>mm^6 g^-2 h^-1</t>
+          <t>L^2 mol^-2 h^-1</t>
         </is>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -2964,7 +2964,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model parameters used in the Zn biodegradation simulation.</t>
+          <t>Model parameters used in the Zn biodegradation simulation. The simulations used diffusivities 15-26% above the tabulated values (mm^2 h^-1: Zn2+ 3.38, Cl- 9.7, OH- 25.45, O2 10.8) and a film tortuosity of 120.</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>5.606 g cm^-3</t>
+          <t>3.998 g cm^-3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -3248,26 +3248,10 @@
       <c r="D18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Zn2+ sat. concentration</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>[Zn]_sat</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>10 mg L^-1</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>[37]</t>
-        </is>
-      </c>
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="n"/>
+      <c r="D19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3308,7 +3292,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>142.3 mmol L^-1</t>
+          <t>142.3 mmol L^-1 (5.04e-6 g mm^-3)</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -3330,7 +3314,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>3.5 mg L^-1</t>
+          <t>3.5 mg L^-1 (3.5e-9 g mm^-3)</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -3393,6 +3377,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3428,11 +3413,13 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>[1, 100]</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>35.91</v>
+          <t>[1, 1e5]</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>[v4 optimum]</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3448,11 +3435,13 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>[5, 100]</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>27.17</v>
+          <t>[0.01, 1e3]</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>[v4 optimum]</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3468,11 +3457,13 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>[0.05, 5.0]</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.51</v>
+          <t>[0.5, 50]</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>[v4 optimum]</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -16471,6 +16462,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -16719,7 +16711,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>802,365</t>
+          <t>37,399</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -16741,7 +16733,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>121,120</t>
+          <t>[to update]</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -16763,7 +16755,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>0.1 mm</t>
+          <t>0.5 mm</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -16839,7 +16831,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>0.25 h</t>
+          <t>4 h</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -16914,7 +16906,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>50</v>
@@ -16931,7 +16923,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>2,592</t>
+          <t>[to update]</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -17041,7 +17033,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>2 h</t>
+          <t>~20 min</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -17149,7 +17141,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Dirichlet</t>
+          <t>Dirichlet (C_O2 = 3.5 mg L^-1)</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -17219,7 +17211,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -2968,7 +2968,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3430,12 +3429,12 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>L^2 mol^-2 h^-1</t>
+          <t>mm^6 g^-2 h^-1</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>[0.01, 1e3]</t>
+          <t>[8.0e6, 8.0e11]</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -16462,7 +16461,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17211,6 +17209,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17273,7 +17272,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>L^2 mol^-2 h^-1</t>
+          <t>mm^6 g^-2 h^-1</t>
         </is>
       </c>
     </row>

--- a/SourceData_original_order.xlsx
+++ b/SourceData_original_order.xlsx
@@ -21,12 +21,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 3" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 2" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 4" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5b" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 6" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8a,b" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8c,d" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 3" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 4b" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7a,b" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7c,d" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S1" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S2" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S3" sheetId="24" state="visible" r:id="rId24"/>
@@ -3376,7 +3376,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3637,7 +3636,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 2</t>
+          <t>Supplementary Figure 1</t>
         </is>
       </c>
     </row>
@@ -3648,6 +3647,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 4</t>
+          <t>Supplementary Figure 3</t>
         </is>
       </c>
     </row>
@@ -3838,6 +3838,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5120,7 +5121,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 5b</t>
+          <t>Supplementary Figure 4b</t>
         </is>
       </c>
     </row>
@@ -5138,6 +5139,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -5928,7 +5930,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 6</t>
+          <t>Supplementary Figure 5</t>
         </is>
       </c>
     </row>
@@ -5939,6 +5941,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -10058,6 +10061,7 @@
       </c>
       <c r="H174" s="1" t="n"/>
     </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
@@ -11843,7 +11847,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 8a,b</t>
+          <t>Supplementary Figure 7a,b</t>
         </is>
       </c>
     </row>
@@ -11854,6 +11858,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -15785,6 +15790,7 @@
         <v>3.411422</v>
       </c>
     </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
@@ -15879,7 +15885,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 8c,d</t>
+          <t>Supplementary Figure 7c,d</t>
         </is>
       </c>
     </row>
@@ -15890,6 +15896,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -16035,7 +16042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16044,94 +16051,85 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Table S1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) gave the lowest RMSE, which was used as a consistency check but was not the main selection criterion, and was adopted on physical grounds (RMSE values may differ from those of the calibrated model, as these validation cases were evaluated prior to model calibration).</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Limiting regimes of the interfacial oxygen flux.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>RMSE (%)</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regime</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Interfacial flux J_O2</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Hard minimum</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0.0568</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Reaction-controlled</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Da &lt;&lt; 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>k_ORR C_b</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Mixed control</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>0.077</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Da ~ 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C_b/(1/k_ORR + delta/D_O2,eff)</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Hybrid cathodic</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0.0766</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Coupled ORR (no O2 cap)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0.2983</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Diffusion-controlled</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Da &gt;&gt; 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D_O2,eff C_b/delta</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -17209,7 +17207,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
